--- a/docs/throttle_curve.xlsx
+++ b/docs/throttle_curve.xlsx
@@ -2306,37 +2306,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <xdr:twoCellAnchor>
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="5200650" cy="9639300"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="1" name="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
-        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2c67b8969846442c"/>
+          <c:chart r:id="R2c67b8969846442c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/docs/throttle_curve.xlsx
+++ b/docs/throttle_curve.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4421ADC-D504-4888-8C6B-BC9395912B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8300B69C-D164-481D-913D-ED74C7CA62F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Throttle Curves" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
   <si>
     <t>Astral · Throttle curves</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>Astral · Throttle parameters</t>
-  </si>
-  <si>
-    <t>黄色单元格为各 ECU 独立的 a / k；初始值与当前 JBeam 一致。</t>
   </si>
   <si>
     <t>1 · Progressive</t>
@@ -67,55 +64,16 @@
     <t>k</t>
   </si>
   <si>
-    <t>ECU part</t>
-  </si>
-  <si>
-    <t>Astral_enginemanagement_rally2</t>
-  </si>
-  <si>
     <t>WRC17 / Rally1</t>
-  </si>
-  <si>
-    <t>Astral_enginemanagement_wrc17</t>
   </si>
   <si>
     <t>WRC (11–16)</t>
   </si>
   <si>
-    <t>Astral_enginemanagement_tribute</t>
-  </si>
-  <si>
     <t>RX1</t>
   </si>
   <si>
-    <t>Astral_enginemanagement_rx</t>
-  </si>
-  <si>
     <t>RX3</t>
-  </si>
-  <si>
-    <t>Astral_enginemanagement_rx3</t>
-  </si>
-  <si>
-    <t>y = (1 − a) × ln(1 + k × x) / ln(1 + k) + a × x；k = 0 时，y = x。</t>
-  </si>
-  <si>
-    <t>x 为油门输入，y 为映射输出，均为 0～1；图中用百分比显示。</t>
-  </si>
-  <si>
-    <t>a：线性部分权重（0～1）；k：对数曲线系数（大于 −1）。</t>
-  </si>
-  <si>
-    <t>WRC17 与 Rally1 当前共用同一个 ECU，调整这一行会对应这套共用标定。</t>
-  </si>
-  <si>
-    <t>本表是参数设计表；Excel 参数不会自动写回 JBeam。</t>
-  </si>
-  <si>
-    <t>数据来源：Astral_ecu.jbeam 的 throttleMap.maps；计算公式：throttleMap.lua。</t>
-  </si>
-  <si>
-    <t>绘图点由公式自动计算，步长 1%；曲线平滑已开启。</t>
   </si>
   <si>
     <t>Astral · Throttle samples</t>
@@ -140,7 +98,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -152,9 +110,66 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="20"/>
       <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -171,36 +186,77 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF667B91"/>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Carlito"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -214,11 +270,106 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF31475E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -226,54 +377,197 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="20" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="22" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -309,7 +603,7 @@
             <a:r>
               <a:rPr lang="en-US" sz="1200">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="微软雅黑"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
               <a:t>Throttle input / output</a:t>
@@ -2332,7 +2626,7 @@
                 <a:r>
                   <a:rPr lang="en-US" sz="900">
                     <a:latin typeface="Arial"/>
-                    <a:ea typeface="Arial"/>
+                    <a:ea typeface="微软雅黑"/>
                     <a:cs typeface="Arial"/>
                   </a:rPr>
                   <a:t>Throttle output</a:t>
@@ -2353,7 +2647,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="微软雅黑"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -2383,7 +2677,7 @@
                 <a:r>
                   <a:rPr lang="en-US" sz="900">
                     <a:latin typeface="Arial"/>
-                    <a:ea typeface="Arial"/>
+                    <a:ea typeface="微软雅黑"/>
                     <a:cs typeface="Arial"/>
                   </a:rPr>
                   <a:t>Throttle input</a:t>
@@ -2411,7 +2705,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="微软雅黑"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -2434,7 +2728,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="Arial"/>
+              <a:ea typeface="微软雅黑"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -2464,19 +2758,14 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="11246386" cy="5623193"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart">
@@ -2499,7 +2788,7 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2708,7 +2997,7 @@
     <col min="2" max="15" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="23" customHeight="1">
+    <row r="1" spans="1:15" ht="12" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2725,23 +3014,23 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="23" customHeight="1">
+    <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="23" customHeight="1">
@@ -2763,14 +3052,14 @@
     </row>
     <row r="4" spans="1:15" ht="23" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
+      <c r="C4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -3399,7 +3688,7 @@
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="C4:E4"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <extLst>
@@ -3432,7 +3721,7 @@
     <col min="10" max="14" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="23" customHeight="1">
+    <row r="1" spans="1:14" ht="12" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3448,41 +3737,26 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" ht="23" customHeight="1">
+    <row r="2" spans="1:14" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
     </row>
     <row r="3" spans="1:14" ht="23" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
     </row>
     <row r="4" spans="1:14" ht="23" customHeight="1">
       <c r="A4" s="1"/>
@@ -3500,21 +3774,21 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" ht="23" customHeight="1">
+    <row r="5" spans="1:14" ht="32" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="23"/>
+      <c r="G5" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="14"/>
+      <c r="H5" s="23"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -3522,197 +3796,155 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="23" customHeight="1">
+    <row r="6" spans="1:14" ht="32" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" ht="31" customHeight="1">
+      <c r="A7" s="1"/>
+      <c r="B7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-0.92</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="6">
+        <v>-0.45</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" ht="31" customHeight="1">
+      <c r="A8" s="1"/>
+      <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="12" t="s">
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-0.95</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="6">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="H8" s="6">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" ht="31" customHeight="1">
+      <c r="A9" s="1"/>
+      <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-    </row>
-    <row r="7" spans="1:14" ht="23" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="C9" s="6">
         <v>0</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D9" s="6">
         <v>-0.92</v>
       </c>
-      <c r="E7" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="E9" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="F9" s="6">
         <v>-0.45</v>
       </c>
-      <c r="G7" s="4">
-        <v>0.35</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="G9" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="6">
         <v>1.5</v>
       </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="11" t="s">
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" ht="31" customHeight="1">
+      <c r="A10" s="1"/>
+      <c r="B10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-    </row>
-    <row r="8" spans="1:14" ht="23" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
+      <c r="C10" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-0.88</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.69</v>
+      </c>
+      <c r="F10" s="6">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.59</v>
+      </c>
+      <c r="H10" s="6">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" ht="31" customHeight="1">
+      <c r="A11" s="1"/>
+      <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="4">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4">
-        <v>-0.95</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="F8" s="4">
-        <v>-0.55000000000000004</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-    </row>
-    <row r="9" spans="1:14" ht="23" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4">
-        <v>-0.92</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="F9" s="4">
-        <v>-0.45</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="H9" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-    </row>
-    <row r="10" spans="1:14" ht="23" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="4">
+      <c r="C11" s="6">
         <v>0.15</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D11" s="6">
         <v>-0.88</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E11" s="6">
         <v>0.69</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F11" s="6">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G11" s="6">
         <v>0.59</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H11" s="6">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I10" s="1"/>
-      <c r="J10" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-    </row>
-    <row r="11" spans="1:14" ht="23" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="D11" s="4">
-        <v>-0.88</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0.69</v>
-      </c>
-      <c r="F11" s="4">
-        <v>-0.28000000000000003</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0.59</v>
-      </c>
-      <c r="H11" s="4">
-        <v>9.8000000000000007</v>
-      </c>
       <c r="I11" s="1"/>
-      <c r="J11" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
     </row>
     <row r="12" spans="1:14" ht="23" customHeight="1">
       <c r="A12" s="1"/>
@@ -3748,129 +3980,24 @@
     </row>
     <row r="14" spans="1:14" ht="23" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
     </row>
     <row r="15" spans="1:14" ht="23" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
     </row>
     <row r="16" spans="1:14" ht="23" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
     </row>
     <row r="17" spans="1:14" ht="23" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
     </row>
     <row r="18" spans="1:14" ht="23" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
     </row>
     <row r="19" spans="1:14" ht="23" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
     </row>
     <row r="20" spans="1:14" ht="23" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
     </row>
     <row r="21" spans="1:14" ht="23" customHeight="1">
       <c r="A21" s="1"/>
@@ -3921,27 +4048,13 @@
       <c r="N23" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="4">
     <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:N3"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="J6:N6"/>
-    <mergeCell ref="J7:N7"/>
-    <mergeCell ref="J8:N8"/>
-    <mergeCell ref="J9:N9"/>
-    <mergeCell ref="J10:N10"/>
-    <mergeCell ref="B18:N18"/>
-    <mergeCell ref="B19:N19"/>
-    <mergeCell ref="B20:N20"/>
-    <mergeCell ref="J11:N11"/>
-    <mergeCell ref="B14:N14"/>
-    <mergeCell ref="B15:N15"/>
-    <mergeCell ref="B16:N16"/>
-    <mergeCell ref="B17:N17"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="decimal" sqref="C7:C11 G7:G11 E7:E11" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
@@ -3970,7 +4083,7 @@
     <col min="8" max="11" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23" customHeight="1">
+    <row r="1" spans="1:11" ht="12" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3983,20 +4096,20 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="23" customHeight="1">
+    <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="B2" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
     </row>
     <row r="3" spans="1:11" ht="23" customHeight="1">
       <c r="A3" s="1"/>
@@ -4018,30 +4131,30 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="8" t="str">
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="20" t="str">
         <f>'Throttle Curves'!C4</f>
         <v>WRC17 / Rally1</v>
       </c>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-    </row>
-    <row r="5" spans="1:11" ht="23" customHeight="1">
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+    </row>
+    <row r="5" spans="1:11" ht="32" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="8" t="s">
         <v>6</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -4050,28 +4163,28 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="23" customHeight="1">
+    <row r="6" spans="1:11" ht="31" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="5">
+      <c r="B6" s="9">
         <v>0</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="9">
         <f t="shared" ref="C6:C37" si="0">IF($I$9=0,$B6,(1-$H$9)*LN(1+$I$9*$B6)/LN(1+$I$9)+$H$9*$B6)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="9">
         <f t="shared" ref="D6:D37" si="1">IF($I$10=0,$B6,(1-$H$10)*LN(1+$I$10*$B6)/LN(1+$I$10)+$H$10*$B6)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="9">
         <f t="shared" ref="E6:E37" si="2">IF($I$11=0,$B6,(1-$H$11)*LN(1+$I$11*$B6)/LN(1+$I$11)+$H$11*$B6)</f>
         <v>0</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="G6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="11">
         <f>MATCH('Throttle Curves'!C4,Parameters!B7:B11,0)</f>
         <v>2</v>
       </c>
@@ -4079,20 +4192,20 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" ht="23" customHeight="1">
+    <row r="7" spans="1:11" ht="31" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="5">
+      <c r="B7" s="12">
         <v>0.01</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="12">
         <f t="shared" si="0"/>
         <v>3.186337086193345E-3</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="12">
         <f t="shared" si="1"/>
         <v>7.6801448322603195E-3</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="12">
         <f t="shared" si="2"/>
         <v>1.391976367936305E-2</v>
       </c>
@@ -4103,146 +4216,146 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" ht="23" customHeight="1">
+    <row r="8" spans="1:11" ht="32" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="5">
+      <c r="B8" s="9">
         <v>0.02</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="9">
         <f t="shared" si="0"/>
         <v>6.4033824337768443E-3</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="9">
         <f t="shared" si="1"/>
         <v>1.5389017612306488E-2</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="9">
         <f t="shared" si="2"/>
         <v>2.7712236977093824E-2</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="G8" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>8</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" ht="23" customHeight="1">
+    <row r="9" spans="1:11" ht="31" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="5">
+      <c r="B9" s="12">
         <v>0.03</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="12">
         <f t="shared" si="0"/>
         <v>9.6517337079458313E-3</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="12">
         <f t="shared" si="1"/>
         <v>2.3126938755721561E-2</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="12">
         <f t="shared" si="2"/>
         <v>4.1379903667644352E-2</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1">
+      <c r="G9" s="14">
         <v>1</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="15">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,1)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="15">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,2)</f>
         <v>-0.95</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" ht="23" customHeight="1">
+    <row r="10" spans="1:11" ht="31" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="5">
+      <c r="B10" s="9">
         <v>0.04</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="9">
         <f t="shared" si="0"/>
         <v>1.2932006193754548E-2</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="9">
         <f t="shared" si="1"/>
         <v>3.0894234068771745E-2</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="9">
         <f t="shared" si="2"/>
         <v>5.4925175529730766E-2</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="1">
+      <c r="G10" s="16">
         <v>2</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="17">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,3)</f>
         <v>0.25</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="17">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,4)</f>
         <v>-0.55000000000000004</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11" ht="23" customHeight="1">
+    <row r="11" spans="1:11" ht="31" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="5">
+      <c r="B11" s="12">
         <v>0.05</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="12">
         <f t="shared" si="0"/>
         <v>1.6244833495600405E-2</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="12">
         <f t="shared" si="1"/>
         <v>3.8691234870011873E-2</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="12">
         <f t="shared" si="2"/>
         <v>6.835039510225821E-2</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="1">
+      <c r="G11" s="14">
         <v>3</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="15">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,5)</f>
         <v>0.1</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="15">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,6)</f>
         <v>1</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="1:11" ht="23" customHeight="1">
+    <row r="12" spans="1:11" ht="31" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="5">
+      <c r="B12" s="9">
         <v>0.06</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="9">
         <f t="shared" si="0"/>
         <v>1.9590868271767738E-2</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="9">
         <f t="shared" si="1"/>
         <v>4.6518278115341136E-2</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="9">
         <f t="shared" si="2"/>
         <v>8.1657838309627112E-2</v>
       </c>
@@ -4253,20 +4366,20 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" ht="23" customHeight="1">
+    <row r="13" spans="1:11" ht="31" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="5">
+      <c r="B13" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="12">
         <f t="shared" si="0"/>
         <v>2.2970783006160234E-2</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="12">
         <f t="shared" si="1"/>
         <v>5.437570652662372E-2</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="12">
         <f t="shared" si="2"/>
         <v>9.4849716963780112E-2</v>
       </c>
@@ -4277,20 +4390,20 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" ht="23" customHeight="1">
+    <row r="14" spans="1:11" ht="31" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="5">
+      <c r="B14" s="9">
         <v>0.08</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="9">
         <f t="shared" si="0"/>
         <v>2.6385270819504796E-2</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="9">
         <f t="shared" si="1"/>
         <v>6.2263868724000346E-2</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="9">
         <f t="shared" si="2"/>
         <v>0.10792818114986957</v>
       </c>
@@ -4301,20 +4414,20 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" ht="23" customHeight="1">
+    <row r="15" spans="1:11" ht="31" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="5">
+      <c r="B15" s="12">
         <v>0.09</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="12">
         <f t="shared" si="0"/>
         <v>2.9835046322475019E-2</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="12">
         <f t="shared" si="1"/>
         <v>7.0183119362015323E-2</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="12">
         <f t="shared" si="2"/>
         <v>0.12089532150198161</v>
       </c>
@@ -4325,20 +4438,20 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" ht="23" customHeight="1">
+    <row r="16" spans="1:11" ht="31" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="5">
+      <c r="B16" s="9">
         <v>0.1</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="9">
         <f t="shared" si="0"/>
         <v>3.33208465133598E-2</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="9">
         <f t="shared" si="1"/>
         <v>7.8133819269695204E-2</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="9">
         <f t="shared" si="2"/>
         <v>0.13375317137494153</v>
       </c>
@@ -4349,20 +4462,20 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" ht="23" customHeight="1">
+    <row r="17" spans="1:11" ht="31" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="5">
+      <c r="B17" s="12">
         <v>0.11</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="12">
         <f t="shared" si="0"/>
         <v>3.6843431723099021E-2</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="12">
         <f t="shared" si="1"/>
         <v>8.6116335594713919E-2</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="12">
         <f t="shared" si="2"/>
         <v>0.14650370891784326</v>
       </c>
@@ -4373,20 +4486,20 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" ht="23" customHeight="1">
+    <row r="18" spans="1:11" ht="31" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="5">
+      <c r="B18" s="9">
         <v>0.12</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="9">
         <f t="shared" si="0"/>
         <v>4.0403586610716101E-2</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="9">
         <f t="shared" si="1"/>
         <v>9.4131041951792213E-2</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="9">
         <f t="shared" si="2"/>
         <v>0.15914885905459161</v>
       </c>
@@ -4397,20 +4510,20 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:11" ht="23" customHeight="1">
+    <row r="19" spans="1:11" ht="31" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="5">
+      <c r="B19" s="12">
         <v>0.13</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="12">
         <f t="shared" si="0"/>
         <v>4.4002121212408853E-2</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="12">
         <f t="shared" si="1"/>
         <v>0.10217831857547742</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="12">
         <f t="shared" si="2"/>
         <v>0.17169049537641662</v>
       </c>
@@ -4421,20 +4534,20 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" ht="23" customHeight="1">
+    <row r="20" spans="1:11" ht="31" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="5">
+      <c r="B20" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="9">
         <f t="shared" si="0"/>
         <v>4.7639872047806051E-2</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="9">
         <f t="shared" si="1"/>
         <v>0.1102585524774635</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="9">
         <f t="shared" si="2"/>
         <v>0.18413044195101544</v>
       </c>
@@ -4445,20 +4558,20 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" ht="23" customHeight="1">
+    <row r="21" spans="1:11" ht="31" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="5">
+      <c r="B21" s="12">
         <v>0.15</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="12">
         <f t="shared" si="0"/>
         <v>5.1317703287169718E-2</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="12">
         <f t="shared" si="1"/>
         <v>0.11837213760861129</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="12">
         <f t="shared" si="2"/>
         <v>0.19647047505268539</v>
       </c>
@@ -4469,20 +4582,20 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" ht="23" customHeight="1">
+    <row r="22" spans="1:11" ht="31" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="5">
+      <c r="B22" s="9">
         <v>0.16</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="9">
         <f t="shared" si="0"/>
         <v>5.5036507983617249E-2</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="9">
         <f t="shared" si="1"/>
         <v>0.1265194750258396</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="9">
         <f t="shared" si="2"/>
         <v>0.20871232481756263</v>
       </c>
@@ -4493,20 +4606,20 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" ht="23" customHeight="1">
+    <row r="23" spans="1:11" ht="31" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="5">
+      <c r="B23" s="12">
         <v>0.17</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="12">
         <f t="shared" si="0"/>
         <v>5.8797209374757908E-2</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="12">
         <f t="shared" si="1"/>
         <v>0.13470097306406517</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="12">
         <f t="shared" si="2"/>
         <v>0.22085767682781182</v>
       </c>
@@ -4517,20 +4630,20 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" ht="23" customHeight="1">
+    <row r="24" spans="1:11" ht="31" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="5">
+      <c r="B24" s="9">
         <v>0.18</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="9">
         <f t="shared" si="0"/>
         <v>6.2600762258491024E-2</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="9">
         <f t="shared" si="1"/>
         <v>0.1429170475133727</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="9">
         <f t="shared" si="2"/>
         <v>0.23290817362840482</v>
       </c>
@@ -4541,20 +4654,20 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
-    <row r="25" spans="1:11" ht="23" customHeight="1">
+    <row r="25" spans="1:11" ht="31" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="5">
+      <c r="B25" s="12">
         <v>0.19</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="12">
         <f t="shared" si="0"/>
         <v>6.6448154448093127E-2</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="12">
         <f t="shared" si="1"/>
         <v>0.15116812180161127</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="12">
         <f t="shared" si="2"/>
         <v>0.24486541617989693</v>
       </c>
@@ -4565,20 +4678,20 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
     </row>
-    <row r="26" spans="1:11" ht="23" customHeight="1">
+    <row r="26" spans="1:11" ht="31" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="5">
+      <c r="B26" s="9">
         <v>0.2</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="9">
         <f t="shared" si="0"/>
         <v>7.0340408312143138E-2</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="9">
         <f t="shared" si="1"/>
         <v>0.1594546271826133</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="9">
         <f t="shared" si="2"/>
         <v>0.25673096525041444</v>
       </c>
@@ -4589,20 +4702,20 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
     </row>
-    <row r="27" spans="1:11" ht="23" customHeight="1">
+    <row r="27" spans="1:11" ht="31" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="5">
+      <c r="B27" s="12">
         <v>0.21</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="12">
         <f t="shared" si="0"/>
         <v>7.4278582405290297E-2</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="12">
         <f t="shared" si="1"/>
         <v>0.1677770029302495</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="12">
         <f t="shared" si="2"/>
         <v>0.26850634274988283</v>
       </c>
@@ -4613,20 +4726,20 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
     </row>
-    <row r="28" spans="1:11" ht="23" customHeight="1">
+    <row r="28" spans="1:11" ht="31" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="5">
+      <c r="B28" s="9">
         <v>0.22</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="9">
         <f t="shared" si="0"/>
         <v>7.8263773196372607E-2</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="9">
         <f t="shared" si="1"/>
         <v>0.1761356965385342</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="9">
         <f t="shared" si="2"/>
         <v>0.28019303300934545</v>
       </c>
@@ -4637,20 +4750,20 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
     </row>
-    <row r="29" spans="1:11" ht="23" customHeight="1">
+    <row r="29" spans="1:11" ht="31" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="5">
+      <c r="B29" s="12">
         <v>0.23</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="12">
         <f t="shared" si="0"/>
         <v>8.2297116900944781E-2</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="12">
         <f t="shared" si="1"/>
         <v>0.18453116392801255</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="12">
         <f t="shared" si="2"/>
         <v>0.29179248400806368</v>
       </c>
@@ -4661,20 +4774,20 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
-    <row r="30" spans="1:11" ht="23" customHeight="1">
+    <row r="30" spans="1:11" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="5">
+      <c r="B30" s="9">
         <v>0.24</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="9">
         <f t="shared" si="0"/>
         <v>8.6379791425876637E-2</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="9">
         <f t="shared" si="1"/>
         <v>0.19296386965866436</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="9">
         <f t="shared" si="2"/>
         <v>0.30330610855093548</v>
       </c>
@@ -4685,20 +4798,20 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:11" ht="23" customHeight="1">
+    <row r="31" spans="1:11" ht="31" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="5">
+      <c r="B31" s="12">
         <v>0.25</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="12">
         <f t="shared" si="0"/>
         <v>9.0513018434350292E-2</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="12">
         <f t="shared" si="1"/>
         <v>0.20143428714957642</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="12">
         <f t="shared" si="2"/>
         <v>0.31473528539862616</v>
       </c>
@@ -4709,20 +4822,20 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:11" ht="23" customHeight="1">
+    <row r="32" spans="1:11" ht="31" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="5">
+      <c r="B32" s="9">
         <v>0.26</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="9">
         <f t="shared" si="0"/>
         <v>9.469806554031196E-2</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="9">
         <f t="shared" si="1"/>
         <v>0.20994289890563997</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="9">
         <f t="shared" si="2"/>
         <v>0.32608136035267266</v>
       </c>
@@ -4733,20 +4846,20 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
     </row>
-    <row r="33" spans="1:11" ht="23" customHeight="1">
+    <row r="33" spans="1:11" ht="31" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="5">
+      <c r="B33" s="12">
         <v>0.27</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="12">
         <f t="shared" si="0"/>
         <v>9.8936248642242236E-2</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="12">
         <f t="shared" si="1"/>
         <v>0.21849019675154671</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="12">
         <f t="shared" si="2"/>
         <v>0.33734564729769712</v>
       </c>
@@ -4757,20 +4870,20 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
     </row>
-    <row r="34" spans="1:11" ht="23" customHeight="1">
+    <row r="34" spans="1:11" ht="31" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="5">
+      <c r="B34" s="9">
         <v>0.28000000000000003</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="9">
         <f t="shared" si="0"/>
         <v>0.10322893440699456</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="9">
         <f t="shared" si="1"/>
         <v>0.22707668207336662</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="9">
         <f t="shared" si="2"/>
         <v>0.34852942920274782</v>
       </c>
@@ -4781,20 +4894,20 @@
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
     </row>
-    <row r="35" spans="1:11" ht="23" customHeight="1">
+    <row r="35" spans="1:11" ht="31" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="5">
+      <c r="B35" s="12">
         <v>0.28999999999999998</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="12">
         <f t="shared" si="0"/>
         <v>0.10757754291543231</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="12">
         <f t="shared" si="1"/>
         <v>0.23570286606800478</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="12">
         <f t="shared" si="2"/>
         <v>0.35963395908367646</v>
       </c>
@@ -4805,20 +4918,20 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
     </row>
-    <row r="36" spans="1:11" ht="23" customHeight="1">
+    <row r="36" spans="1:11" ht="31" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="5">
+      <c r="B36" s="9">
         <v>0.3</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="9">
         <f t="shared" si="0"/>
         <v>0.11198355048268077</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="9">
         <f t="shared" si="1"/>
         <v>0.24436927000084591</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="9">
         <f t="shared" si="2"/>
         <v>0.37066046092835692</v>
       </c>
@@ -4829,20 +4942,20 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
     </row>
-    <row r="37" spans="1:11" ht="23" customHeight="1">
+    <row r="37" spans="1:11" ht="31" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="5">
+      <c r="B37" s="12">
         <v>0.31</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="12">
         <f t="shared" si="0"/>
         <v>0.11644849266700712</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="12">
         <f t="shared" si="1"/>
         <v>0.25307642547191278</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="12">
         <f t="shared" si="2"/>
         <v>0.3816101305864531</v>
       </c>
@@ -4853,20 +4966,20 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
     </row>
-    <row r="38" spans="1:11" ht="23" customHeight="1">
+    <row r="38" spans="1:11" ht="31" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="5">
+      <c r="B38" s="9">
         <v>0.32</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="9">
         <f t="shared" ref="C38:C69" si="3">IF($I$9=0,$B38,(1-$H$9)*LN(1+$I$9*$B38)/LN(1+$I$9)+$H$9*$B38)</f>
         <v>0.12097396748267401</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="9">
         <f t="shared" ref="D38:D69" si="4">IF($I$10=0,$B38,(1-$H$10)*LN(1+$I$10*$B38)/LN(1+$I$10)+$H$10*$B38)</f>
         <v>0.26182487469087928</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="9">
         <f t="shared" ref="E38:E69" si="5">IF($I$11=0,$B38,(1-$H$11)*LN(1+$I$11*$B38)/LN(1+$I$11)+$H$11*$B38)</f>
         <v>0.39248413662535597</v>
       </c>
@@ -4877,20 +4990,20 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
     </row>
-    <row r="39" spans="1:11" ht="23" customHeight="1">
+    <row r="39" spans="1:11" ht="31" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="5">
+      <c r="B39" s="12">
         <v>0.33</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="12">
         <f t="shared" si="3"/>
         <v>0.12556163883358859</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="12">
         <f t="shared" si="4"/>
         <v>0.27061517076129021</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="12">
         <f t="shared" si="5"/>
         <v>0.40328362115381855</v>
       </c>
@@ -4901,20 +5014,20 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
-    <row r="40" spans="1:11" ht="23" customHeight="1">
+    <row r="40" spans="1:11" ht="31" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="5">
+      <c r="B40" s="9">
         <v>0.34</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="9">
         <f t="shared" si="3"/>
         <v>0.13021324018620845</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="9">
         <f t="shared" si="4"/>
         <v>0.27944787797436538</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="9">
         <f t="shared" si="5"/>
         <v>0.41400970061474307</v>
       </c>
@@ -4925,20 +5038,20 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
-    <row r="41" spans="1:11" ht="23" customHeight="1">
+    <row r="41" spans="1:11" ht="31" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="5">
+      <c r="B41" s="12">
         <v>0.35</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41" s="12">
         <f t="shared" si="3"/>
         <v>0.13493057850199364</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="12">
         <f t="shared" si="4"/>
         <v>0.28832357211277315</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="12">
         <f t="shared" si="5"/>
         <v>0.42466346654849568</v>
       </c>
@@ -4949,20 +5062,20 @@
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
     </row>
-    <row r="42" spans="1:11" ht="23" customHeight="1">
+    <row r="42" spans="1:11" ht="31" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="5">
+      <c r="B42" s="9">
         <v>0.36</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="9">
         <f t="shared" si="3"/>
         <v>0.1397155384517296</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="9">
         <f t="shared" si="4"/>
         <v>0.29724284076478735</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="9">
         <f t="shared" si="5"/>
         <v>0.43524598632805317</v>
       </c>
@@ -4973,20 +5086,20 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
     </row>
-    <row r="43" spans="1:11" ht="23" customHeight="1">
+    <row r="43" spans="1:11" ht="31" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="5">
+      <c r="B43" s="12">
         <v>0.37</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="12">
         <f t="shared" si="3"/>
         <v>0.14457008693631948</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="12">
         <f t="shared" si="4"/>
         <v>0.3062062836492514</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="12">
         <f t="shared" si="5"/>
         <v>0.44575830386722187</v>
       </c>
@@ -4997,20 +5110,20 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
     </row>
-    <row r="44" spans="1:11" ht="23" customHeight="1">
+    <row r="44" spans="1:11" ht="31" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="5">
+      <c r="B44" s="9">
         <v>0.38</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="9">
         <f t="shared" si="3"/>
         <v>0.14949627794118397</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="9">
         <f t="shared" si="4"/>
         <v>0.31521451295180247</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="9">
         <f t="shared" si="5"/>
         <v>0.45620144030309984</v>
       </c>
@@ -5021,20 +5134,20 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
     </row>
-    <row r="45" spans="1:11" ht="23" customHeight="1">
+    <row r="45" spans="1:11" ht="31" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="5">
+      <c r="B45" s="12">
         <v>0.39</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45" s="12">
         <f t="shared" si="3"/>
         <v>0.15449625775425421</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="12">
         <f t="shared" si="4"/>
         <v>0.32426815367282602</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="12">
         <f t="shared" si="5"/>
         <v>0.46657639465390466</v>
       </c>
@@ -5045,20 +5158,20 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" spans="1:11" ht="23" customHeight="1">
+    <row r="46" spans="1:11" ht="31" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="B46" s="5">
+      <c r="B46" s="9">
         <v>0.4</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C46" s="9">
         <f t="shared" si="3"/>
         <v>0.1595722705807357</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="9">
         <f t="shared" si="4"/>
         <v>0.33336784398763486</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46" s="9">
         <f t="shared" si="5"/>
         <v>0.47688414445321758</v>
       </c>
@@ -5069,20 +5182,20 @@
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
     </row>
-    <row r="47" spans="1:11" ht="23" customHeight="1">
+    <row r="47" spans="1:11" ht="31" customHeight="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="5">
+      <c r="B47" s="12">
         <v>0.41</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47" s="12">
         <f t="shared" si="3"/>
         <v>0.16472666459140581</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="12">
         <f t="shared" si="4"/>
         <v>0.3425142356193922</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="12">
         <f t="shared" si="5"/>
         <v>0.48712564636166195</v>
       </c>
@@ -5093,20 +5206,20 @@
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
     </row>
-    <row r="48" spans="1:11" ht="23" customHeight="1">
+    <row r="48" spans="1:11" ht="31" customHeight="1">
       <c r="A48" s="1"/>
-      <c r="B48" s="5">
+      <c r="B48" s="9">
         <v>0.42</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="9">
         <f t="shared" si="3"/>
         <v>0.16996189844524612</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="9">
         <f t="shared" si="4"/>
         <v>0.35170799422532273</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="9">
         <f t="shared" si="5"/>
         <v>0.4973018367569616</v>
       </c>
@@ -5117,20 +5230,20 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
     </row>
-    <row r="49" spans="1:11" ht="23" customHeight="1">
+    <row r="49" spans="1:11" ht="31" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="5">
+      <c r="B49" s="12">
         <v>0.43</v>
       </c>
-      <c r="C49" s="5">
+      <c r="C49" s="12">
         <f t="shared" si="3"/>
         <v>0.17528054833176071</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="12">
         <f t="shared" si="4"/>
         <v>0.36094979979678654</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="12">
         <f t="shared" si="5"/>
         <v>0.50741363230329817</v>
       </c>
@@ -5141,20 +5254,20 @@
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
     </row>
-    <row r="50" spans="1:11" ht="23" customHeight="1">
+    <row r="50" spans="1:11" ht="31" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="5">
+      <c r="B50" s="9">
         <v>0.44</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50" s="9">
         <f t="shared" si="3"/>
         <v>0.18068531558347348</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="9">
         <f t="shared" si="4"/>
         <v>0.37024034707381337</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="9">
         <f t="shared" si="5"/>
         <v>0.51746193050082889</v>
       </c>
@@ -5165,20 +5278,20 @@
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
     </row>
-    <row r="51" spans="1:11" ht="23" customHeight="1">
+    <row r="51" spans="1:11" ht="31" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="B51" s="5">
+      <c r="B51" s="12">
         <v>0.45</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51" s="12">
         <f t="shared" si="3"/>
         <v>0.18617903491491378</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="12">
         <f t="shared" si="4"/>
         <v>0.37958034597473334</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="12">
         <f t="shared" si="5"/>
         <v>0.5274476102161888</v>
       </c>
@@ -5189,20 +5302,20 @@
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
     </row>
-    <row r="52" spans="1:11" ht="23" customHeight="1">
+    <row r="52" spans="1:11" ht="31" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="5">
+      <c r="B52" s="9">
         <v>0.46</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52" s="9">
         <f t="shared" si="3"/>
         <v>0.19176468335099819</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D52" s="9">
         <f t="shared" si="4"/>
         <v>0.38897052204156446</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="9">
         <f t="shared" si="5"/>
         <v>0.5373715321947633</v>
       </c>
@@ -5213,20 +5326,20 @@
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
     </row>
-    <row r="53" spans="1:11" ht="23" customHeight="1">
+    <row r="53" spans="1:11" ht="31" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="5">
+      <c r="B53" s="12">
         <v>0.47</v>
       </c>
-      <c r="C53" s="5">
+      <c r="C53" s="12">
         <f t="shared" si="3"/>
         <v>0.19744538991520971</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D53" s="12">
         <f t="shared" si="4"/>
         <v>0.39841161690185894</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="12">
         <f t="shared" si="5"/>
         <v>0.54723453955547574</v>
       </c>
@@ -5237,20 +5350,20 @@
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
     </row>
-    <row r="54" spans="1:11" ht="23" customHeight="1">
+    <row r="54" spans="1:11" ht="31" customHeight="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="5">
+      <c r="B54" s="9">
         <v>0.48</v>
       </c>
-      <c r="C54" s="5">
+      <c r="C54" s="9">
         <f t="shared" si="3"/>
         <v>0.20322444615651072</v>
       </c>
-      <c r="D54" s="5">
+      <c r="D54" s="9">
         <f t="shared" si="4"/>
         <v>0.40790438874774249</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="9">
         <f t="shared" si="5"/>
         <v>0.55703745826880269</v>
       </c>
@@ -5261,20 +5374,20 @@
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
     </row>
-    <row r="55" spans="1:11" ht="23" customHeight="1">
+    <row r="55" spans="1:11" ht="31" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="B55" s="5">
+      <c r="B55" s="12">
         <v>0.49</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55" s="12">
         <f t="shared" si="3"/>
         <v>0.20910531760365855</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55" s="12">
         <f t="shared" si="4"/>
         <v>0.4174496128329182</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55" s="12">
         <f t="shared" si="5"/>
         <v>0.56678109761869333</v>
       </c>
@@ -5285,20 +5398,20 @@
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
     </row>
-    <row r="56" spans="1:11" ht="23" customHeight="1">
+    <row r="56" spans="1:11" ht="31" customHeight="1">
       <c r="A56" s="1"/>
-      <c r="B56" s="5">
+      <c r="B56" s="9">
         <v>0.5</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56" s="9">
         <f t="shared" si="3"/>
         <v>0.21509165624673118</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="9">
         <f t="shared" si="4"/>
         <v>0.42704808198845362</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="9">
         <f t="shared" si="5"/>
         <v>0.57646625064904067</v>
       </c>
@@ -5309,20 +5422,20 @@
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
     </row>
-    <row r="57" spans="1:11" ht="23" customHeight="1">
+    <row r="57" spans="1:11" ht="31" customHeight="1">
       <c r="A57" s="1"/>
-      <c r="B57" s="5">
+      <c r="B57" s="12">
         <v>0.51</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C57" s="12">
         <f t="shared" si="3"/>
         <v>0.22118731415842602</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D57" s="12">
         <f t="shared" si="4"/>
         <v>0.43670060715820669</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="12">
         <f t="shared" si="5"/>
         <v>0.5860936945953189</v>
       </c>
@@ -5333,20 +5446,20 @@
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
     </row>
-    <row r="58" spans="1:11" ht="23" customHeight="1">
+    <row r="58" spans="1:11" ht="31" customHeight="1">
       <c r="A58" s="1"/>
-      <c r="B58" s="5">
+      <c r="B58" s="9">
         <v>0.52</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="9">
         <f t="shared" si="3"/>
         <v>0.22739635838235542</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="9">
         <f t="shared" si="4"/>
         <v>0.44640801795479484</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="9">
         <f t="shared" si="5"/>
         <v>0.59566419130197479</v>
       </c>
@@ -5357,20 +5470,20 @@
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
     </row>
-    <row r="59" spans="1:11" ht="23" customHeight="1">
+    <row r="59" spans="1:11" ht="31" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="5">
+      <c r="B59" s="12">
         <v>0.53</v>
       </c>
-      <c r="C59" s="5">
+      <c r="C59" s="12">
         <f t="shared" si="3"/>
         <v>0.23372308723244489</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="12">
         <f t="shared" si="4"/>
         <v>0.45617116323706058</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="12">
         <f t="shared" si="5"/>
         <v>0.60517848762613446</v>
       </c>
@@ -5381,20 +5494,20 @@
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
     </row>
-    <row r="60" spans="1:11" ht="23" customHeight="1">
+    <row r="60" spans="1:11" ht="31" customHeight="1">
       <c r="A60" s="1"/>
-      <c r="B60" s="5">
+      <c r="B60" s="9">
         <v>0.54</v>
       </c>
-      <c r="C60" s="5">
+      <c r="C60" s="9">
         <f t="shared" si="3"/>
         <v>0.24017204816703402</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D60" s="9">
         <f t="shared" si="4"/>
         <v>0.46599091171004031</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="9">
         <f t="shared" si="5"/>
         <v>0.61463731582815906</v>
       </c>
@@ -5405,20 +5518,20 @@
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
     </row>
-    <row r="61" spans="1:11" ht="23" customHeight="1">
+    <row r="61" spans="1:11" ht="31" customHeight="1">
       <c r="A61" s="1"/>
-      <c r="B61" s="5">
+      <c r="B61" s="12">
         <v>0.55000000000000004</v>
       </c>
-      <c r="C61" s="5">
+      <c r="C61" s="12">
         <f t="shared" si="3"/>
         <v>0.24674805742384046</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D61" s="12">
         <f t="shared" si="4"/>
         <v>0.47586815254849502</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="12">
         <f t="shared" si="5"/>
         <v>0.62404139394956171</v>
       </c>
@@ -5429,20 +5542,20 @@
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
     </row>
-    <row r="62" spans="1:11" ht="23" customHeight="1">
+    <row r="62" spans="1:11" ht="31" customHeight="1">
       <c r="A62" s="1"/>
-      <c r="B62" s="5">
+      <c r="B62" s="9">
         <v>0.56000000000000005</v>
       </c>
-      <c r="C62" s="5">
+      <c r="C62" s="9">
         <f t="shared" si="3"/>
         <v>0.25345622162814618</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D62" s="9">
         <f t="shared" si="4"/>
         <v>0.48580379604512214</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="9">
         <f t="shared" si="5"/>
         <v>0.63339142617877142</v>
       </c>
@@ -5453,20 +5566,20 @@
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
     </row>
-    <row r="63" spans="1:11" ht="23" customHeight="1">
+    <row r="63" spans="1:11" ht="31" customHeight="1">
       <c r="A63" s="1"/>
-      <c r="B63" s="5">
+      <c r="B63" s="12">
         <v>0.56999999999999995</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C63" s="12">
         <f t="shared" si="3"/>
         <v>0.26030196161705293</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D63" s="12">
         <f t="shared" si="4"/>
         <v>0.49579877428463126</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="12">
         <f t="shared" si="5"/>
         <v>0.64268810320521186</v>
       </c>
@@ -5477,20 +5590,20 @@
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
     </row>
-    <row r="64" spans="1:11" ht="23" customHeight="1">
+    <row r="64" spans="1:11" ht="31" customHeight="1">
       <c r="A64" s="1"/>
-      <c r="B64" s="5">
+      <c r="B64" s="9">
         <v>0.57999999999999996</v>
       </c>
-      <c r="C64" s="5">
+      <c r="C64" s="9">
         <f t="shared" si="3"/>
         <v>0.26729103875825755</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D64" s="9">
         <f t="shared" si="4"/>
         <v>0.50585404184493254</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64" s="9">
         <f t="shared" si="5"/>
         <v>0.65193210256214051</v>
       </c>
@@ -5501,20 +5614,20 @@
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
     </row>
-    <row r="65" spans="1:11" ht="23" customHeight="1">
+    <row r="65" spans="1:11" ht="31" customHeight="1">
       <c r="A65" s="1"/>
-      <c r="B65" s="5">
+      <c r="B65" s="12">
         <v>0.59</v>
       </c>
-      <c r="C65" s="5">
+      <c r="C65" s="12">
         <f t="shared" si="3"/>
         <v>0.27442958408348866</v>
       </c>
-      <c r="D65" s="5">
+      <c r="D65" s="12">
         <f t="shared" si="4"/>
         <v>0.51597057652675415</v>
       </c>
-      <c r="E65" s="5">
+      <c r="E65" s="12">
         <f t="shared" si="5"/>
         <v>0.66112408895866737</v>
       </c>
@@ -5525,20 +5638,20 @@
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
     </row>
-    <row r="66" spans="1:11" ht="23" customHeight="1">
+    <row r="66" spans="1:11" ht="31" customHeight="1">
       <c r="A66" s="1"/>
-      <c r="B66" s="5">
+      <c r="B66" s="9">
         <v>0.6</v>
       </c>
-      <c r="C66" s="5">
+      <c r="C66" s="9">
         <f t="shared" si="3"/>
         <v>0.28172413060573137</v>
       </c>
-      <c r="D66" s="5">
+      <c r="D66" s="9">
         <f t="shared" si="4"/>
         <v>0.5261493801130871</v>
       </c>
-      <c r="E66" s="5">
+      <c r="E66" s="9">
         <f t="shared" si="5"/>
         <v>0.67026471460137405</v>
       </c>
@@ -5549,20 +5662,20 @@
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
     </row>
-    <row r="67" spans="1:11" ht="23" customHeight="1">
+    <row r="67" spans="1:11" ht="31" customHeight="1">
       <c r="A67" s="1"/>
-      <c r="B67" s="5">
+      <c r="B67" s="12">
         <v>0.61</v>
       </c>
-      <c r="C67" s="5">
+      <c r="C67" s="12">
         <f t="shared" si="3"/>
         <v>0.28918164924710904</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D67" s="12">
         <f t="shared" si="4"/>
         <v>0.53639147915992924</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E67" s="12">
         <f t="shared" si="5"/>
         <v>0.67935461950590303</v>
       </c>
@@ -5573,20 +5686,20 @@
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
     </row>
-    <row r="68" spans="1:11" ht="23" customHeight="1">
+    <row r="68" spans="1:11" ht="31" customHeight="1">
       <c r="A68" s="1"/>
-      <c r="B68" s="5">
+      <c r="B68" s="9">
         <v>0.62</v>
       </c>
-      <c r="C68" s="5">
+      <c r="C68" s="9">
         <f t="shared" si="3"/>
         <v>0.29680958887258779</v>
       </c>
-      <c r="D68" s="5">
+      <c r="D68" s="9">
         <f t="shared" si="4"/>
         <v>0.54669792581989296</v>
       </c>
-      <c r="E68" s="5">
+      <c r="E68" s="9">
         <f t="shared" si="5"/>
         <v>0.68839443179891013</v>
       </c>
@@ -5597,20 +5710,20 @@
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
     </row>
-    <row r="69" spans="1:11" ht="23" customHeight="1">
+    <row r="69" spans="1:11" ht="31" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="5">
+      <c r="B69" s="12">
         <v>0.63</v>
       </c>
-      <c r="C69" s="5">
+      <c r="C69" s="12">
         <f t="shared" si="3"/>
         <v>0.30461592100575746</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="12">
         <f t="shared" si="4"/>
         <v>0.55706979870032503</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E69" s="12">
         <f t="shared" si="5"/>
         <v>0.69738476801071747</v>
       </c>
@@ -5621,20 +5734,20 @@
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
     </row>
-    <row r="70" spans="1:11" ht="23" customHeight="1">
+    <row r="70" spans="1:11" ht="31" customHeight="1">
       <c r="A70" s="1"/>
-      <c r="B70" s="5">
+      <c r="B70" s="9">
         <v>0.64</v>
       </c>
-      <c r="C70" s="5">
+      <c r="C70" s="9">
         <f t="shared" ref="C70:C106" si="6">IF($I$9=0,$B70,(1-$H$9)*LN(1+$I$9*$B70)/LN(1+$I$9)+$H$9*$B70)</f>
         <v>0.31260918989955822</v>
       </c>
-      <c r="D70" s="5">
+      <c r="D70" s="9">
         <f t="shared" ref="D70:D106" si="7">IF($I$10=0,$B70,(1-$H$10)*LN(1+$I$10*$B70)/LN(1+$I$10)+$H$10*$B70)</f>
         <v>0.56750820375769195</v>
       </c>
-      <c r="E70" s="5">
+      <c r="E70" s="9">
         <f t="shared" ref="E70:E106" si="8">IF($I$11=0,$B70,(1-$H$11)*LN(1+$I$11*$B70)/LN(1+$I$11)+$H$11*$B70)</f>
         <v>0.70632623335902323</v>
       </c>
@@ -5645,20 +5758,20 @@
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
     </row>
-    <row r="71" spans="1:11" ht="23" customHeight="1">
+    <row r="71" spans="1:11" ht="31" customHeight="1">
       <c r="A71" s="1"/>
-      <c r="B71" s="5">
+      <c r="B71" s="12">
         <v>0.65</v>
       </c>
-      <c r="C71" s="5">
+      <c r="C71" s="12">
         <f t="shared" si="6"/>
         <v>0.32079856875041485</v>
       </c>
-      <c r="D71" s="5">
+      <c r="D71" s="12">
         <f t="shared" si="7"/>
         <v>0.5780142752300842</v>
       </c>
-      <c r="E71" s="5">
+      <c r="E71" s="12">
         <f t="shared" si="8"/>
         <v>0.71521942202398203</v>
       </c>
@@ -5669,20 +5782,20 @@
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
     </row>
-    <row r="72" spans="1:11" ht="23" customHeight="1">
+    <row r="72" spans="1:11" ht="31" customHeight="1">
       <c r="A72" s="1"/>
-      <c r="B72" s="5">
+      <c r="B72" s="9">
         <v>0.66</v>
       </c>
-      <c r="C72" s="5">
+      <c r="C72" s="9">
         <f t="shared" si="6"/>
         <v>0.3291939229831008</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="9">
         <f t="shared" si="7"/>
         <v>0.58858917660980759</v>
       </c>
-      <c r="E72" s="5">
+      <c r="E72" s="9">
         <f t="shared" si="8"/>
         <v>0.72406491741498025</v>
       </c>
@@ -5693,20 +5806,20 @@
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
     </row>
-    <row r="73" spans="1:11" ht="23" customHeight="1">
+    <row r="73" spans="1:11" ht="31" customHeight="1">
       <c r="A73" s="1"/>
-      <c r="B73" s="5">
+      <c r="B73" s="12">
         <v>0.67</v>
       </c>
-      <c r="C73" s="5">
+      <c r="C73" s="12">
         <f t="shared" si="6"/>
         <v>0.33780588170117226</v>
       </c>
-      <c r="D73" s="5">
+      <c r="D73" s="12">
         <f t="shared" si="7"/>
         <v>0.59923410165814361</v>
       </c>
-      <c r="E73" s="5">
+      <c r="E73" s="12">
         <f t="shared" si="8"/>
         <v>0.73286329242939496</v>
       </c>
@@ -5717,20 +5830,20 @@
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
     </row>
-    <row r="74" spans="1:11" ht="23" customHeight="1">
+    <row r="74" spans="1:11" ht="31" customHeight="1">
       <c r="A74" s="1"/>
-      <c r="B74" s="5">
+      <c r="B74" s="9">
         <v>0.68</v>
       </c>
-      <c r="C74" s="5">
+      <c r="C74" s="9">
         <f t="shared" si="6"/>
         <v>0.34664591860085897</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="9">
         <f t="shared" si="7"/>
         <v>0.60995027546449632</v>
       </c>
-      <c r="E74" s="5">
+      <c r="E74" s="9">
         <f t="shared" si="8"/>
         <v>0.74161510970363209</v>
       </c>
@@ -5741,20 +5854,20 @@
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
     </row>
-    <row r="75" spans="1:11" ht="23" customHeight="1">
+    <row r="75" spans="1:11" ht="31" customHeight="1">
       <c r="A75" s="1"/>
-      <c r="B75" s="5">
+      <c r="B75" s="12">
         <v>0.69</v>
       </c>
-      <c r="C75" s="5">
+      <c r="C75" s="12">
         <f t="shared" si="6"/>
         <v>0.35572644389352442</v>
       </c>
-      <c r="D75" s="5">
+      <c r="D75" s="12">
         <f t="shared" si="7"/>
         <v>0.62073895555227376</v>
       </c>
-      <c r="E75" s="5">
+      <c r="E75" s="12">
         <f t="shared" si="8"/>
         <v>0.75032092185671373</v>
       </c>
@@ -5765,20 +5878,20 @@
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
     </row>
-    <row r="76" spans="1:11" ht="23" customHeight="1">
+    <row r="76" spans="1:11" ht="31" customHeight="1">
       <c r="A76" s="1"/>
-      <c r="B76" s="5">
+      <c r="B76" s="9">
         <v>0.7</v>
       </c>
-      <c r="C76" s="5">
+      <c r="C76" s="9">
         <f t="shared" si="6"/>
         <v>0.36506090908439143</v>
       </c>
-      <c r="D76" s="5">
+      <c r="D76" s="9">
         <f t="shared" si="7"/>
         <v>0.63160143303400229</v>
       </c>
-      <c r="E76" s="5">
+      <c r="E76" s="9">
         <f t="shared" si="8"/>
         <v>0.75898127172667929</v>
       </c>
@@ -5789,20 +5902,20 @@
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
     </row>
-    <row r="77" spans="1:11" ht="23" customHeight="1">
+    <row r="77" spans="1:11" ht="31" customHeight="1">
       <c r="A77" s="1"/>
-      <c r="B77" s="5">
+      <c r="B77" s="12">
         <v>0.71</v>
       </c>
-      <c r="C77" s="5">
+      <c r="C77" s="12">
         <f t="shared" si="6"/>
         <v>0.37466392682746691</v>
       </c>
-      <c r="D77" s="5">
+      <c r="D77" s="12">
         <f t="shared" si="7"/>
         <v>0.64253903381832389</v>
       </c>
-      <c r="E77" s="5">
+      <c r="E77" s="12">
         <f t="shared" si="8"/>
         <v>0.76759669260005581</v>
       </c>
@@ -5813,20 +5926,20 @@
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
     </row>
-    <row r="78" spans="1:11" ht="23" customHeight="1">
+    <row r="78" spans="1:11" ht="31" customHeight="1">
       <c r="A78" s="1"/>
-      <c r="B78" s="5">
+      <c r="B78" s="9">
         <v>0.72</v>
       </c>
-      <c r="C78" s="5">
+      <c r="C78" s="9">
         <f t="shared" si="6"/>
         <v>0.3845514085370963</v>
       </c>
-      <c r="D78" s="5">
+      <c r="D78" s="9">
         <f t="shared" si="7"/>
         <v>0.65355311987170273</v>
       </c>
-      <c r="E78" s="5">
+      <c r="E78" s="9">
         <f t="shared" si="8"/>
         <v>0.77616770843463589</v>
       </c>
@@ -5837,20 +5950,20 @@
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
     </row>
-    <row r="79" spans="1:11" ht="23" customHeight="1">
+    <row r="79" spans="1:11" ht="31" customHeight="1">
       <c r="A79" s="1"/>
-      <c r="B79" s="5">
+      <c r="B79" s="12">
         <v>0.73</v>
       </c>
-      <c r="C79" s="5">
+      <c r="C79" s="12">
         <f t="shared" si="6"/>
         <v>0.39474072300959206</v>
       </c>
-      <c r="D79" s="5">
+      <c r="D79" s="12">
         <f t="shared" si="7"/>
         <v>0.66464509053784282</v>
       </c>
-      <c r="E79" s="5">
+      <c r="E79" s="12">
         <f t="shared" si="8"/>
         <v>0.78469483407579999</v>
       </c>
@@ -5861,20 +5974,20 @@
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
     </row>
-    <row r="80" spans="1:11" ht="23" customHeight="1">
+    <row r="80" spans="1:11" ht="31" customHeight="1">
       <c r="A80" s="1"/>
-      <c r="B80" s="5">
+      <c r="B80" s="9">
         <v>0.74</v>
       </c>
-      <c r="C80" s="5">
+      <c r="C80" s="9">
         <f t="shared" si="6"/>
         <v>0.4052508800257974</v>
       </c>
-      <c r="D80" s="5">
+      <c r="D80" s="9">
         <f t="shared" si="7"/>
         <v>0.67581638391801158</v>
       </c>
-      <c r="E80" s="5">
+      <c r="E80" s="9">
         <f t="shared" si="8"/>
         <v>0.7931785754666032</v>
       </c>
@@ -5885,20 +5998,20 @@
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
     </row>
-    <row r="81" spans="1:11" ht="23" customHeight="1">
+    <row r="81" spans="1:11" ht="31" customHeight="1">
       <c r="A81" s="1"/>
-      <c r="B81" s="5">
+      <c r="B81" s="12">
         <v>0.75</v>
       </c>
-      <c r="C81" s="5">
+      <c r="C81" s="12">
         <f t="shared" si="6"/>
         <v>0.41610274380958168</v>
       </c>
-      <c r="D81" s="5">
+      <c r="D81" s="12">
         <f t="shared" si="7"/>
         <v>0.68706847831567486</v>
       </c>
-      <c r="E81" s="5">
+      <c r="E81" s="12">
         <f t="shared" si="8"/>
         <v>0.80161942985184376</v>
       </c>
@@ -5909,20 +6022,20 @@
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
     </row>
-    <row r="82" spans="1:11" ht="23" customHeight="1">
+    <row r="82" spans="1:11" ht="31" customHeight="1">
       <c r="A82" s="1"/>
-      <c r="B82" s="5">
+      <c r="B82" s="9">
         <v>0.76</v>
       </c>
-      <c r="C82" s="5">
+      <c r="C82" s="9">
         <f t="shared" si="6"/>
         <v>0.42731928236457911</v>
       </c>
-      <c r="D82" s="5">
+      <c r="D82" s="9">
         <f t="shared" si="7"/>
         <v>0.69840289374907738</v>
       </c>
-      <c r="E82" s="5">
+      <c r="E82" s="9">
         <f t="shared" si="8"/>
         <v>0.81001788597631541</v>
       </c>
@@ -5933,20 +6046,20 @@
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
     </row>
-    <row r="83" spans="1:11" ht="23" customHeight="1">
+    <row r="83" spans="1:11" ht="31" customHeight="1">
       <c r="A83" s="1"/>
-      <c r="B83" s="5">
+      <c r="B83" s="12">
         <v>0.77</v>
       </c>
-      <c r="C83" s="5">
+      <c r="C83" s="12">
         <f t="shared" si="6"/>
         <v>0.43892586017817919</v>
       </c>
-      <c r="D83" s="5">
+      <c r="D83" s="12">
         <f t="shared" si="7"/>
         <v>0.70982119353563444</v>
       </c>
-      <c r="E83" s="5">
+      <c r="E83" s="12">
         <f t="shared" si="8"/>
         <v>0.81837442427744556</v>
       </c>
@@ -5957,20 +6070,20 @@
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
     </row>
-    <row r="84" spans="1:11" ht="23" customHeight="1">
+    <row r="84" spans="1:11" ht="31" customHeight="1">
       <c r="A84" s="1"/>
-      <c r="B84" s="5">
+      <c r="B84" s="9">
         <v>0.78</v>
       </c>
-      <c r="C84" s="5">
+      <c r="C84" s="9">
         <f t="shared" si="6"/>
         <v>0.45095058367145918</v>
       </c>
-      <c r="D84" s="5">
+      <c r="D84" s="9">
         <f t="shared" si="7"/>
         <v>0.72132498595226613</v>
       </c>
-      <c r="E84" s="5">
+      <c r="E84" s="9">
         <f t="shared" si="8"/>
         <v>0.82668951707250571</v>
       </c>
@@ -5981,20 +6094,20 @@
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
     </row>
-    <row r="85" spans="1:11" ht="23" customHeight="1">
+    <row r="85" spans="1:11" ht="31" customHeight="1">
       <c r="A85" s="1"/>
-      <c r="B85" s="5">
+      <c r="B85" s="12">
         <v>0.79</v>
       </c>
-      <c r="C85" s="5">
+      <c r="C85" s="12">
         <f t="shared" si="6"/>
         <v>0.46342471122880308</v>
       </c>
-      <c r="D85" s="5">
+      <c r="D85" s="12">
         <f t="shared" si="7"/>
         <v>0.73291592597608868</v>
       </c>
-      <c r="E85" s="5">
+      <c r="E85" s="12">
         <f t="shared" si="8"/>
         <v>0.83496362874057861</v>
       </c>
@@ -6005,20 +6118,20 @@
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
     </row>
-    <row r="86" spans="1:11" ht="23" customHeight="1">
+    <row r="86" spans="1:11" ht="31" customHeight="1">
       <c r="A86" s="1"/>
-      <c r="B86" s="5">
+      <c r="B86" s="9">
         <v>0.8</v>
       </c>
-      <c r="C86" s="5">
+      <c r="C86" s="9">
         <f t="shared" si="6"/>
         <v>0.4763831428591197</v>
       </c>
-      <c r="D86" s="5">
+      <c r="D86" s="9">
         <f t="shared" si="7"/>
         <v>0.74459571711016936</v>
       </c>
-      <c r="E86" s="5">
+      <c r="E86" s="9">
         <f t="shared" si="8"/>
         <v>0.84319721589945518</v>
       </c>
@@ -6029,20 +6142,20 @@
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
     </row>
-    <row r="87" spans="1:11" ht="23" customHeight="1">
+    <row r="87" spans="1:11" ht="31" customHeight="1">
       <c r="A87" s="1"/>
-      <c r="B87" s="5">
+      <c r="B87" s="12">
         <v>0.81</v>
       </c>
-      <c r="C87" s="5">
+      <c r="C87" s="12">
         <f t="shared" si="6"/>
         <v>0.48986500879948736</v>
       </c>
-      <c r="D87" s="5">
+      <c r="D87" s="12">
         <f t="shared" si="7"/>
         <v>0.75636611329938919</v>
       </c>
-      <c r="E87" s="5">
+      <c r="E87" s="12">
         <f t="shared" si="8"/>
         <v>0.85139072757763268</v>
       </c>
@@ -6053,20 +6166,20 @@
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
     </row>
-    <row r="88" spans="1:11" ht="23" customHeight="1">
+    <row r="88" spans="1:11" ht="31" customHeight="1">
       <c r="A88" s="1"/>
-      <c r="B88" s="5">
+      <c r="B88" s="9">
         <v>0.82</v>
       </c>
-      <c r="C88" s="5">
+      <c r="C88" s="9">
         <f t="shared" si="6"/>
         <v>0.50391438206641781</v>
       </c>
-      <c r="D88" s="5">
+      <c r="D88" s="9">
         <f t="shared" si="7"/>
         <v>0.76822892094179585</v>
       </c>
-      <c r="E88" s="5">
+      <c r="E88" s="9">
         <f t="shared" si="8"/>
         <v>0.85954460538157429</v>
       </c>
@@ -6077,20 +6190,20 @@
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
     </row>
-    <row r="89" spans="1:11" ht="23" customHeight="1">
+    <row r="89" spans="1:11" ht="31" customHeight="1">
       <c r="A89" s="1"/>
-      <c r="B89" s="5">
+      <c r="B89" s="12">
         <v>0.83</v>
       </c>
-      <c r="C89" s="5">
+      <c r="C89" s="12">
         <f t="shared" si="6"/>
         <v>0.51858114765802221</v>
       </c>
-      <c r="D89" s="5">
+      <c r="D89" s="12">
         <f t="shared" si="7"/>
         <v>0.7801860010012226</v>
       </c>
-      <c r="E89" s="5">
+      <c r="E89" s="12">
         <f t="shared" si="8"/>
         <v>0.86765928365838596</v>
       </c>
@@ -6101,20 +6214,20 @@
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
     </row>
-    <row r="90" spans="1:11" ht="23" customHeight="1">
+    <row r="90" spans="1:11" ht="31" customHeight="1">
       <c r="A90" s="1"/>
-      <c r="B90" s="5">
+      <c r="B90" s="9">
         <v>0.84</v>
       </c>
-      <c r="C90" s="5">
+      <c r="C90" s="9">
         <f t="shared" si="6"/>
         <v>0.5339220716420624</v>
       </c>
-      <c r="D90" s="5">
+      <c r="D90" s="9">
         <f t="shared" si="7"/>
         <v>0.7922392712273485</v>
       </c>
-      <c r="E90" s="5">
+      <c r="E90" s="9">
         <f t="shared" si="8"/>
         <v>0.87573518965405928</v>
       </c>
@@ -6125,20 +6238,20 @@
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
     </row>
-    <row r="91" spans="1:11" ht="23" customHeight="1">
+    <row r="91" spans="1:11" ht="31" customHeight="1">
       <c r="A91" s="1"/>
-      <c r="B91" s="5">
+      <c r="B91" s="12">
         <v>0.85</v>
       </c>
-      <c r="C91" s="5">
+      <c r="C91" s="12">
         <f t="shared" si="6"/>
         <v>0.5500021279603855</v>
       </c>
-      <c r="D91" s="5">
+      <c r="D91" s="12">
         <f t="shared" si="7"/>
         <v>0.80439070848982852</v>
       </c>
-      <c r="E91" s="5">
+      <c r="E91" s="12">
         <f t="shared" si="8"/>
         <v>0.88377274366742875</v>
       </c>
@@ -6149,20 +6262,20 @@
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="1:11" ht="23" customHeight="1">
+    <row r="92" spans="1:11" ht="31" customHeight="1">
       <c r="A92" s="1"/>
-      <c r="B92" s="5">
+      <c r="B92" s="9">
         <v>0.86</v>
       </c>
-      <c r="C92" s="5">
+      <c r="C92" s="9">
         <f t="shared" si="6"/>
         <v>0.56689616129346987</v>
       </c>
-      <c r="D92" s="5">
+      <c r="D92" s="9">
         <f t="shared" si="7"/>
         <v>0.81664235123359474</v>
       </c>
-      <c r="E92" s="5">
+      <c r="E92" s="9">
         <f t="shared" si="8"/>
         <v>0.89177235919997588</v>
       </c>
@@ -6173,20 +6286,20 @@
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
     </row>
-    <row r="93" spans="1:11" ht="23" customHeight="1">
+    <row r="93" spans="1:11" ht="31" customHeight="1">
       <c r="A93" s="1"/>
-      <c r="B93" s="5">
+      <c r="B93" s="12">
         <v>0.87</v>
       </c>
-      <c r="C93" s="5">
+      <c r="C93" s="12">
         <f t="shared" si="6"/>
         <v>0.58469099360378995</v>
       </c>
-      <c r="D93" s="5">
+      <c r="D93" s="12">
         <f t="shared" si="7"/>
         <v>0.82899630206296215</v>
       </c>
-      <c r="E93" s="5">
+      <c r="E93" s="12">
         <f t="shared" si="8"/>
         <v>0.89973444310162098</v>
       </c>
@@ -6197,20 +6310,20 @@
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
     </row>
-    <row r="94" spans="1:11" ht="23" customHeight="1">
+    <row r="94" spans="1:11" ht="31" customHeight="1">
       <c r="A94" s="1"/>
-      <c r="B94" s="5">
+      <c r="B94" s="9">
         <v>0.88</v>
       </c>
-      <c r="C94" s="5">
+      <c r="C94" s="9">
         <f t="shared" si="6"/>
         <v>0.60348812446218625</v>
       </c>
-      <c r="D94" s="5">
+      <c r="D94" s="9">
         <f t="shared" si="7"/>
         <v>0.84145473046272989</v>
       </c>
-      <c r="E94" s="5">
+      <c r="E94" s="9">
         <f t="shared" si="8"/>
         <v>0.90765939571262133</v>
       </c>
@@ -6221,20 +6334,20 @@
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
     </row>
-    <row r="95" spans="1:11" ht="23" customHeight="1">
+    <row r="95" spans="1:11" ht="31" customHeight="1">
       <c r="A95" s="1"/>
-      <c r="B95" s="5">
+      <c r="B95" s="12">
         <v>0.89</v>
       </c>
-      <c r="C95" s="5">
+      <c r="C95" s="12">
         <f t="shared" si="6"/>
         <v>0.6234072380669563</v>
       </c>
-      <c r="D95" s="5">
+      <c r="D95" s="12">
         <f t="shared" si="7"/>
         <v>0.85401987566508752</v>
       </c>
-      <c r="E95" s="5">
+      <c r="E95" s="12">
         <f t="shared" si="8"/>
         <v>0.91554761100171322</v>
       </c>
@@ -6245,20 +6358,20 @@
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
     </row>
-    <row r="96" spans="1:11" ht="23" customHeight="1">
+    <row r="96" spans="1:11" ht="31" customHeight="1">
       <c r="A96" s="1"/>
-      <c r="B96" s="5">
+      <c r="B96" s="9">
         <v>0.9</v>
       </c>
-      <c r="C96" s="5">
+      <c r="C96" s="9">
         <f t="shared" si="6"/>
         <v>0.64459082462355466</v>
       </c>
-      <c r="D96" s="5">
+      <c r="D96" s="9">
         <f t="shared" si="7"/>
         <v>0.86669404967180197</v>
       </c>
-      <c r="E96" s="5">
+      <c r="E96" s="9">
         <f t="shared" si="8"/>
         <v>0.92339947670060074</v>
       </c>
@@ -6269,20 +6382,20 @@
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
     </row>
-    <row r="97" spans="1:11" ht="23" customHeight="1">
+    <row r="97" spans="1:11" ht="31" customHeight="1">
       <c r="A97" s="1"/>
-      <c r="B97" s="5">
+      <c r="B97" s="12">
         <v>0.91</v>
       </c>
-      <c r="C97" s="5">
+      <c r="C97" s="12">
         <f t="shared" si="6"/>
         <v>0.66721037000116235</v>
       </c>
-      <c r="D97" s="5">
+      <c r="D97" s="12">
         <f t="shared" si="7"/>
         <v>0.87947964044189242</v>
       </c>
-      <c r="E97" s="5">
+      <c r="E97" s="12">
         <f t="shared" si="8"/>
         <v>0.93121537443492164</v>
       </c>
@@ -6293,20 +6406,20 @@
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
     </row>
-    <row r="98" spans="1:11" ht="23" customHeight="1">
+    <row r="98" spans="1:11" ht="31" customHeight="1">
       <c r="A98" s="1"/>
-      <c r="B98" s="5">
+      <c r="B98" s="9">
         <v>0.92</v>
       </c>
-      <c r="C98" s="5">
+      <c r="C98" s="9">
         <f t="shared" si="6"/>
         <v>0.69147479910585075</v>
       </c>
-      <c r="D98" s="5">
+      <c r="D98" s="9">
         <f t="shared" si="7"/>
         <v>0.89237911525578284</v>
       </c>
-      <c r="E98" s="5">
+      <c r="E98" s="9">
         <f t="shared" si="8"/>
         <v>0.93899567985178833</v>
       </c>
@@ -6317,20 +6430,20 @@
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
     </row>
-    <row r="99" spans="1:11" ht="23" customHeight="1">
+    <row r="99" spans="1:11" ht="31" customHeight="1">
       <c r="A99" s="1"/>
-      <c r="B99" s="5">
+      <c r="B99" s="12">
         <v>0.93</v>
       </c>
-      <c r="C99" s="5">
+      <c r="C99" s="12">
         <f t="shared" si="6"/>
         <v>0.71764223557463891</v>
       </c>
-      <c r="D99" s="5">
+      <c r="D99" s="12">
         <f t="shared" si="7"/>
         <v>0.90539502426779028</v>
       </c>
-      <c r="E99" s="5">
+      <c r="E99" s="12">
         <f t="shared" si="8"/>
         <v>0.9467407627440203</v>
       </c>
@@ -6341,20 +6454,20 @@
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
     </row>
-    <row r="100" spans="1:11" ht="23" customHeight="1">
+    <row r="100" spans="1:11" ht="31" customHeight="1">
       <c r="A100" s="1"/>
-      <c r="B100" s="5">
+      <c r="B100" s="9">
         <v>0.94</v>
       </c>
-      <c r="C100" s="5">
+      <c r="C100" s="9">
         <f t="shared" si="6"/>
         <v>0.74603677513171862</v>
       </c>
-      <c r="D100" s="5">
+      <c r="D100" s="9">
         <f t="shared" si="7"/>
         <v>0.91853000425974562</v>
       </c>
-      <c r="E100" s="5">
+      <c r="E100" s="9">
         <f t="shared" si="8"/>
         <v>0.95445098717116272</v>
       </c>
@@ -6365,20 +6478,20 @@
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
     </row>
-    <row r="101" spans="1:11" ht="23" customHeight="1">
+    <row r="101" spans="1:11" ht="31" customHeight="1">
       <c r="A101" s="1"/>
-      <c r="B101" s="5">
+      <c r="B101" s="12">
         <v>0.95</v>
       </c>
-      <c r="C101" s="5">
+      <c r="C101" s="12">
         <f t="shared" si="6"/>
         <v>0.77707307876902676</v>
       </c>
-      <c r="D101" s="5">
+      <c r="D101" s="12">
         <f t="shared" si="7"/>
         <v>0.93178678260956671</v>
       </c>
-      <c r="E101" s="5">
+      <c r="E101" s="12">
         <f t="shared" si="8"/>
         <v>0.96212671157739738</v>
       </c>
@@ -6389,20 +6502,20 @@
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
     </row>
-    <row r="102" spans="1:11" ht="23" customHeight="1">
+    <row r="102" spans="1:11" ht="31" customHeight="1">
       <c r="A102" s="1"/>
-      <c r="B102" s="5">
+      <c r="B102" s="9">
         <v>0.96</v>
       </c>
-      <c r="C102" s="5">
+      <c r="C102" s="9">
         <f t="shared" si="6"/>
         <v>0.8112936145727736</v>
       </c>
-      <c r="D102" s="5">
+      <c r="D102" s="9">
         <f t="shared" si="7"/>
         <v>0.94516818148972548</v>
       </c>
-      <c r="E102" s="5">
+      <c r="E102" s="9">
         <f t="shared" si="8"/>
         <v>0.96976828890643507</v>
       </c>
@@ -6413,20 +6526,20 @@
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
     </row>
-    <row r="103" spans="1:11" ht="23" customHeight="1">
+    <row r="103" spans="1:11" ht="31" customHeight="1">
       <c r="A103" s="1"/>
-      <c r="B103" s="5">
+      <c r="B103" s="12">
         <v>0.97</v>
       </c>
-      <c r="C103" s="5">
+      <c r="C103" s="12">
         <f t="shared" si="6"/>
         <v>0.84942725912383288</v>
       </c>
-      <c r="D103" s="5">
+      <c r="D103" s="12">
         <f t="shared" si="7"/>
         <v>0.95867712231178137</v>
       </c>
-      <c r="E103" s="5">
+      <c r="E103" s="12">
         <f t="shared" si="8"/>
         <v>0.97737606671348642</v>
       </c>
@@ -6437,20 +6550,20 @@
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
     </row>
-    <row r="104" spans="1:11" ht="23" customHeight="1">
+    <row r="104" spans="1:11" ht="31" customHeight="1">
       <c r="A104" s="1"/>
-      <c r="B104" s="5">
+      <c r="B104" s="9">
         <v>0.98</v>
       </c>
-      <c r="C104" s="5">
+      <c r="C104" s="9">
         <f t="shared" si="6"/>
         <v>0.8924858866687011</v>
       </c>
-      <c r="D104" s="5">
+      <c r="D104" s="9">
         <f t="shared" si="7"/>
         <v>0.97231663043448913</v>
       </c>
-      <c r="E104" s="5">
+      <c r="E104" s="9">
         <f t="shared" si="8"/>
         <v>0.98495038727439643</v>
       </c>
@@ -6461,20 +6574,20 @@
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
     </row>
-    <row r="105" spans="1:11" ht="23" customHeight="1">
+    <row r="105" spans="1:11" ht="31" customHeight="1">
       <c r="A105" s="1"/>
-      <c r="B105" s="5">
+      <c r="B105" s="12">
         <v>0.99</v>
       </c>
-      <c r="C105" s="5">
+      <c r="C105" s="12">
         <f t="shared" si="6"/>
         <v>0.94193295954412271</v>
       </c>
-      <c r="D105" s="5">
+      <c r="D105" s="12">
         <f t="shared" si="7"/>
         <v>0.98608984015446355</v>
       </c>
-      <c r="E105" s="5">
+      <c r="E105" s="12">
         <f t="shared" si="8"/>
         <v>0.99249158769203172</v>
       </c>
@@ -6485,20 +6598,20 @@
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
     </row>
-    <row r="106" spans="1:11" ht="23" customHeight="1">
+    <row r="106" spans="1:11" ht="31" customHeight="1">
       <c r="A106" s="1"/>
-      <c r="B106" s="5">
+      <c r="B106" s="9">
         <v>1</v>
       </c>
-      <c r="C106" s="5">
+      <c r="C106" s="9">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D106" s="5">
+      <c r="D106" s="9">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="E106" s="5">
+      <c r="E106" s="9">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -6514,7 +6627,7 @@
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="H4:K4"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/throttle_curve.xlsx
+++ b/docs/throttle_curve.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8300B69C-D164-481D-913D-ED74C7CA62F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABA224D-6D44-4BC5-AC19-4D847F13A550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Throttle Curves" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -114,10 +114,6 @@
       <color rgb="FF195DB1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Carlito"/>
     </font>
     <font>
       <sz val="9"/>
@@ -494,85 +490,83 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="19" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="18" fillId="17" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="22" fillId="20" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="21" fillId="20" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="24" fillId="22" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="23" fillId="22" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -590,7 +584,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -2991,32 +2985,32 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="12" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-    </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="18" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+    </row>
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="19"/>
@@ -3031,664 +3025,664 @@
       <c r="L2" s="19"/>
       <c r="M2" s="19"/>
       <c r="N2" s="19"/>
-      <c r="O2" s="1"/>
-    </row>
-    <row r="3" spans="1:15" ht="23" customHeight="1">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-    </row>
-    <row r="4" spans="1:15" ht="23" customHeight="1">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2" t="s">
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="1:15" ht="23" customHeight="1">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" ht="23" customHeight="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" ht="23" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" ht="23" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:15" ht="23" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" ht="23" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="1:15" ht="23" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" ht="23" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" ht="23" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" ht="23" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" ht="23" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" ht="23" customHeight="1">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="1:15" ht="23" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="1:15" ht="23" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="1:15" ht="23" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" ht="23" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-    </row>
-    <row r="21" spans="1:15" ht="23" customHeight="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="1:15" ht="23" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-    </row>
-    <row r="23" spans="1:15" ht="23" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-    </row>
-    <row r="24" spans="1:15" ht="23" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15" ht="23" customHeight="1">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="1:15" ht="23" customHeight="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="1:15" ht="23" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="1:15" ht="23" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="1:15" ht="23" customHeight="1">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="1:15" ht="23" customHeight="1">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="1:15" ht="23" customHeight="1">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="1:15" ht="23" customHeight="1">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-    </row>
-    <row r="33" spans="1:15" ht="23" customHeight="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="1:15" ht="23" customHeight="1">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="1:15" ht="23" customHeight="1">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="1:15" ht="23" customHeight="1">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="1:15" ht="23" customHeight="1">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="1:15" ht="23" customHeight="1">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="1:15" ht="23" customHeight="1">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="1:15" ht="23" customHeight="1">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+    </row>
+    <row r="18" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+    </row>
+    <row r="19" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+    </row>
+    <row r="20" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+    </row>
+    <row r="21" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+    </row>
+    <row r="22" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+    </row>
+    <row r="23" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+    </row>
+    <row r="24" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+    </row>
+    <row r="25" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+    </row>
+    <row r="26" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+    </row>
+    <row r="29" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+    </row>
+    <row r="30" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+    </row>
+    <row r="31" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+    </row>
+    <row r="32" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+    </row>
+    <row r="33" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+    </row>
+    <row r="34" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+    </row>
+    <row r="35" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+    </row>
+    <row r="36" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+    </row>
+    <row r="37" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+    </row>
+    <row r="38" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+    </row>
+    <row r="40" spans="1:15" ht="23.1" customHeight="1">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="C4:E4"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <extLst>
@@ -3712,7 +3706,7 @@
     <tabColor rgb="FFC49A32"/>
   </sheetPr>
   <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -3722,24 +3716,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="12" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" ht="35" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="18" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+    </row>
+    <row r="2" spans="1:14" ht="35.1" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="19"/>
@@ -3755,297 +3749,297 @@
       <c r="M2" s="19"/>
       <c r="N2" s="19"/>
     </row>
-    <row r="3" spans="1:14" ht="23" customHeight="1">
-      <c r="A3" s="1"/>
-    </row>
-    <row r="4" spans="1:14" ht="23" customHeight="1">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" ht="32" customHeight="1">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="23" t="s">
+    <row r="3" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A3" s="2"/>
+    </row>
+    <row r="4" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" ht="32.1" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23" t="s">
+      <c r="D5" s="22"/>
+      <c r="E5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23" t="s">
+      <c r="F5" s="22"/>
+      <c r="G5" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" ht="32" customHeight="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3" t="s">
+      <c r="H5" s="22"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" ht="32.1" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" ht="31" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="5" t="s">
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <v>0</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <v>-0.92</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>0.5</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <v>-0.45</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <v>0.35</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="7">
         <v>1.5</v>
       </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" ht="31" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="7" t="s">
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>0</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="7">
         <v>-0.95</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>0.25</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>-0.55000000000000004</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="7">
         <v>0.1</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="7">
         <v>1</v>
       </c>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" ht="31" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="5" t="s">
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <v>0</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <v>-0.92</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>0.4</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <v>-0.45</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="7">
         <v>0.1</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="7">
         <v>1.5</v>
       </c>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" ht="31" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="7" t="s">
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>0.15</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <v>-0.88</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>0.69</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="7">
         <v>0.59</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="7">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" ht="31" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="5" t="s">
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>0.15</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="7">
         <v>-0.88</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>0.69</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="7">
         <v>0.59</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="7">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:14" ht="23" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-    </row>
-    <row r="13" spans="1:14" ht="23" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-    </row>
-    <row r="14" spans="1:14" ht="23" customHeight="1">
-      <c r="A14" s="1"/>
-    </row>
-    <row r="15" spans="1:14" ht="23" customHeight="1">
-      <c r="A15" s="1"/>
-    </row>
-    <row r="16" spans="1:14" ht="23" customHeight="1">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:14" ht="23" customHeight="1">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:14" ht="23" customHeight="1">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:14" ht="23" customHeight="1">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:14" ht="23" customHeight="1">
-      <c r="A20" s="1"/>
-    </row>
-    <row r="21" spans="1:14" ht="23" customHeight="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-    </row>
-    <row r="22" spans="1:14" ht="23" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-    </row>
-    <row r="23" spans="1:14" ht="23" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+    </row>
+    <row r="14" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+    </row>
+    <row r="23" spans="1:14" ht="23.1" customHeight="1">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4054,7 +4048,7 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="decimal" sqref="C7:C11 G7:G11 E7:E11" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
@@ -4074,7 +4068,7 @@
     <tabColor rgb="FF93A0AC"/>
   </sheetPr>
   <dimension ref="A1:K106"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="5" width="20" customWidth="1"/>
@@ -4084,21 +4078,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="12" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:11" ht="35" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="18" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" spans="1:11" ht="35.1" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="19"/>
@@ -4111,30 +4105,30 @@
       <c r="J2" s="19"/>
       <c r="K2" s="19"/>
     </row>
-    <row r="3" spans="1:11" ht="23" customHeight="1">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" ht="23" customHeight="1">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="2" t="s">
+    <row r="3" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="20" t="str">
+      <c r="H4" s="23" t="str">
         <f>'Throttle Curves'!C4</f>
         <v>WRC17 / Rally1</v>
       </c>
@@ -4142,2492 +4136,2492 @@
       <c r="J4" s="19"/>
       <c r="K4" s="19"/>
     </row>
-    <row r="5" spans="1:11" ht="32" customHeight="1">
-      <c r="A5" s="1"/>
-      <c r="B5" s="8" t="s">
+    <row r="5" spans="1:11" ht="32.1" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" ht="31" customHeight="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="9">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="10">
         <v>0</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="10">
         <f t="shared" ref="C6:C37" si="0">IF($I$9=0,$B6,(1-$H$9)*LN(1+$I$9*$B6)/LN(1+$I$9)+$H$9*$B6)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="10">
         <f t="shared" ref="D6:D37" si="1">IF($I$10=0,$B6,(1-$H$10)*LN(1+$I$10*$B6)/LN(1+$I$10)+$H$10*$B6)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="10">
         <f t="shared" ref="E6:E37" si="2">IF($I$11=0,$B6,(1-$H$11)*LN(1+$I$11*$B6)/LN(1+$I$11)+$H$11*$B6)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="10" t="s">
+      <c r="F6" s="2"/>
+      <c r="G6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="12">
         <f>MATCH('Throttle Curves'!C4,Parameters!B7:B11,0)</f>
         <v>2</v>
       </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" ht="31" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="12">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="13">
         <v>0.01</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="13">
         <f t="shared" si="0"/>
         <v>3.186337086193345E-3</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="13">
         <f t="shared" si="1"/>
         <v>7.6801448322603195E-3</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <f t="shared" si="2"/>
         <v>1.391976367936305E-2</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="9">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" ht="32.1" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="10">
         <v>0.02</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <f t="shared" si="0"/>
         <v>6.4033824337768443E-3</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="10">
         <f t="shared" si="1"/>
         <v>1.5389017612306488E-2</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="10">
         <f t="shared" si="2"/>
         <v>2.7712236977093824E-2</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="13" t="s">
+      <c r="F8" s="2"/>
+      <c r="G8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" ht="31" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="12">
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="13">
         <v>0.03</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="13">
         <f t="shared" si="0"/>
         <v>9.6517337079458313E-3</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="13">
         <f t="shared" si="1"/>
         <v>2.3126938755721561E-2</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <f t="shared" si="2"/>
         <v>4.1379903667644352E-2</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="14">
+      <c r="F9" s="2"/>
+      <c r="G9" s="15">
         <v>1</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="16">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,1)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="16">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,2)</f>
         <v>-0.95</v>
       </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" ht="31" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="9">
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="10">
         <v>0.04</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="10">
         <f t="shared" si="0"/>
         <v>1.2932006193754548E-2</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="10">
         <f t="shared" si="1"/>
         <v>3.0894234068771745E-2</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="10">
         <f t="shared" si="2"/>
         <v>5.4925175529730766E-2</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="16">
+      <c r="F10" s="2"/>
+      <c r="G10" s="17">
         <v>2</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="18">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,3)</f>
         <v>0.25</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="18">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,4)</f>
         <v>-0.55000000000000004</v>
       </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" ht="31" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="12">
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="13">
         <v>0.05</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <f t="shared" si="0"/>
         <v>1.6244833495600405E-2</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <f t="shared" si="1"/>
         <v>3.8691234870011873E-2</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <f t="shared" si="2"/>
         <v>6.835039510225821E-2</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="14">
+      <c r="F11" s="2"/>
+      <c r="G11" s="15">
         <v>3</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="16">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,5)</f>
         <v>0.1</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="16">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,6)</f>
         <v>1</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" ht="31" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="9">
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="10">
         <v>0.06</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="10">
         <f t="shared" si="0"/>
         <v>1.9590868271767738E-2</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="10">
         <f t="shared" si="1"/>
         <v>4.6518278115341136E-2</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="10">
         <f t="shared" si="2"/>
         <v>8.1657838309627112E-2</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" ht="31" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="12">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="13">
         <f t="shared" si="0"/>
         <v>2.2970783006160234E-2</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="13">
         <f t="shared" si="1"/>
         <v>5.437570652662372E-2</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <f t="shared" si="2"/>
         <v>9.4849716963780112E-2</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" ht="31" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="9">
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="10">
         <v>0.08</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="10">
         <f t="shared" si="0"/>
         <v>2.6385270819504796E-2</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="10">
         <f t="shared" si="1"/>
         <v>6.2263868724000346E-2</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="10">
         <f t="shared" si="2"/>
         <v>0.10792818114986957</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" ht="31" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="12">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="13">
         <v>0.09</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="13">
         <f t="shared" si="0"/>
         <v>2.9835046322475019E-2</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="13">
         <f t="shared" si="1"/>
         <v>7.0183119362015323E-2</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="13">
         <f t="shared" si="2"/>
         <v>0.12089532150198161</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" ht="31" customHeight="1">
-      <c r="A16" s="1"/>
-      <c r="B16" s="9">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="B16" s="10">
         <v>0.1</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="10">
         <f t="shared" si="0"/>
         <v>3.33208465133598E-2</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="10">
         <f t="shared" si="1"/>
         <v>7.8133819269695204E-2</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <f t="shared" si="2"/>
         <v>0.13375317137494153</v>
       </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" ht="31" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="12">
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="B17" s="13">
         <v>0.11</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="13">
         <f t="shared" si="0"/>
         <v>3.6843431723099021E-2</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="13">
         <f t="shared" si="1"/>
         <v>8.6116335594713919E-2</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="13">
         <f t="shared" si="2"/>
         <v>0.14650370891784326</v>
       </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" ht="31" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="9">
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A18" s="2"/>
+      <c r="B18" s="10">
         <v>0.12</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="10">
         <f t="shared" si="0"/>
         <v>4.0403586610716101E-2</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="10">
         <f t="shared" si="1"/>
         <v>9.4131041951792213E-2</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="10">
         <f t="shared" si="2"/>
         <v>0.15914885905459161</v>
       </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" ht="31" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="12">
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="13">
         <v>0.13</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="13">
         <f t="shared" si="0"/>
         <v>4.4002121212408853E-2</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="13">
         <f t="shared" si="1"/>
         <v>0.10217831857547742</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="13">
         <f t="shared" si="2"/>
         <v>0.17169049537641662</v>
       </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" ht="31" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="9">
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A20" s="2"/>
+      <c r="B20" s="10">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="10">
         <f t="shared" si="0"/>
         <v>4.7639872047806051E-2</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="10">
         <f t="shared" si="1"/>
         <v>0.1102585524774635</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="10">
         <f t="shared" si="2"/>
         <v>0.18413044195101544</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" ht="31" customHeight="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="12">
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A21" s="2"/>
+      <c r="B21" s="13">
         <v>0.15</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="13">
         <f t="shared" si="0"/>
         <v>5.1317703287169718E-2</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="13">
         <f t="shared" si="1"/>
         <v>0.11837213760861129</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="13">
         <f t="shared" si="2"/>
         <v>0.19647047505268539</v>
       </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" ht="31" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="9">
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A22" s="2"/>
+      <c r="B22" s="10">
         <v>0.16</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="10">
         <f t="shared" si="0"/>
         <v>5.5036507983617249E-2</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="10">
         <f t="shared" si="1"/>
         <v>0.1265194750258396</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="10">
         <f t="shared" si="2"/>
         <v>0.20871232481756263</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" ht="31" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="12">
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A23" s="2"/>
+      <c r="B23" s="13">
         <v>0.17</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="13">
         <f t="shared" si="0"/>
         <v>5.8797209374757908E-2</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="13">
         <f t="shared" si="1"/>
         <v>0.13470097306406517</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="13">
         <f t="shared" si="2"/>
         <v>0.22085767682781182</v>
       </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-    </row>
-    <row r="24" spans="1:11" ht="31" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="9">
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A24" s="2"/>
+      <c r="B24" s="10">
         <v>0.18</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="10">
         <f t="shared" si="0"/>
         <v>6.2600762258491024E-2</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="10">
         <f t="shared" si="1"/>
         <v>0.1429170475133727</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="10">
         <f t="shared" si="2"/>
         <v>0.23290817362840482</v>
       </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" ht="31" customHeight="1">
-      <c r="A25" s="1"/>
-      <c r="B25" s="12">
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A25" s="2"/>
+      <c r="B25" s="13">
         <v>0.19</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="13">
         <f t="shared" si="0"/>
         <v>6.6448154448093127E-2</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="13">
         <f t="shared" si="1"/>
         <v>0.15116812180161127</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="13">
         <f t="shared" si="2"/>
         <v>0.24486541617989693</v>
       </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-    </row>
-    <row r="26" spans="1:11" ht="31" customHeight="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="9">
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="10">
         <v>0.2</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="10">
         <f t="shared" si="0"/>
         <v>7.0340408312143138E-2</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="10">
         <f t="shared" si="1"/>
         <v>0.1594546271826133</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="10">
         <f t="shared" si="2"/>
         <v>0.25673096525041444</v>
       </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-    </row>
-    <row r="27" spans="1:11" ht="31" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="12">
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A27" s="2"/>
+      <c r="B27" s="13">
         <v>0.21</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="13">
         <f t="shared" si="0"/>
         <v>7.4278582405290297E-2</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="13">
         <f t="shared" si="1"/>
         <v>0.1677770029302495</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="13">
         <f t="shared" si="2"/>
         <v>0.26850634274988283</v>
       </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-    </row>
-    <row r="28" spans="1:11" ht="31" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="B28" s="9">
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="10">
         <v>0.22</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="10">
         <f t="shared" si="0"/>
         <v>7.8263773196372607E-2</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="10">
         <f t="shared" si="1"/>
         <v>0.1761356965385342</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="10">
         <f t="shared" si="2"/>
         <v>0.28019303300934545</v>
       </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-    </row>
-    <row r="29" spans="1:11" ht="31" customHeight="1">
-      <c r="A29" s="1"/>
-      <c r="B29" s="12">
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A29" s="2"/>
+      <c r="B29" s="13">
         <v>0.23</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="13">
         <f t="shared" si="0"/>
         <v>8.2297116900944781E-2</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="13">
         <f t="shared" si="1"/>
         <v>0.18453116392801255</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="13">
         <f t="shared" si="2"/>
         <v>0.29179248400806368</v>
       </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-    </row>
-    <row r="30" spans="1:11" ht="31" customHeight="1">
-      <c r="A30" s="1"/>
-      <c r="B30" s="9">
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+    </row>
+    <row r="30" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A30" s="2"/>
+      <c r="B30" s="10">
         <v>0.24</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="10">
         <f t="shared" si="0"/>
         <v>8.6379791425876637E-2</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="10">
         <f t="shared" si="1"/>
         <v>0.19296386965866436</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="10">
         <f t="shared" si="2"/>
         <v>0.30330610855093548</v>
       </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-    </row>
-    <row r="31" spans="1:11" ht="31" customHeight="1">
-      <c r="A31" s="1"/>
-      <c r="B31" s="12">
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+    </row>
+    <row r="31" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A31" s="2"/>
+      <c r="B31" s="13">
         <v>0.25</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="13">
         <f t="shared" si="0"/>
         <v>9.0513018434350292E-2</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="13">
         <f t="shared" si="1"/>
         <v>0.20143428714957642</v>
       </c>
-      <c r="E31" s="12">
+      <c r="E31" s="13">
         <f t="shared" si="2"/>
         <v>0.31473528539862616</v>
       </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-    </row>
-    <row r="32" spans="1:11" ht="31" customHeight="1">
-      <c r="A32" s="1"/>
-      <c r="B32" s="9">
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A32" s="2"/>
+      <c r="B32" s="10">
         <v>0.26</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="10">
         <f t="shared" si="0"/>
         <v>9.469806554031196E-2</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="10">
         <f t="shared" si="1"/>
         <v>0.20994289890563997</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="10">
         <f t="shared" si="2"/>
         <v>0.32608136035267266</v>
       </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-    </row>
-    <row r="33" spans="1:11" ht="31" customHeight="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="12">
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A33" s="2"/>
+      <c r="B33" s="13">
         <v>0.27</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="13">
         <f t="shared" si="0"/>
         <v>9.8936248642242236E-2</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="13">
         <f t="shared" si="1"/>
         <v>0.21849019675154671</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="13">
         <f t="shared" si="2"/>
         <v>0.33734564729769712</v>
       </c>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-    </row>
-    <row r="34" spans="1:11" ht="31" customHeight="1">
-      <c r="A34" s="1"/>
-      <c r="B34" s="9">
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A34" s="2"/>
+      <c r="B34" s="10">
         <v>0.28000000000000003</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="10">
         <f t="shared" si="0"/>
         <v>0.10322893440699456</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="10">
         <f t="shared" si="1"/>
         <v>0.22707668207336662</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="10">
         <f t="shared" si="2"/>
         <v>0.34852942920274782</v>
       </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-    </row>
-    <row r="35" spans="1:11" ht="31" customHeight="1">
-      <c r="A35" s="1"/>
-      <c r="B35" s="12">
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+    </row>
+    <row r="35" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A35" s="2"/>
+      <c r="B35" s="13">
         <v>0.28999999999999998</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="13">
         <f t="shared" si="0"/>
         <v>0.10757754291543231</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="13">
         <f t="shared" si="1"/>
         <v>0.23570286606800478</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="13">
         <f t="shared" si="2"/>
         <v>0.35963395908367646</v>
       </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-    </row>
-    <row r="36" spans="1:11" ht="31" customHeight="1">
-      <c r="A36" s="1"/>
-      <c r="B36" s="9">
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+    </row>
+    <row r="36" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A36" s="2"/>
+      <c r="B36" s="10">
         <v>0.3</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="10">
         <f t="shared" si="0"/>
         <v>0.11198355048268077</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="10">
         <f t="shared" si="1"/>
         <v>0.24436927000084591</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="10">
         <f t="shared" si="2"/>
         <v>0.37066046092835692</v>
       </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-    </row>
-    <row r="37" spans="1:11" ht="31" customHeight="1">
-      <c r="A37" s="1"/>
-      <c r="B37" s="12">
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+    </row>
+    <row r="37" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A37" s="2"/>
+      <c r="B37" s="13">
         <v>0.31</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="13">
         <f t="shared" si="0"/>
         <v>0.11644849266700712</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="13">
         <f t="shared" si="1"/>
         <v>0.25307642547191278</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="13">
         <f t="shared" si="2"/>
         <v>0.3816101305864531</v>
       </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-    </row>
-    <row r="38" spans="1:11" ht="31" customHeight="1">
-      <c r="A38" s="1"/>
-      <c r="B38" s="9">
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+    </row>
+    <row r="38" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A38" s="2"/>
+      <c r="B38" s="10">
         <v>0.32</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="10">
         <f t="shared" ref="C38:C69" si="3">IF($I$9=0,$B38,(1-$H$9)*LN(1+$I$9*$B38)/LN(1+$I$9)+$H$9*$B38)</f>
         <v>0.12097396748267401</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="10">
         <f t="shared" ref="D38:D69" si="4">IF($I$10=0,$B38,(1-$H$10)*LN(1+$I$10*$B38)/LN(1+$I$10)+$H$10*$B38)</f>
         <v>0.26182487469087928</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="10">
         <f t="shared" ref="E38:E69" si="5">IF($I$11=0,$B38,(1-$H$11)*LN(1+$I$11*$B38)/LN(1+$I$11)+$H$11*$B38)</f>
         <v>0.39248413662535597</v>
       </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-    </row>
-    <row r="39" spans="1:11" ht="31" customHeight="1">
-      <c r="A39" s="1"/>
-      <c r="B39" s="12">
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+    </row>
+    <row r="39" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A39" s="2"/>
+      <c r="B39" s="13">
         <v>0.33</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="13">
         <f t="shared" si="3"/>
         <v>0.12556163883358859</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="13">
         <f t="shared" si="4"/>
         <v>0.27061517076129021</v>
       </c>
-      <c r="E39" s="12">
+      <c r="E39" s="13">
         <f t="shared" si="5"/>
         <v>0.40328362115381855</v>
       </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-    </row>
-    <row r="40" spans="1:11" ht="31" customHeight="1">
-      <c r="A40" s="1"/>
-      <c r="B40" s="9">
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+    </row>
+    <row r="40" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A40" s="2"/>
+      <c r="B40" s="10">
         <v>0.34</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="10">
         <f t="shared" si="3"/>
         <v>0.13021324018620845</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="10">
         <f t="shared" si="4"/>
         <v>0.27944787797436538</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="10">
         <f t="shared" si="5"/>
         <v>0.41400970061474307</v>
       </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-    </row>
-    <row r="41" spans="1:11" ht="31" customHeight="1">
-      <c r="A41" s="1"/>
-      <c r="B41" s="12">
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A41" s="2"/>
+      <c r="B41" s="13">
         <v>0.35</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="13">
         <f t="shared" si="3"/>
         <v>0.13493057850199364</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="13">
         <f t="shared" si="4"/>
         <v>0.28832357211277315</v>
       </c>
-      <c r="E41" s="12">
+      <c r="E41" s="13">
         <f t="shared" si="5"/>
         <v>0.42466346654849568</v>
       </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-    </row>
-    <row r="42" spans="1:11" ht="31" customHeight="1">
-      <c r="A42" s="1"/>
-      <c r="B42" s="9">
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+    </row>
+    <row r="42" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A42" s="2"/>
+      <c r="B42" s="10">
         <v>0.36</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="10">
         <f t="shared" si="3"/>
         <v>0.1397155384517296</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="10">
         <f t="shared" si="4"/>
         <v>0.29724284076478735</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="10">
         <f t="shared" si="5"/>
         <v>0.43524598632805317</v>
       </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-    </row>
-    <row r="43" spans="1:11" ht="31" customHeight="1">
-      <c r="A43" s="1"/>
-      <c r="B43" s="12">
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A43" s="2"/>
+      <c r="B43" s="13">
         <v>0.37</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="13">
         <f t="shared" si="3"/>
         <v>0.14457008693631948</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="13">
         <f t="shared" si="4"/>
         <v>0.3062062836492514</v>
       </c>
-      <c r="E43" s="12">
+      <c r="E43" s="13">
         <f t="shared" si="5"/>
         <v>0.44575830386722187</v>
       </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-    </row>
-    <row r="44" spans="1:11" ht="31" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="9">
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A44" s="2"/>
+      <c r="B44" s="10">
         <v>0.38</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="10">
         <f t="shared" si="3"/>
         <v>0.14949627794118397</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="10">
         <f t="shared" si="4"/>
         <v>0.31521451295180247</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="10">
         <f t="shared" si="5"/>
         <v>0.45620144030309984</v>
       </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-    </row>
-    <row r="45" spans="1:11" ht="31" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="12">
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+    </row>
+    <row r="45" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A45" s="2"/>
+      <c r="B45" s="13">
         <v>0.39</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="13">
         <f t="shared" si="3"/>
         <v>0.15449625775425421</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="13">
         <f t="shared" si="4"/>
         <v>0.32426815367282602</v>
       </c>
-      <c r="E45" s="12">
+      <c r="E45" s="13">
         <f t="shared" si="5"/>
         <v>0.46657639465390466</v>
       </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-    </row>
-    <row r="46" spans="1:11" ht="31" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="B46" s="9">
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+    </row>
+    <row r="46" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A46" s="2"/>
+      <c r="B46" s="10">
         <v>0.4</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="10">
         <f t="shared" si="3"/>
         <v>0.1595722705807357</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="10">
         <f t="shared" si="4"/>
         <v>0.33336784398763486</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="10">
         <f t="shared" si="5"/>
         <v>0.47688414445321758</v>
       </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-    </row>
-    <row r="47" spans="1:11" ht="31" customHeight="1">
-      <c r="A47" s="1"/>
-      <c r="B47" s="12">
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+    </row>
+    <row r="47" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A47" s="2"/>
+      <c r="B47" s="13">
         <v>0.41</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="13">
         <f t="shared" si="3"/>
         <v>0.16472666459140581</v>
       </c>
-      <c r="D47" s="12">
+      <c r="D47" s="13">
         <f t="shared" si="4"/>
         <v>0.3425142356193922</v>
       </c>
-      <c r="E47" s="12">
+      <c r="E47" s="13">
         <f t="shared" si="5"/>
         <v>0.48712564636166195</v>
       </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-    </row>
-    <row r="48" spans="1:11" ht="31" customHeight="1">
-      <c r="A48" s="1"/>
-      <c r="B48" s="9">
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A48" s="2"/>
+      <c r="B48" s="10">
         <v>0.42</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="10">
         <f t="shared" si="3"/>
         <v>0.16996189844524612</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="10">
         <f t="shared" si="4"/>
         <v>0.35170799422532273</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="10">
         <f t="shared" si="5"/>
         <v>0.4973018367569616</v>
       </c>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-    </row>
-    <row r="49" spans="1:11" ht="31" customHeight="1">
-      <c r="A49" s="1"/>
-      <c r="B49" s="12">
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A49" s="2"/>
+      <c r="B49" s="13">
         <v>0.43</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="13">
         <f t="shared" si="3"/>
         <v>0.17528054833176071</v>
       </c>
-      <c r="D49" s="12">
+      <c r="D49" s="13">
         <f t="shared" si="4"/>
         <v>0.36094979979678654</v>
       </c>
-      <c r="E49" s="12">
+      <c r="E49" s="13">
         <f t="shared" si="5"/>
         <v>0.50741363230329817</v>
       </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-    </row>
-    <row r="50" spans="1:11" ht="31" customHeight="1">
-      <c r="A50" s="1"/>
-      <c r="B50" s="9">
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A50" s="2"/>
+      <c r="B50" s="10">
         <v>0.44</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="10">
         <f t="shared" si="3"/>
         <v>0.18068531558347348</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="10">
         <f t="shared" si="4"/>
         <v>0.37024034707381337</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="10">
         <f t="shared" si="5"/>
         <v>0.51746193050082889</v>
       </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-    </row>
-    <row r="51" spans="1:11" ht="31" customHeight="1">
-      <c r="A51" s="1"/>
-      <c r="B51" s="12">
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A51" s="2"/>
+      <c r="B51" s="13">
         <v>0.45</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="13">
         <f t="shared" si="3"/>
         <v>0.18617903491491378</v>
       </c>
-      <c r="D51" s="12">
+      <c r="D51" s="13">
         <f t="shared" si="4"/>
         <v>0.37958034597473334</v>
       </c>
-      <c r="E51" s="12">
+      <c r="E51" s="13">
         <f t="shared" si="5"/>
         <v>0.5274476102161888</v>
       </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-    </row>
-    <row r="52" spans="1:11" ht="31" customHeight="1">
-      <c r="A52" s="1"/>
-      <c r="B52" s="9">
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A52" s="2"/>
+      <c r="B52" s="10">
         <v>0.46</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="10">
         <f t="shared" si="3"/>
         <v>0.19176468335099819</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="10">
         <f t="shared" si="4"/>
         <v>0.38897052204156446</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="10">
         <f t="shared" si="5"/>
         <v>0.5373715321947633</v>
       </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-    </row>
-    <row r="53" spans="1:11" ht="31" customHeight="1">
-      <c r="A53" s="1"/>
-      <c r="B53" s="12">
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A53" s="2"/>
+      <c r="B53" s="13">
         <v>0.47</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="13">
         <f t="shared" si="3"/>
         <v>0.19744538991520971</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="13">
         <f t="shared" si="4"/>
         <v>0.39841161690185894</v>
       </c>
-      <c r="E53" s="12">
+      <c r="E53" s="13">
         <f t="shared" si="5"/>
         <v>0.54723453955547574</v>
       </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-    </row>
-    <row r="54" spans="1:11" ht="31" customHeight="1">
-      <c r="A54" s="1"/>
-      <c r="B54" s="9">
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+    </row>
+    <row r="54" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A54" s="2"/>
+      <c r="B54" s="10">
         <v>0.48</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="10">
         <f t="shared" si="3"/>
         <v>0.20322444615651072</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="10">
         <f t="shared" si="4"/>
         <v>0.40790438874774249</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="10">
         <f t="shared" si="5"/>
         <v>0.55703745826880269</v>
       </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-    </row>
-    <row r="55" spans="1:11" ht="31" customHeight="1">
-      <c r="A55" s="1"/>
-      <c r="B55" s="12">
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+    </row>
+    <row r="55" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A55" s="2"/>
+      <c r="B55" s="13">
         <v>0.49</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="13">
         <f t="shared" si="3"/>
         <v>0.20910531760365855</v>
       </c>
-      <c r="D55" s="12">
+      <c r="D55" s="13">
         <f t="shared" si="4"/>
         <v>0.4174496128329182</v>
       </c>
-      <c r="E55" s="12">
+      <c r="E55" s="13">
         <f t="shared" si="5"/>
         <v>0.56678109761869333</v>
       </c>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-    </row>
-    <row r="56" spans="1:11" ht="31" customHeight="1">
-      <c r="A56" s="1"/>
-      <c r="B56" s="9">
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+    </row>
+    <row r="56" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A56" s="2"/>
+      <c r="B56" s="10">
         <v>0.5</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="10">
         <f t="shared" si="3"/>
         <v>0.21509165624673118</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="10">
         <f t="shared" si="4"/>
         <v>0.42704808198845362</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E56" s="10">
         <f t="shared" si="5"/>
         <v>0.57646625064904067</v>
       </c>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-    </row>
-    <row r="57" spans="1:11" ht="31" customHeight="1">
-      <c r="A57" s="1"/>
-      <c r="B57" s="12">
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+    </row>
+    <row r="57" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A57" s="2"/>
+      <c r="B57" s="13">
         <v>0.51</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57" s="13">
         <f t="shared" si="3"/>
         <v>0.22118731415842602</v>
       </c>
-      <c r="D57" s="12">
+      <c r="D57" s="13">
         <f t="shared" si="4"/>
         <v>0.43670060715820669</v>
       </c>
-      <c r="E57" s="12">
+      <c r="E57" s="13">
         <f t="shared" si="5"/>
         <v>0.5860936945953189</v>
       </c>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-    </row>
-    <row r="58" spans="1:11" ht="31" customHeight="1">
-      <c r="A58" s="1"/>
-      <c r="B58" s="9">
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+    </row>
+    <row r="58" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A58" s="2"/>
+      <c r="B58" s="10">
         <v>0.52</v>
       </c>
-      <c r="C58" s="9">
+      <c r="C58" s="10">
         <f t="shared" si="3"/>
         <v>0.22739635838235542</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="10">
         <f t="shared" si="4"/>
         <v>0.44640801795479484</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="10">
         <f t="shared" si="5"/>
         <v>0.59566419130197479</v>
       </c>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-    </row>
-    <row r="59" spans="1:11" ht="31" customHeight="1">
-      <c r="A59" s="1"/>
-      <c r="B59" s="12">
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+    </row>
+    <row r="59" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A59" s="2"/>
+      <c r="B59" s="13">
         <v>0.53</v>
       </c>
-      <c r="C59" s="12">
+      <c r="C59" s="13">
         <f t="shared" si="3"/>
         <v>0.23372308723244489</v>
       </c>
-      <c r="D59" s="12">
+      <c r="D59" s="13">
         <f t="shared" si="4"/>
         <v>0.45617116323706058</v>
       </c>
-      <c r="E59" s="12">
+      <c r="E59" s="13">
         <f t="shared" si="5"/>
         <v>0.60517848762613446</v>
       </c>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-    </row>
-    <row r="60" spans="1:11" ht="31" customHeight="1">
-      <c r="A60" s="1"/>
-      <c r="B60" s="9">
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+    </row>
+    <row r="60" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A60" s="2"/>
+      <c r="B60" s="10">
         <v>0.54</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="10">
         <f t="shared" si="3"/>
         <v>0.24017204816703402</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="10">
         <f t="shared" si="4"/>
         <v>0.46599091171004031</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="10">
         <f t="shared" si="5"/>
         <v>0.61463731582815906</v>
       </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-    </row>
-    <row r="61" spans="1:11" ht="31" customHeight="1">
-      <c r="A61" s="1"/>
-      <c r="B61" s="12">
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A61" s="2"/>
+      <c r="B61" s="13">
         <v>0.55000000000000004</v>
       </c>
-      <c r="C61" s="12">
+      <c r="C61" s="13">
         <f t="shared" si="3"/>
         <v>0.24674805742384046</v>
       </c>
-      <c r="D61" s="12">
+      <c r="D61" s="13">
         <f t="shared" si="4"/>
         <v>0.47586815254849502</v>
       </c>
-      <c r="E61" s="12">
+      <c r="E61" s="13">
         <f t="shared" si="5"/>
         <v>0.62404139394956171</v>
       </c>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-    </row>
-    <row r="62" spans="1:11" ht="31" customHeight="1">
-      <c r="A62" s="1"/>
-      <c r="B62" s="9">
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+    </row>
+    <row r="62" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A62" s="2"/>
+      <c r="B62" s="10">
         <v>0.56000000000000005</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C62" s="10">
         <f t="shared" si="3"/>
         <v>0.25345622162814618</v>
       </c>
-      <c r="D62" s="9">
+      <c r="D62" s="10">
         <f t="shared" si="4"/>
         <v>0.48580379604512214</v>
       </c>
-      <c r="E62" s="9">
+      <c r="E62" s="10">
         <f t="shared" si="5"/>
         <v>0.63339142617877142</v>
       </c>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-    </row>
-    <row r="63" spans="1:11" ht="31" customHeight="1">
-      <c r="A63" s="1"/>
-      <c r="B63" s="12">
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+    </row>
+    <row r="63" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A63" s="2"/>
+      <c r="B63" s="13">
         <v>0.56999999999999995</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63" s="13">
         <f t="shared" si="3"/>
         <v>0.26030196161705293</v>
       </c>
-      <c r="D63" s="12">
+      <c r="D63" s="13">
         <f t="shared" si="4"/>
         <v>0.49579877428463126</v>
       </c>
-      <c r="E63" s="12">
+      <c r="E63" s="13">
         <f t="shared" si="5"/>
         <v>0.64268810320521186</v>
       </c>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-    </row>
-    <row r="64" spans="1:11" ht="31" customHeight="1">
-      <c r="A64" s="1"/>
-      <c r="B64" s="9">
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+    </row>
+    <row r="64" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A64" s="2"/>
+      <c r="B64" s="10">
         <v>0.57999999999999996</v>
       </c>
-      <c r="C64" s="9">
+      <c r="C64" s="10">
         <f t="shared" si="3"/>
         <v>0.26729103875825755</v>
       </c>
-      <c r="D64" s="9">
+      <c r="D64" s="10">
         <f t="shared" si="4"/>
         <v>0.50585404184493254</v>
       </c>
-      <c r="E64" s="9">
+      <c r="E64" s="10">
         <f t="shared" si="5"/>
         <v>0.65193210256214051</v>
       </c>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-    </row>
-    <row r="65" spans="1:11" ht="31" customHeight="1">
-      <c r="A65" s="1"/>
-      <c r="B65" s="12">
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+    </row>
+    <row r="65" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A65" s="2"/>
+      <c r="B65" s="13">
         <v>0.59</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65" s="13">
         <f t="shared" si="3"/>
         <v>0.27442958408348866</v>
       </c>
-      <c r="D65" s="12">
+      <c r="D65" s="13">
         <f t="shared" si="4"/>
         <v>0.51597057652675415</v>
       </c>
-      <c r="E65" s="12">
+      <c r="E65" s="13">
         <f t="shared" si="5"/>
         <v>0.66112408895866737</v>
       </c>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-    </row>
-    <row r="66" spans="1:11" ht="31" customHeight="1">
-      <c r="A66" s="1"/>
-      <c r="B66" s="9">
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+    </row>
+    <row r="66" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A66" s="2"/>
+      <c r="B66" s="10">
         <v>0.6</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C66" s="10">
         <f t="shared" si="3"/>
         <v>0.28172413060573137</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="10">
         <f t="shared" si="4"/>
         <v>0.5261493801130871</v>
       </c>
-      <c r="E66" s="9">
+      <c r="E66" s="10">
         <f t="shared" si="5"/>
         <v>0.67026471460137405</v>
       </c>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-    </row>
-    <row r="67" spans="1:11" ht="31" customHeight="1">
-      <c r="A67" s="1"/>
-      <c r="B67" s="12">
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+    </row>
+    <row r="67" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A67" s="2"/>
+      <c r="B67" s="13">
         <v>0.61</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="13">
         <f t="shared" si="3"/>
         <v>0.28918164924710904</v>
       </c>
-      <c r="D67" s="12">
+      <c r="D67" s="13">
         <f t="shared" si="4"/>
         <v>0.53639147915992924</v>
       </c>
-      <c r="E67" s="12">
+      <c r="E67" s="13">
         <f t="shared" si="5"/>
         <v>0.67935461950590303</v>
       </c>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-    </row>
-    <row r="68" spans="1:11" ht="31" customHeight="1">
-      <c r="A68" s="1"/>
-      <c r="B68" s="9">
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+    </row>
+    <row r="68" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A68" s="2"/>
+      <c r="B68" s="10">
         <v>0.62</v>
       </c>
-      <c r="C68" s="9">
+      <c r="C68" s="10">
         <f t="shared" si="3"/>
         <v>0.29680958887258779</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="10">
         <f t="shared" si="4"/>
         <v>0.54669792581989296</v>
       </c>
-      <c r="E68" s="9">
+      <c r="E68" s="10">
         <f t="shared" si="5"/>
         <v>0.68839443179891013</v>
       </c>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-    </row>
-    <row r="69" spans="1:11" ht="31" customHeight="1">
-      <c r="A69" s="1"/>
-      <c r="B69" s="12">
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+    </row>
+    <row r="69" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A69" s="2"/>
+      <c r="B69" s="13">
         <v>0.63</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="13">
         <f t="shared" si="3"/>
         <v>0.30461592100575746</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="13">
         <f t="shared" si="4"/>
         <v>0.55706979870032503</v>
       </c>
-      <c r="E69" s="12">
+      <c r="E69" s="13">
         <f t="shared" si="5"/>
         <v>0.69738476801071747</v>
       </c>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-    </row>
-    <row r="70" spans="1:11" ht="31" customHeight="1">
-      <c r="A70" s="1"/>
-      <c r="B70" s="9">
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+    </row>
+    <row r="70" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A70" s="2"/>
+      <c r="B70" s="10">
         <v>0.64</v>
       </c>
-      <c r="C70" s="9">
+      <c r="C70" s="10">
         <f t="shared" ref="C70:C106" si="6">IF($I$9=0,$B70,(1-$H$9)*LN(1+$I$9*$B70)/LN(1+$I$9)+$H$9*$B70)</f>
         <v>0.31260918989955822</v>
       </c>
-      <c r="D70" s="9">
+      <c r="D70" s="10">
         <f t="shared" ref="D70:D106" si="7">IF($I$10=0,$B70,(1-$H$10)*LN(1+$I$10*$B70)/LN(1+$I$10)+$H$10*$B70)</f>
         <v>0.56750820375769195</v>
       </c>
-      <c r="E70" s="9">
+      <c r="E70" s="10">
         <f t="shared" ref="E70:E106" si="8">IF($I$11=0,$B70,(1-$H$11)*LN(1+$I$11*$B70)/LN(1+$I$11)+$H$11*$B70)</f>
         <v>0.70632623335902323</v>
       </c>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-    </row>
-    <row r="71" spans="1:11" ht="31" customHeight="1">
-      <c r="A71" s="1"/>
-      <c r="B71" s="12">
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+    </row>
+    <row r="71" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A71" s="2"/>
+      <c r="B71" s="13">
         <v>0.65</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="13">
         <f t="shared" si="6"/>
         <v>0.32079856875041485</v>
       </c>
-      <c r="D71" s="12">
+      <c r="D71" s="13">
         <f t="shared" si="7"/>
         <v>0.5780142752300842</v>
       </c>
-      <c r="E71" s="12">
+      <c r="E71" s="13">
         <f t="shared" si="8"/>
         <v>0.71521942202398203</v>
       </c>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
-    </row>
-    <row r="72" spans="1:11" ht="31" customHeight="1">
-      <c r="A72" s="1"/>
-      <c r="B72" s="9">
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+    </row>
+    <row r="72" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A72" s="2"/>
+      <c r="B72" s="10">
         <v>0.66</v>
       </c>
-      <c r="C72" s="9">
+      <c r="C72" s="10">
         <f t="shared" si="6"/>
         <v>0.3291939229831008</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D72" s="10">
         <f t="shared" si="7"/>
         <v>0.58858917660980759</v>
       </c>
-      <c r="E72" s="9">
+      <c r="E72" s="10">
         <f t="shared" si="8"/>
         <v>0.72406491741498025</v>
       </c>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-    </row>
-    <row r="73" spans="1:11" ht="31" customHeight="1">
-      <c r="A73" s="1"/>
-      <c r="B73" s="12">
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+    </row>
+    <row r="73" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A73" s="2"/>
+      <c r="B73" s="13">
         <v>0.67</v>
       </c>
-      <c r="C73" s="12">
+      <c r="C73" s="13">
         <f t="shared" si="6"/>
         <v>0.33780588170117226</v>
       </c>
-      <c r="D73" s="12">
+      <c r="D73" s="13">
         <f t="shared" si="7"/>
         <v>0.59923410165814361</v>
       </c>
-      <c r="E73" s="12">
+      <c r="E73" s="13">
         <f t="shared" si="8"/>
         <v>0.73286329242939496</v>
       </c>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-    </row>
-    <row r="74" spans="1:11" ht="31" customHeight="1">
-      <c r="A74" s="1"/>
-      <c r="B74" s="9">
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+    </row>
+    <row r="74" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A74" s="2"/>
+      <c r="B74" s="10">
         <v>0.68</v>
       </c>
-      <c r="C74" s="9">
+      <c r="C74" s="10">
         <f t="shared" si="6"/>
         <v>0.34664591860085897</v>
       </c>
-      <c r="D74" s="9">
+      <c r="D74" s="10">
         <f t="shared" si="7"/>
         <v>0.60995027546449632</v>
       </c>
-      <c r="E74" s="9">
+      <c r="E74" s="10">
         <f t="shared" si="8"/>
         <v>0.74161510970363209</v>
       </c>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-    </row>
-    <row r="75" spans="1:11" ht="31" customHeight="1">
-      <c r="A75" s="1"/>
-      <c r="B75" s="12">
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+    </row>
+    <row r="75" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A75" s="2"/>
+      <c r="B75" s="13">
         <v>0.69</v>
       </c>
-      <c r="C75" s="12">
+      <c r="C75" s="13">
         <f t="shared" si="6"/>
         <v>0.35572644389352442</v>
       </c>
-      <c r="D75" s="12">
+      <c r="D75" s="13">
         <f t="shared" si="7"/>
         <v>0.62073895555227376</v>
       </c>
-      <c r="E75" s="12">
+      <c r="E75" s="13">
         <f t="shared" si="8"/>
         <v>0.75032092185671373</v>
       </c>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
-    </row>
-    <row r="76" spans="1:11" ht="31" customHeight="1">
-      <c r="A76" s="1"/>
-      <c r="B76" s="9">
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+    </row>
+    <row r="76" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A76" s="2"/>
+      <c r="B76" s="10">
         <v>0.7</v>
       </c>
-      <c r="C76" s="9">
+      <c r="C76" s="10">
         <f t="shared" si="6"/>
         <v>0.36506090908439143</v>
       </c>
-      <c r="D76" s="9">
+      <c r="D76" s="10">
         <f t="shared" si="7"/>
         <v>0.63160143303400229</v>
       </c>
-      <c r="E76" s="9">
+      <c r="E76" s="10">
         <f t="shared" si="8"/>
         <v>0.75898127172667929</v>
       </c>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
-    </row>
-    <row r="77" spans="1:11" ht="31" customHeight="1">
-      <c r="A77" s="1"/>
-      <c r="B77" s="12">
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+    </row>
+    <row r="77" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A77" s="2"/>
+      <c r="B77" s="13">
         <v>0.71</v>
       </c>
-      <c r="C77" s="12">
+      <c r="C77" s="13">
         <f t="shared" si="6"/>
         <v>0.37466392682746691</v>
       </c>
-      <c r="D77" s="12">
+      <c r="D77" s="13">
         <f t="shared" si="7"/>
         <v>0.64253903381832389</v>
       </c>
-      <c r="E77" s="12">
+      <c r="E77" s="13">
         <f t="shared" si="8"/>
         <v>0.76759669260005581</v>
       </c>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
-    </row>
-    <row r="78" spans="1:11" ht="31" customHeight="1">
-      <c r="A78" s="1"/>
-      <c r="B78" s="9">
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+    </row>
+    <row r="78" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A78" s="2"/>
+      <c r="B78" s="10">
         <v>0.72</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C78" s="10">
         <f t="shared" si="6"/>
         <v>0.3845514085370963</v>
       </c>
-      <c r="D78" s="9">
+      <c r="D78" s="10">
         <f t="shared" si="7"/>
         <v>0.65355311987170273</v>
       </c>
-      <c r="E78" s="9">
+      <c r="E78" s="10">
         <f t="shared" si="8"/>
         <v>0.77616770843463589</v>
       </c>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-      <c r="K78" s="1"/>
-    </row>
-    <row r="79" spans="1:11" ht="31" customHeight="1">
-      <c r="A79" s="1"/>
-      <c r="B79" s="12">
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+    </row>
+    <row r="79" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A79" s="2"/>
+      <c r="B79" s="13">
         <v>0.73</v>
       </c>
-      <c r="C79" s="12">
+      <c r="C79" s="13">
         <f t="shared" si="6"/>
         <v>0.39474072300959206</v>
       </c>
-      <c r="D79" s="12">
+      <c r="D79" s="13">
         <f t="shared" si="7"/>
         <v>0.66464509053784282</v>
       </c>
-      <c r="E79" s="12">
+      <c r="E79" s="13">
         <f t="shared" si="8"/>
         <v>0.78469483407579999</v>
       </c>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
-    </row>
-    <row r="80" spans="1:11" ht="31" customHeight="1">
-      <c r="A80" s="1"/>
-      <c r="B80" s="9">
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+    </row>
+    <row r="80" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A80" s="2"/>
+      <c r="B80" s="10">
         <v>0.74</v>
       </c>
-      <c r="C80" s="9">
+      <c r="C80" s="10">
         <f t="shared" si="6"/>
         <v>0.4052508800257974</v>
       </c>
-      <c r="D80" s="9">
+      <c r="D80" s="10">
         <f t="shared" si="7"/>
         <v>0.67581638391801158</v>
       </c>
-      <c r="E80" s="9">
+      <c r="E80" s="10">
         <f t="shared" si="8"/>
         <v>0.7931785754666032</v>
       </c>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
-      <c r="K80" s="1"/>
-    </row>
-    <row r="81" spans="1:11" ht="31" customHeight="1">
-      <c r="A81" s="1"/>
-      <c r="B81" s="12">
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2"/>
+    </row>
+    <row r="81" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A81" s="2"/>
+      <c r="B81" s="13">
         <v>0.75</v>
       </c>
-      <c r="C81" s="12">
+      <c r="C81" s="13">
         <f t="shared" si="6"/>
         <v>0.41610274380958168</v>
       </c>
-      <c r="D81" s="12">
+      <c r="D81" s="13">
         <f t="shared" si="7"/>
         <v>0.68706847831567486</v>
       </c>
-      <c r="E81" s="12">
+      <c r="E81" s="13">
         <f t="shared" si="8"/>
         <v>0.80161942985184376</v>
       </c>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
-    </row>
-    <row r="82" spans="1:11" ht="31" customHeight="1">
-      <c r="A82" s="1"/>
-      <c r="B82" s="9">
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+    </row>
+    <row r="82" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A82" s="2"/>
+      <c r="B82" s="10">
         <v>0.76</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82" s="10">
         <f t="shared" si="6"/>
         <v>0.42731928236457911</v>
       </c>
-      <c r="D82" s="9">
+      <c r="D82" s="10">
         <f t="shared" si="7"/>
         <v>0.69840289374907738</v>
       </c>
-      <c r="E82" s="9">
+      <c r="E82" s="10">
         <f t="shared" si="8"/>
         <v>0.81001788597631541</v>
       </c>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-    </row>
-    <row r="83" spans="1:11" ht="31" customHeight="1">
-      <c r="A83" s="1"/>
-      <c r="B83" s="12">
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
+    </row>
+    <row r="83" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A83" s="2"/>
+      <c r="B83" s="13">
         <v>0.77</v>
       </c>
-      <c r="C83" s="12">
+      <c r="C83" s="13">
         <f t="shared" si="6"/>
         <v>0.43892586017817919</v>
       </c>
-      <c r="D83" s="12">
+      <c r="D83" s="13">
         <f t="shared" si="7"/>
         <v>0.70982119353563444</v>
       </c>
-      <c r="E83" s="12">
+      <c r="E83" s="13">
         <f t="shared" si="8"/>
         <v>0.81837442427744556</v>
       </c>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-      <c r="K83" s="1"/>
-    </row>
-    <row r="84" spans="1:11" ht="31" customHeight="1">
-      <c r="A84" s="1"/>
-      <c r="B84" s="9">
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
+    </row>
+    <row r="84" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A84" s="2"/>
+      <c r="B84" s="10">
         <v>0.78</v>
       </c>
-      <c r="C84" s="9">
+      <c r="C84" s="10">
         <f t="shared" si="6"/>
         <v>0.45095058367145918</v>
       </c>
-      <c r="D84" s="9">
+      <c r="D84" s="10">
         <f t="shared" si="7"/>
         <v>0.72132498595226613</v>
       </c>
-      <c r="E84" s="9">
+      <c r="E84" s="10">
         <f t="shared" si="8"/>
         <v>0.82668951707250571</v>
       </c>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
-      <c r="K84" s="1"/>
-    </row>
-    <row r="85" spans="1:11" ht="31" customHeight="1">
-      <c r="A85" s="1"/>
-      <c r="B85" s="12">
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
+    </row>
+    <row r="85" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A85" s="2"/>
+      <c r="B85" s="13">
         <v>0.79</v>
       </c>
-      <c r="C85" s="12">
+      <c r="C85" s="13">
         <f t="shared" si="6"/>
         <v>0.46342471122880308</v>
       </c>
-      <c r="D85" s="12">
+      <c r="D85" s="13">
         <f t="shared" si="7"/>
         <v>0.73291592597608868</v>
       </c>
-      <c r="E85" s="12">
+      <c r="E85" s="13">
         <f t="shared" si="8"/>
         <v>0.83496362874057861</v>
       </c>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
-      <c r="K85" s="1"/>
-    </row>
-    <row r="86" spans="1:11" ht="31" customHeight="1">
-      <c r="A86" s="1"/>
-      <c r="B86" s="9">
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2"/>
+    </row>
+    <row r="86" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A86" s="2"/>
+      <c r="B86" s="10">
         <v>0.8</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C86" s="10">
         <f t="shared" si="6"/>
         <v>0.4763831428591197</v>
       </c>
-      <c r="D86" s="9">
+      <c r="D86" s="10">
         <f t="shared" si="7"/>
         <v>0.74459571711016936</v>
       </c>
-      <c r="E86" s="9">
+      <c r="E86" s="10">
         <f t="shared" si="8"/>
         <v>0.84319721589945518</v>
       </c>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
-      <c r="K86" s="1"/>
-    </row>
-    <row r="87" spans="1:11" ht="31" customHeight="1">
-      <c r="A87" s="1"/>
-      <c r="B87" s="12">
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
+    </row>
+    <row r="87" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A87" s="2"/>
+      <c r="B87" s="13">
         <v>0.81</v>
       </c>
-      <c r="C87" s="12">
+      <c r="C87" s="13">
         <f t="shared" si="6"/>
         <v>0.48986500879948736</v>
       </c>
-      <c r="D87" s="12">
+      <c r="D87" s="13">
         <f t="shared" si="7"/>
         <v>0.75636611329938919</v>
       </c>
-      <c r="E87" s="12">
+      <c r="E87" s="13">
         <f t="shared" si="8"/>
         <v>0.85139072757763268</v>
       </c>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
-      <c r="K87" s="1"/>
-    </row>
-    <row r="88" spans="1:11" ht="31" customHeight="1">
-      <c r="A88" s="1"/>
-      <c r="B88" s="9">
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
+    </row>
+    <row r="88" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A88" s="2"/>
+      <c r="B88" s="10">
         <v>0.82</v>
       </c>
-      <c r="C88" s="9">
+      <c r="C88" s="10">
         <f t="shared" si="6"/>
         <v>0.50391438206641781</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="10">
         <f t="shared" si="7"/>
         <v>0.76822892094179585</v>
       </c>
-      <c r="E88" s="9">
+      <c r="E88" s="10">
         <f t="shared" si="8"/>
         <v>0.85954460538157429</v>
       </c>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
-      <c r="K88" s="1"/>
-    </row>
-    <row r="89" spans="1:11" ht="31" customHeight="1">
-      <c r="A89" s="1"/>
-      <c r="B89" s="12">
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="2"/>
+    </row>
+    <row r="89" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A89" s="2"/>
+      <c r="B89" s="13">
         <v>0.83</v>
       </c>
-      <c r="C89" s="12">
+      <c r="C89" s="13">
         <f t="shared" si="6"/>
         <v>0.51858114765802221</v>
       </c>
-      <c r="D89" s="12">
+      <c r="D89" s="13">
         <f t="shared" si="7"/>
         <v>0.7801860010012226</v>
       </c>
-      <c r="E89" s="12">
+      <c r="E89" s="13">
         <f t="shared" si="8"/>
         <v>0.86765928365838596</v>
       </c>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1"/>
-      <c r="K89" s="1"/>
-    </row>
-    <row r="90" spans="1:11" ht="31" customHeight="1">
-      <c r="A90" s="1"/>
-      <c r="B90" s="9">
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+    </row>
+    <row r="90" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A90" s="2"/>
+      <c r="B90" s="10">
         <v>0.84</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C90" s="10">
         <f t="shared" si="6"/>
         <v>0.5339220716420624</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="10">
         <f t="shared" si="7"/>
         <v>0.7922392712273485</v>
       </c>
-      <c r="E90" s="9">
+      <c r="E90" s="10">
         <f t="shared" si="8"/>
         <v>0.87573518965405928</v>
       </c>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
-      <c r="K90" s="1"/>
-    </row>
-    <row r="91" spans="1:11" ht="31" customHeight="1">
-      <c r="A91" s="1"/>
-      <c r="B91" s="12">
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+    </row>
+    <row r="91" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A91" s="2"/>
+      <c r="B91" s="13">
         <v>0.85</v>
       </c>
-      <c r="C91" s="12">
+      <c r="C91" s="13">
         <f t="shared" si="6"/>
         <v>0.5500021279603855</v>
       </c>
-      <c r="D91" s="12">
+      <c r="D91" s="13">
         <f t="shared" si="7"/>
         <v>0.80439070848982852</v>
       </c>
-      <c r="E91" s="12">
+      <c r="E91" s="13">
         <f t="shared" si="8"/>
         <v>0.88377274366742875</v>
       </c>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
-    </row>
-    <row r="92" spans="1:11" ht="31" customHeight="1">
-      <c r="A92" s="1"/>
-      <c r="B92" s="9">
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
+    </row>
+    <row r="92" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A92" s="2"/>
+      <c r="B92" s="10">
         <v>0.86</v>
       </c>
-      <c r="C92" s="9">
+      <c r="C92" s="10">
         <f t="shared" si="6"/>
         <v>0.56689616129346987</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D92" s="10">
         <f t="shared" si="7"/>
         <v>0.81664235123359474</v>
       </c>
-      <c r="E92" s="9">
+      <c r="E92" s="10">
         <f t="shared" si="8"/>
         <v>0.89177235919997588</v>
       </c>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
-      <c r="K92" s="1"/>
-    </row>
-    <row r="93" spans="1:11" ht="31" customHeight="1">
-      <c r="A93" s="1"/>
-      <c r="B93" s="12">
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+    </row>
+    <row r="93" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A93" s="2"/>
+      <c r="B93" s="13">
         <v>0.87</v>
       </c>
-      <c r="C93" s="12">
+      <c r="C93" s="13">
         <f t="shared" si="6"/>
         <v>0.58469099360378995</v>
       </c>
-      <c r="D93" s="12">
+      <c r="D93" s="13">
         <f t="shared" si="7"/>
         <v>0.82899630206296215</v>
       </c>
-      <c r="E93" s="12">
+      <c r="E93" s="13">
         <f t="shared" si="8"/>
         <v>0.89973444310162098</v>
       </c>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1"/>
-      <c r="K93" s="1"/>
-    </row>
-    <row r="94" spans="1:11" ht="31" customHeight="1">
-      <c r="A94" s="1"/>
-      <c r="B94" s="9">
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+    </row>
+    <row r="94" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A94" s="2"/>
+      <c r="B94" s="10">
         <v>0.88</v>
       </c>
-      <c r="C94" s="9">
+      <c r="C94" s="10">
         <f t="shared" si="6"/>
         <v>0.60348812446218625</v>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="10">
         <f t="shared" si="7"/>
         <v>0.84145473046272989</v>
       </c>
-      <c r="E94" s="9">
+      <c r="E94" s="10">
         <f t="shared" si="8"/>
         <v>0.90765939571262133</v>
       </c>
-      <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1"/>
-      <c r="K94" s="1"/>
-    </row>
-    <row r="95" spans="1:11" ht="31" customHeight="1">
-      <c r="A95" s="1"/>
-      <c r="B95" s="12">
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
+    </row>
+    <row r="95" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A95" s="2"/>
+      <c r="B95" s="13">
         <v>0.89</v>
       </c>
-      <c r="C95" s="12">
+      <c r="C95" s="13">
         <f t="shared" si="6"/>
         <v>0.6234072380669563</v>
       </c>
-      <c r="D95" s="12">
+      <c r="D95" s="13">
         <f t="shared" si="7"/>
         <v>0.85401987566508752</v>
       </c>
-      <c r="E95" s="12">
+      <c r="E95" s="13">
         <f t="shared" si="8"/>
         <v>0.91554761100171322</v>
       </c>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
-      <c r="K95" s="1"/>
-    </row>
-    <row r="96" spans="1:11" ht="31" customHeight="1">
-      <c r="A96" s="1"/>
-      <c r="B96" s="9">
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+    </row>
+    <row r="96" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A96" s="2"/>
+      <c r="B96" s="10">
         <v>0.9</v>
       </c>
-      <c r="C96" s="9">
+      <c r="C96" s="10">
         <f t="shared" si="6"/>
         <v>0.64459082462355466</v>
       </c>
-      <c r="D96" s="9">
+      <c r="D96" s="10">
         <f t="shared" si="7"/>
         <v>0.86669404967180197</v>
       </c>
-      <c r="E96" s="9">
+      <c r="E96" s="10">
         <f t="shared" si="8"/>
         <v>0.92339947670060074</v>
       </c>
-      <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
-      <c r="K96" s="1"/>
-    </row>
-    <row r="97" spans="1:11" ht="31" customHeight="1">
-      <c r="A97" s="1"/>
-      <c r="B97" s="12">
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+    </row>
+    <row r="97" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A97" s="2"/>
+      <c r="B97" s="13">
         <v>0.91</v>
       </c>
-      <c r="C97" s="12">
+      <c r="C97" s="13">
         <f t="shared" si="6"/>
         <v>0.66721037000116235</v>
       </c>
-      <c r="D97" s="12">
+      <c r="D97" s="13">
         <f t="shared" si="7"/>
         <v>0.87947964044189242</v>
       </c>
-      <c r="E97" s="12">
+      <c r="E97" s="13">
         <f t="shared" si="8"/>
         <v>0.93121537443492164</v>
       </c>
-      <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="1"/>
-      <c r="K97" s="1"/>
-    </row>
-    <row r="98" spans="1:11" ht="31" customHeight="1">
-      <c r="A98" s="1"/>
-      <c r="B98" s="9">
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
+    </row>
+    <row r="98" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A98" s="2"/>
+      <c r="B98" s="10">
         <v>0.92</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C98" s="10">
         <f t="shared" si="6"/>
         <v>0.69147479910585075</v>
       </c>
-      <c r="D98" s="9">
+      <c r="D98" s="10">
         <f t="shared" si="7"/>
         <v>0.89237911525578284</v>
       </c>
-      <c r="E98" s="9">
+      <c r="E98" s="10">
         <f t="shared" si="8"/>
         <v>0.93899567985178833</v>
       </c>
-      <c r="F98" s="1"/>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="1"/>
-      <c r="K98" s="1"/>
-    </row>
-    <row r="99" spans="1:11" ht="31" customHeight="1">
-      <c r="A99" s="1"/>
-      <c r="B99" s="12">
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
+    </row>
+    <row r="99" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A99" s="2"/>
+      <c r="B99" s="13">
         <v>0.93</v>
       </c>
-      <c r="C99" s="12">
+      <c r="C99" s="13">
         <f t="shared" si="6"/>
         <v>0.71764223557463891</v>
       </c>
-      <c r="D99" s="12">
+      <c r="D99" s="13">
         <f t="shared" si="7"/>
         <v>0.90539502426779028</v>
       </c>
-      <c r="E99" s="12">
+      <c r="E99" s="13">
         <f t="shared" si="8"/>
         <v>0.9467407627440203</v>
       </c>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1"/>
-      <c r="K99" s="1"/>
-    </row>
-    <row r="100" spans="1:11" ht="31" customHeight="1">
-      <c r="A100" s="1"/>
-      <c r="B100" s="9">
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2"/>
+    </row>
+    <row r="100" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A100" s="2"/>
+      <c r="B100" s="10">
         <v>0.94</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C100" s="10">
         <f t="shared" si="6"/>
         <v>0.74603677513171862</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D100" s="10">
         <f t="shared" si="7"/>
         <v>0.91853000425974562</v>
       </c>
-      <c r="E100" s="9">
+      <c r="E100" s="10">
         <f t="shared" si="8"/>
         <v>0.95445098717116272</v>
       </c>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1"/>
-      <c r="K100" s="1"/>
-    </row>
-    <row r="101" spans="1:11" ht="31" customHeight="1">
-      <c r="A101" s="1"/>
-      <c r="B101" s="12">
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+    </row>
+    <row r="101" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A101" s="2"/>
+      <c r="B101" s="13">
         <v>0.95</v>
       </c>
-      <c r="C101" s="12">
+      <c r="C101" s="13">
         <f t="shared" si="6"/>
         <v>0.77707307876902676</v>
       </c>
-      <c r="D101" s="12">
+      <c r="D101" s="13">
         <f t="shared" si="7"/>
         <v>0.93178678260956671</v>
       </c>
-      <c r="E101" s="12">
+      <c r="E101" s="13">
         <f t="shared" si="8"/>
         <v>0.96212671157739738</v>
       </c>
-      <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1"/>
-      <c r="K101" s="1"/>
-    </row>
-    <row r="102" spans="1:11" ht="31" customHeight="1">
-      <c r="A102" s="1"/>
-      <c r="B102" s="9">
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
+    </row>
+    <row r="102" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A102" s="2"/>
+      <c r="B102" s="10">
         <v>0.96</v>
       </c>
-      <c r="C102" s="9">
+      <c r="C102" s="10">
         <f t="shared" si="6"/>
         <v>0.8112936145727736</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="10">
         <f t="shared" si="7"/>
         <v>0.94516818148972548</v>
       </c>
-      <c r="E102" s="9">
+      <c r="E102" s="10">
         <f t="shared" si="8"/>
         <v>0.96976828890643507</v>
       </c>
-      <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
-      <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="1"/>
-      <c r="K102" s="1"/>
-    </row>
-    <row r="103" spans="1:11" ht="31" customHeight="1">
-      <c r="A103" s="1"/>
-      <c r="B103" s="12">
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
+    </row>
+    <row r="103" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A103" s="2"/>
+      <c r="B103" s="13">
         <v>0.97</v>
       </c>
-      <c r="C103" s="12">
+      <c r="C103" s="13">
         <f t="shared" si="6"/>
         <v>0.84942725912383288</v>
       </c>
-      <c r="D103" s="12">
+      <c r="D103" s="13">
         <f t="shared" si="7"/>
         <v>0.95867712231178137</v>
       </c>
-      <c r="E103" s="12">
+      <c r="E103" s="13">
         <f t="shared" si="8"/>
         <v>0.97737606671348642</v>
       </c>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1"/>
-      <c r="K103" s="1"/>
-    </row>
-    <row r="104" spans="1:11" ht="31" customHeight="1">
-      <c r="A104" s="1"/>
-      <c r="B104" s="9">
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+    </row>
+    <row r="104" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A104" s="2"/>
+      <c r="B104" s="10">
         <v>0.98</v>
       </c>
-      <c r="C104" s="9">
+      <c r="C104" s="10">
         <f t="shared" si="6"/>
         <v>0.8924858866687011</v>
       </c>
-      <c r="D104" s="9">
+      <c r="D104" s="10">
         <f t="shared" si="7"/>
         <v>0.97231663043448913</v>
       </c>
-      <c r="E104" s="9">
+      <c r="E104" s="10">
         <f t="shared" si="8"/>
         <v>0.98495038727439643</v>
       </c>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1"/>
-      <c r="K104" s="1"/>
-    </row>
-    <row r="105" spans="1:11" ht="31" customHeight="1">
-      <c r="A105" s="1"/>
-      <c r="B105" s="12">
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+    </row>
+    <row r="105" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A105" s="2"/>
+      <c r="B105" s="13">
         <v>0.99</v>
       </c>
-      <c r="C105" s="12">
+      <c r="C105" s="13">
         <f t="shared" si="6"/>
         <v>0.94193295954412271</v>
       </c>
-      <c r="D105" s="12">
+      <c r="D105" s="13">
         <f t="shared" si="7"/>
         <v>0.98608984015446355</v>
       </c>
-      <c r="E105" s="12">
+      <c r="E105" s="13">
         <f t="shared" si="8"/>
         <v>0.99249158769203172</v>
       </c>
-      <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
-      <c r="J105" s="1"/>
-      <c r="K105" s="1"/>
-    </row>
-    <row r="106" spans="1:11" ht="31" customHeight="1">
-      <c r="A106" s="1"/>
-      <c r="B106" s="9">
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
+    </row>
+    <row r="106" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A106" s="2"/>
+      <c r="B106" s="10">
         <v>1</v>
       </c>
-      <c r="C106" s="9">
+      <c r="C106" s="10">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D106" s="9">
+      <c r="D106" s="10">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="E106" s="9">
+      <c r="E106" s="10">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="1"/>
-      <c r="K106" s="1"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="H4:K4"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/throttle_curve.xlsx
+++ b/docs/throttle_curve.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\xlsx-locale-20261027\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABA224D-6D44-4BC5-AC19-4D847F13A550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F1388E-3FA3-476A-A59E-E86EF9A176BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Throttle Curves" sheetId="1" r:id="rId1"/>
     <sheet name="Parameters" sheetId="2" r:id="rId2"/>
-    <sheet name="Samples" sheetId="3" r:id="rId3"/>
+    <sheet name="Locale" sheetId="4" state="hidden" r:id="rId3"/>
+    <sheet name="Samples" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
   <si>
     <t>Astral · Throttle curves</t>
   </si>
@@ -90,6 +91,116 @@
   <si>
     <t>档位</t>
   </si>
+  <si>
+    <t>Language / 语言</t>
+  </si>
+  <si>
+    <t>简体中文</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>en-US</t>
+  </si>
+  <si>
+    <t>zh-CN</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>chart.throttleInputOutput</t>
+  </si>
+  <si>
+    <t>Throttle input / output</t>
+  </si>
+  <si>
+    <t>油门输入 / 输出</t>
+  </si>
+  <si>
+    <t>label.aggressiveMap</t>
+  </si>
+  <si>
+    <t>3 · 激进</t>
+  </si>
+  <si>
+    <t>label.mapSetting</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>label.parameterRow</t>
+  </si>
+  <si>
+    <t>Parameter row</t>
+  </si>
+  <si>
+    <t>label.progressiveMap</t>
+  </si>
+  <si>
+    <t>1 · 渐进</t>
+  </si>
+  <si>
+    <t>label.selectedEcu</t>
+  </si>
+  <si>
+    <t>Selected ECU</t>
+  </si>
+  <si>
+    <t>label.subtleLinearMap</t>
+  </si>
+  <si>
+    <t>2 · 轻度线性</t>
+  </si>
+  <si>
+    <t>label.throttleInput</t>
+  </si>
+  <si>
+    <t>油门输入</t>
+  </si>
+  <si>
+    <t>label.throttleOutput</t>
+  </si>
+  <si>
+    <t>Throttle output</t>
+  </si>
+  <si>
+    <t>油门输出</t>
+  </si>
+  <si>
+    <t>label.vehicleEcu</t>
+  </si>
+  <si>
+    <t>Vehicle / ECU</t>
+  </si>
+  <si>
+    <t>title.throttleCurves</t>
+  </si>
+  <si>
+    <t>Astral · 油门曲线</t>
+  </si>
+  <si>
+    <t>title.throttleParameters</t>
+  </si>
+  <si>
+    <t>Astral · 油门参数</t>
+  </si>
+  <si>
+    <t>title.throttleSamples</t>
+  </si>
+  <si>
+    <t>Astral · 油门采样</t>
+  </si>
+  <si>
+    <t>WRC17 / Rally1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>简体中文</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -98,7 +209,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -251,8 +362,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,8 +488,21 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -489,15 +626,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -549,6 +690,11 @@
     <xf numFmtId="2" fontId="23" fillId="22" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -556,6 +702,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -566,7 +718,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -584,28 +736,37 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>Throttle input / output</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$2</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>油门输入 / 输出</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -622,7 +783,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1 · Progressive</c:v>
+                  <c:v>1 · 渐进</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1278,7 +1439,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2 · Subtle Linear</c:v>
+                  <c:v>2 · 轻度线性</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1934,7 +2095,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>3 · Aggressive</c:v>
+                  <c:v>3 · 激进</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2613,22 +2774,31 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Throttle output</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>油门输出</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0%" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -2641,7 +2811,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -2664,22 +2834,31 @@
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Throttle input</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>油门输入</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0%" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -2699,7 +2878,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -2722,7 +2901,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="微软雅黑"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -2745,7 +2924,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -2980,711 +3159,733 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB206089-FBD2-467B-8F4B-31CF7045B0EC}">
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="12" customHeight="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-    </row>
-    <row r="2" spans="1:15" ht="35.1" customHeight="1">
-      <c r="A2" s="2"/>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="2"/>
-    </row>
-    <row r="3" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-    </row>
-    <row r="6" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-    </row>
-    <row r="13" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-    </row>
-    <row r="15" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-    </row>
-    <row r="21" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-    </row>
-    <row r="22" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-    </row>
-    <row r="23" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-    </row>
-    <row r="24" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-    </row>
-    <row r="25" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-    </row>
-    <row r="26" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-    </row>
-    <row r="27" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-    </row>
-    <row r="28" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-    </row>
-    <row r="29" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-    </row>
-    <row r="30" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-    </row>
-    <row r="31" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-    </row>
-    <row r="32" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-    </row>
-    <row r="33" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-    </row>
-    <row r="34" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-    </row>
-    <row r="35" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-    </row>
-    <row r="36" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-    </row>
-    <row r="37" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-    </row>
-    <row r="38" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-    </row>
-    <row r="40" spans="1:15" ht="23.1" customHeight="1">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+    <row r="1" spans="1:15" ht="22" customHeight="1">
+      <c r="A1" s="1"/>
+      <c r="B1" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" spans="1:15" ht="35.15" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="20" t="str">
+        <f>VLOOKUP("title.throttleCurves",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>Astral · 油门曲线</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="1"/>
+    </row>
+    <row r="3" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+    </row>
+    <row r="4" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A4" s="1"/>
+      <c r="B4" s="2" t="str">
+        <f>VLOOKUP("label.vehicleEcu",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>车型 / ECU</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+    </row>
+    <row r="8" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+    </row>
+    <row r="9" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+    </row>
+    <row r="10" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+    </row>
+    <row r="14" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+    </row>
+    <row r="15" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+    </row>
+    <row r="16" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+    </row>
+    <row r="17" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+    </row>
+    <row r="18" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+    </row>
+    <row r="19" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+    </row>
+    <row r="20" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+    </row>
+    <row r="21" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+    </row>
+    <row r="22" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+    </row>
+    <row r="23" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+    </row>
+    <row r="24" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+    </row>
+    <row r="33" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="1:15" ht="23.15" customHeight="1">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="C4:E4"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="E1:G1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"English,简体中文"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -3701,12 +3902,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1D4258-7AC3-4B90-84C1-21E361C79A19}">
   <sheetPr>
     <tabColor rgb="FFC49A32"/>
   </sheetPr>
   <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -3716,330 +3917,335 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="12" customHeight="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" spans="1:14" ht="35.1" customHeight="1">
-      <c r="A2" s="2"/>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-    </row>
-    <row r="3" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" ht="32.1" customHeight="1">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" spans="1:14" ht="32.1" customHeight="1">
-      <c r="A6" s="2"/>
-      <c r="B6" s="4" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="35.15" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="20" t="str">
+        <f>VLOOKUP("title.throttleParameters",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>Astral · 油门参数</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+    </row>
+    <row r="3" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" ht="32.15" customHeight="1">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="26" t="str">
+        <f>VLOOKUP("label.progressiveMap",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>1 · 渐进</v>
+      </c>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26" t="str">
+        <f>VLOOKUP("label.subtleLinearMap",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>2 · 轻度线性</v>
+      </c>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="str">
+        <f>VLOOKUP("label.aggressiveMap",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>3 · 激进</v>
+      </c>
+      <c r="H5" s="26"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" ht="32.15" customHeight="1">
+      <c r="A6" s="1"/>
+      <c r="B6" s="3" t="str">
+        <f>VLOOKUP("label.vehicleEcu",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>车型 / ECU</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" ht="31" customHeight="1">
+      <c r="A7" s="1"/>
+      <c r="B7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-0.92</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="6">
+        <v>-0.45</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" ht="31" customHeight="1">
+      <c r="A8" s="1"/>
+      <c r="B8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-0.95</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="6">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="H8" s="6">
         <v>1</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:14" ht="30.95" customHeight="1">
-      <c r="A7" s="2"/>
-      <c r="B7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" ht="31" customHeight="1">
+      <c r="A9" s="1"/>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="6">
         <v>0</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D9" s="6">
         <v>-0.92</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E9" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="F9" s="6">
         <v>-0.45</v>
       </c>
-      <c r="G7" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="H7" s="7">
+      <c r="G9" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="6">
         <v>1.5</v>
       </c>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" ht="30.95" customHeight="1">
-      <c r="A8" s="2"/>
-      <c r="B8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-0.95</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="F8" s="7">
-        <v>-0.55000000000000004</v>
-      </c>
-      <c r="G8" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="H8" s="7">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:14" ht="30.95" customHeight="1">
-      <c r="A9" s="2"/>
-      <c r="B9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="7">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-0.92</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.4</v>
-      </c>
-      <c r="F9" s="7">
-        <v>-0.45</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="H9" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:14" ht="30.95" customHeight="1">
-      <c r="A10" s="2"/>
-      <c r="B10" s="8" t="s">
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" ht="31" customHeight="1">
+      <c r="A10" s="1"/>
+      <c r="B10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>0.15</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>-0.88</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>0.69</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="6">
         <v>0.59</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:14" ht="30.95" customHeight="1">
-      <c r="A11" s="2"/>
-      <c r="B11" s="6" t="s">
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" ht="31" customHeight="1">
+      <c r="A11" s="1"/>
+      <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>0.15</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>-0.88</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>0.69</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>0.59</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A15" s="2"/>
-    </row>
-    <row r="16" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A16" s="2"/>
-    </row>
-    <row r="17" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A17" s="2"/>
-    </row>
-    <row r="18" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A18" s="2"/>
-    </row>
-    <row r="19" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A20" s="2"/>
-    </row>
-    <row r="21" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-    </row>
-    <row r="22" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-    </row>
-    <row r="23" spans="1:14" ht="23.1" customHeight="1">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="1:14" ht="23.15" customHeight="1">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4059,16 +4265,237 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ED5CD8A-80FA-4CD3-9EF5-D92DD92FF1E9}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="18" t="str">
+        <f>IF('Throttle Curves'!$E$1="English",B2,C2)</f>
+        <v>油门输入 / 输出</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="18" t="str">
+        <f>IF('Throttle Curves'!$E$1="English",B3,C3)</f>
+        <v>3 · 激进</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="18" t="str">
+        <f>IF('Throttle Curves'!$E$1="English",B4,C4)</f>
+        <v>档位</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="18" t="str">
+        <f>IF('Throttle Curves'!$E$1="English",B5,C5)</f>
+        <v>参数行</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="18" t="str">
+        <f>IF('Throttle Curves'!$E$1="English",B6,C6)</f>
+        <v>1 · 渐进</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="18" t="str">
+        <f>IF('Throttle Curves'!$E$1="English",B7,C7)</f>
+        <v>所选 ECU</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="18" t="str">
+        <f>IF('Throttle Curves'!$E$1="English",B8,C8)</f>
+        <v>2 · 轻度线性</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="18" t="str">
+        <f>IF('Throttle Curves'!$E$1="English",B9,C9)</f>
+        <v>油门输入</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="18" t="str">
+        <f>IF('Throttle Curves'!$E$1="English",B10,C10)</f>
+        <v>油门输出</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="18" t="str">
+        <f>IF('Throttle Curves'!$E$1="English",B11,C11)</f>
+        <v>车型 / ECU</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="18" t="str">
+        <f>IF('Throttle Curves'!$E$1="English",B12,C12)</f>
+        <v>Astral · 油门曲线</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="18" t="str">
+        <f>IF('Throttle Curves'!$E$1="English",B13,C13)</f>
+        <v>Astral · 油门参数</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="18" t="str">
+        <f>IF('Throttle Curves'!$E$1="English",B14,C14)</f>
+        <v>Astral · 油门采样</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2B2F7F4-3824-4480-BC2C-FC1B217FF633}">
   <sheetPr>
     <tabColor rgb="FF93A0AC"/>
   </sheetPr>
   <dimension ref="A1:K106"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="5" width="20" customWidth="1"/>
@@ -4078,2543 +4505,2551 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="12" customHeight="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-    </row>
-    <row r="2" spans="1:11" ht="35.1" customHeight="1">
-      <c r="A2" s="2"/>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" spans="1:11" ht="23.1" customHeight="1">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" spans="1:11" ht="23.1" customHeight="1">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="23" t="str">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="35.15" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="20" t="str">
+        <f>VLOOKUP("title.throttleSamples",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>Astral · 油门采样</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+    </row>
+    <row r="3" spans="1:11" ht="23.15" customHeight="1">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" ht="23.15" customHeight="1">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="2" t="str">
+        <f>VLOOKUP("label.selectedEcu",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>所选 ECU</v>
+      </c>
+      <c r="H4" s="27" t="str">
         <f>'Throttle Curves'!C4</f>
         <v>WRC17 / Rally1</v>
       </c>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-    </row>
-    <row r="5" spans="1:11" ht="32.1" customHeight="1">
-      <c r="A5" s="2"/>
-      <c r="B5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A6" s="2"/>
-      <c r="B6" s="10">
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+    </row>
+    <row r="5" spans="1:11" ht="32.15" customHeight="1">
+      <c r="A5" s="1"/>
+      <c r="B5" s="8" t="str">
+        <f>VLOOKUP("label.throttleInput",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>油门输入</v>
+      </c>
+      <c r="C5" s="8" t="str">
+        <f>VLOOKUP("label.progressiveMap",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>1 · 渐进</v>
+      </c>
+      <c r="D5" s="8" t="str">
+        <f>VLOOKUP("label.subtleLinearMap",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>2 · 轻度线性</v>
+      </c>
+      <c r="E5" s="8" t="str">
+        <f>VLOOKUP("label.aggressiveMap",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>3 · 激进</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" ht="31" customHeight="1">
+      <c r="A6" s="1"/>
+      <c r="B6" s="9">
         <v>0</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <f t="shared" ref="C6:C37" si="0">IF($I$9=0,$B6,(1-$H$9)*LN(1+$I$9*$B6)/LN(1+$I$9)+$H$9*$B6)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <f t="shared" ref="D6:D37" si="1">IF($I$10=0,$B6,(1-$H$10)*LN(1+$I$10*$B6)/LN(1+$I$10)+$H$10*$B6)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <f t="shared" ref="E6:E37" si="2">IF($I$11=0,$B6,(1-$H$11)*LN(1+$I$11*$B6)/LN(1+$I$11)+$H$11*$B6)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="12">
+      <c r="F6" s="1"/>
+      <c r="G6" s="10" t="str">
+        <f>VLOOKUP("label.parameterRow",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>参数行</v>
+      </c>
+      <c r="H6" s="11">
         <f>MATCH('Throttle Curves'!C4,Parameters!B7:B11,0)</f>
         <v>2</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A7" s="2"/>
-      <c r="B7" s="13">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="31" customHeight="1">
+      <c r="A7" s="1"/>
+      <c r="B7" s="12">
         <v>0.01</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="12">
         <f t="shared" si="0"/>
         <v>3.186337086193345E-3</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <f t="shared" si="1"/>
         <v>7.6801448322603195E-3</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <f t="shared" si="2"/>
         <v>1.391976367936305E-2</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" ht="32.1" customHeight="1">
-      <c r="A8" s="2"/>
-      <c r="B8" s="10">
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="32.15" customHeight="1">
+      <c r="A8" s="1"/>
+      <c r="B8" s="9">
         <v>0.02</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <f t="shared" si="0"/>
         <v>6.4033824337768443E-3</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <f t="shared" si="1"/>
         <v>1.5389017612306488E-2</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <f t="shared" si="2"/>
         <v>2.7712236977093824E-2</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="9" t="s">
+      <c r="F8" s="1"/>
+      <c r="G8" s="13" t="str">
+        <f>VLOOKUP("label.mapSetting",Locale!$A$2:$D$14,4,FALSE)</f>
+        <v>档位</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A9" s="2"/>
-      <c r="B9" s="13">
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="31" customHeight="1">
+      <c r="A9" s="1"/>
+      <c r="B9" s="12">
         <v>0.03</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="12">
         <f t="shared" si="0"/>
         <v>9.6517337079458313E-3</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <f t="shared" si="1"/>
         <v>2.3126938755721561E-2</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <f t="shared" si="2"/>
         <v>4.1379903667644352E-2</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="15">
+      <c r="F9" s="1"/>
+      <c r="G9" s="14">
         <v>1</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="15">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,1)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="15">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,2)</f>
         <v>-0.95</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A10" s="2"/>
-      <c r="B10" s="10">
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="31" customHeight="1">
+      <c r="A10" s="1"/>
+      <c r="B10" s="9">
         <v>0.04</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <f t="shared" si="0"/>
         <v>1.2932006193754548E-2</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <f t="shared" si="1"/>
         <v>3.0894234068771745E-2</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <f t="shared" si="2"/>
         <v>5.4925175529730766E-2</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="17">
+      <c r="F10" s="1"/>
+      <c r="G10" s="16">
         <v>2</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="17">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,3)</f>
         <v>0.25</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="17">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,4)</f>
         <v>-0.55000000000000004</v>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A11" s="2"/>
-      <c r="B11" s="13">
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="31" customHeight="1">
+      <c r="A11" s="1"/>
+      <c r="B11" s="12">
         <v>0.05</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="12">
         <f t="shared" si="0"/>
         <v>1.6244833495600405E-2</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <f t="shared" si="1"/>
         <v>3.8691234870011873E-2</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <f t="shared" si="2"/>
         <v>6.835039510225821E-2</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="15">
+      <c r="F11" s="1"/>
+      <c r="G11" s="14">
         <v>3</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="15">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,5)</f>
         <v>0.1</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="15">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,6)</f>
         <v>1</v>
       </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A12" s="2"/>
-      <c r="B12" s="10">
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="31" customHeight="1">
+      <c r="A12" s="1"/>
+      <c r="B12" s="9">
         <v>0.06</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <f t="shared" si="0"/>
         <v>1.9590868271767738E-2</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <f t="shared" si="1"/>
         <v>4.6518278115341136E-2</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <f t="shared" si="2"/>
         <v>8.1657838309627112E-2</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A13" s="2"/>
-      <c r="B13" s="13">
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="31" customHeight="1">
+      <c r="A13" s="1"/>
+      <c r="B13" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="12">
         <f t="shared" si="0"/>
         <v>2.2970783006160234E-2</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <f t="shared" si="1"/>
         <v>5.437570652662372E-2</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <f t="shared" si="2"/>
         <v>9.4849716963780112E-2</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A14" s="2"/>
-      <c r="B14" s="10">
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="31" customHeight="1">
+      <c r="A14" s="1"/>
+      <c r="B14" s="9">
         <v>0.08</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <f t="shared" si="0"/>
         <v>2.6385270819504796E-2</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <f t="shared" si="1"/>
         <v>6.2263868724000346E-2</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <f t="shared" si="2"/>
         <v>0.10792818114986957</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A15" s="2"/>
-      <c r="B15" s="13">
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" ht="31" customHeight="1">
+      <c r="A15" s="1"/>
+      <c r="B15" s="12">
         <v>0.09</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="12">
         <f t="shared" si="0"/>
         <v>2.9835046322475019E-2</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="12">
         <f t="shared" si="1"/>
         <v>7.0183119362015323E-2</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <f t="shared" si="2"/>
         <v>0.12089532150198161</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A16" s="2"/>
-      <c r="B16" s="10">
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" ht="31" customHeight="1">
+      <c r="A16" s="1"/>
+      <c r="B16" s="9">
         <v>0.1</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <f t="shared" si="0"/>
         <v>3.33208465133598E-2</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <f t="shared" si="1"/>
         <v>7.8133819269695204E-2</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <f t="shared" si="2"/>
         <v>0.13375317137494153</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A17" s="2"/>
-      <c r="B17" s="13">
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" ht="31" customHeight="1">
+      <c r="A17" s="1"/>
+      <c r="B17" s="12">
         <v>0.11</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="12">
         <f t="shared" si="0"/>
         <v>3.6843431723099021E-2</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="12">
         <f t="shared" si="1"/>
         <v>8.6116335594713919E-2</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="12">
         <f t="shared" si="2"/>
         <v>0.14650370891784326</v>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A18" s="2"/>
-      <c r="B18" s="10">
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" ht="31" customHeight="1">
+      <c r="A18" s="1"/>
+      <c r="B18" s="9">
         <v>0.12</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <f t="shared" si="0"/>
         <v>4.0403586610716101E-2</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <f t="shared" si="1"/>
         <v>9.4131041951792213E-2</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <f t="shared" si="2"/>
         <v>0.15914885905459161</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A19" s="2"/>
-      <c r="B19" s="13">
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" ht="31" customHeight="1">
+      <c r="A19" s="1"/>
+      <c r="B19" s="12">
         <v>0.13</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="12">
         <f t="shared" si="0"/>
         <v>4.4002121212408853E-2</v>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="12">
         <f t="shared" si="1"/>
         <v>0.10217831857547742</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="12">
         <f t="shared" si="2"/>
         <v>0.17169049537641662</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A20" s="2"/>
-      <c r="B20" s="10">
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" ht="31" customHeight="1">
+      <c r="A20" s="1"/>
+      <c r="B20" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <f t="shared" si="0"/>
         <v>4.7639872047806051E-2</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <f t="shared" si="1"/>
         <v>0.1102585524774635</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <f t="shared" si="2"/>
         <v>0.18413044195101544</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A21" s="2"/>
-      <c r="B21" s="13">
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" ht="31" customHeight="1">
+      <c r="A21" s="1"/>
+      <c r="B21" s="12">
         <v>0.15</v>
       </c>
-      <c r="C21" s="13">
+      <c r="C21" s="12">
         <f t="shared" si="0"/>
         <v>5.1317703287169718E-2</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="12">
         <f t="shared" si="1"/>
         <v>0.11837213760861129</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="12">
         <f t="shared" si="2"/>
         <v>0.19647047505268539</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A22" s="2"/>
-      <c r="B22" s="10">
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" ht="31" customHeight="1">
+      <c r="A22" s="1"/>
+      <c r="B22" s="9">
         <v>0.16</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <f t="shared" si="0"/>
         <v>5.5036507983617249E-2</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <f t="shared" si="1"/>
         <v>0.1265194750258396</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <f t="shared" si="2"/>
         <v>0.20871232481756263</v>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A23" s="2"/>
-      <c r="B23" s="13">
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" ht="31" customHeight="1">
+      <c r="A23" s="1"/>
+      <c r="B23" s="12">
         <v>0.17</v>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="12">
         <f t="shared" si="0"/>
         <v>5.8797209374757908E-2</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="12">
         <f t="shared" si="1"/>
         <v>0.13470097306406517</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="12">
         <f t="shared" si="2"/>
         <v>0.22085767682781182</v>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A24" s="2"/>
-      <c r="B24" s="10">
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" ht="31" customHeight="1">
+      <c r="A24" s="1"/>
+      <c r="B24" s="9">
         <v>0.18</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="9">
         <f t="shared" si="0"/>
         <v>6.2600762258491024E-2</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="9">
         <f t="shared" si="1"/>
         <v>0.1429170475133727</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="9">
         <f t="shared" si="2"/>
         <v>0.23290817362840482</v>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A25" s="2"/>
-      <c r="B25" s="13">
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" ht="31" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="B25" s="12">
         <v>0.19</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C25" s="12">
         <f t="shared" si="0"/>
         <v>6.6448154448093127E-2</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="12">
         <f t="shared" si="1"/>
         <v>0.15116812180161127</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="12">
         <f t="shared" si="2"/>
         <v>0.24486541617989693</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A26" s="2"/>
-      <c r="B26" s="10">
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" ht="31" customHeight="1">
+      <c r="A26" s="1"/>
+      <c r="B26" s="9">
         <v>0.2</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="9">
         <f t="shared" si="0"/>
         <v>7.0340408312143138E-2</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <f t="shared" si="1"/>
         <v>0.1594546271826133</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="9">
         <f t="shared" si="2"/>
         <v>0.25673096525041444</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A27" s="2"/>
-      <c r="B27" s="13">
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" ht="31" customHeight="1">
+      <c r="A27" s="1"/>
+      <c r="B27" s="12">
         <v>0.21</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="12">
         <f t="shared" si="0"/>
         <v>7.4278582405290297E-2</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="12">
         <f t="shared" si="1"/>
         <v>0.1677770029302495</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="12">
         <f t="shared" si="2"/>
         <v>0.26850634274988283</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A28" s="2"/>
-      <c r="B28" s="10">
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" ht="31" customHeight="1">
+      <c r="A28" s="1"/>
+      <c r="B28" s="9">
         <v>0.22</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="9">
         <f t="shared" si="0"/>
         <v>7.8263773196372607E-2</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="9">
         <f t="shared" si="1"/>
         <v>0.1761356965385342</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="9">
         <f t="shared" si="2"/>
         <v>0.28019303300934545</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A29" s="2"/>
-      <c r="B29" s="13">
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" ht="31" customHeight="1">
+      <c r="A29" s="1"/>
+      <c r="B29" s="12">
         <v>0.23</v>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="12">
         <f t="shared" si="0"/>
         <v>8.2297116900944781E-2</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="12">
         <f t="shared" si="1"/>
         <v>0.18453116392801255</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="12">
         <f t="shared" si="2"/>
         <v>0.29179248400806368</v>
       </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A30" s="2"/>
-      <c r="B30" s="10">
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" spans="1:11" ht="31" customHeight="1">
+      <c r="A30" s="1"/>
+      <c r="B30" s="9">
         <v>0.24</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="9">
         <f t="shared" si="0"/>
         <v>8.6379791425876637E-2</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <f t="shared" si="1"/>
         <v>0.19296386965866436</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="9">
         <f t="shared" si="2"/>
         <v>0.30330610855093548</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A31" s="2"/>
-      <c r="B31" s="13">
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" ht="31" customHeight="1">
+      <c r="A31" s="1"/>
+      <c r="B31" s="12">
         <v>0.25</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="12">
         <f t="shared" si="0"/>
         <v>9.0513018434350292E-2</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="12">
         <f t="shared" si="1"/>
         <v>0.20143428714957642</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="12">
         <f t="shared" si="2"/>
         <v>0.31473528539862616</v>
       </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A32" s="2"/>
-      <c r="B32" s="10">
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" ht="31" customHeight="1">
+      <c r="A32" s="1"/>
+      <c r="B32" s="9">
         <v>0.26</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="9">
         <f t="shared" si="0"/>
         <v>9.469806554031196E-2</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <f t="shared" si="1"/>
         <v>0.20994289890563997</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="9">
         <f t="shared" si="2"/>
         <v>0.32608136035267266</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A33" s="2"/>
-      <c r="B33" s="13">
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+    </row>
+    <row r="33" spans="1:11" ht="31" customHeight="1">
+      <c r="A33" s="1"/>
+      <c r="B33" s="12">
         <v>0.27</v>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="12">
         <f t="shared" si="0"/>
         <v>9.8936248642242236E-2</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="12">
         <f t="shared" si="1"/>
         <v>0.21849019675154671</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="12">
         <f t="shared" si="2"/>
         <v>0.33734564729769712</v>
       </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A34" s="2"/>
-      <c r="B34" s="10">
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+    </row>
+    <row r="34" spans="1:11" ht="31" customHeight="1">
+      <c r="A34" s="1"/>
+      <c r="B34" s="9">
         <v>0.28000000000000003</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="9">
         <f t="shared" si="0"/>
         <v>0.10322893440699456</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="9">
         <f t="shared" si="1"/>
         <v>0.22707668207336662</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="9">
         <f t="shared" si="2"/>
         <v>0.34852942920274782</v>
       </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A35" s="2"/>
-      <c r="B35" s="13">
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+    </row>
+    <row r="35" spans="1:11" ht="31" customHeight="1">
+      <c r="A35" s="1"/>
+      <c r="B35" s="12">
         <v>0.28999999999999998</v>
       </c>
-      <c r="C35" s="13">
+      <c r="C35" s="12">
         <f t="shared" si="0"/>
         <v>0.10757754291543231</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="12">
         <f t="shared" si="1"/>
         <v>0.23570286606800478</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="12">
         <f t="shared" si="2"/>
         <v>0.35963395908367646</v>
       </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A36" s="2"/>
-      <c r="B36" s="10">
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+    </row>
+    <row r="36" spans="1:11" ht="31" customHeight="1">
+      <c r="A36" s="1"/>
+      <c r="B36" s="9">
         <v>0.3</v>
       </c>
-      <c r="C36" s="10">
+      <c r="C36" s="9">
         <f t="shared" si="0"/>
         <v>0.11198355048268077</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="9">
         <f t="shared" si="1"/>
         <v>0.24436927000084591</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="9">
         <f t="shared" si="2"/>
         <v>0.37066046092835692</v>
       </c>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A37" s="2"/>
-      <c r="B37" s="13">
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+    </row>
+    <row r="37" spans="1:11" ht="31" customHeight="1">
+      <c r="A37" s="1"/>
+      <c r="B37" s="12">
         <v>0.31</v>
       </c>
-      <c r="C37" s="13">
+      <c r="C37" s="12">
         <f t="shared" si="0"/>
         <v>0.11644849266700712</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="12">
         <f t="shared" si="1"/>
         <v>0.25307642547191278</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="12">
         <f t="shared" si="2"/>
         <v>0.3816101305864531</v>
       </c>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A38" s="2"/>
-      <c r="B38" s="10">
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+    </row>
+    <row r="38" spans="1:11" ht="31" customHeight="1">
+      <c r="A38" s="1"/>
+      <c r="B38" s="9">
         <v>0.32</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="9">
         <f t="shared" ref="C38:C69" si="3">IF($I$9=0,$B38,(1-$H$9)*LN(1+$I$9*$B38)/LN(1+$I$9)+$H$9*$B38)</f>
         <v>0.12097396748267401</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="9">
         <f t="shared" ref="D38:D69" si="4">IF($I$10=0,$B38,(1-$H$10)*LN(1+$I$10*$B38)/LN(1+$I$10)+$H$10*$B38)</f>
         <v>0.26182487469087928</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="9">
         <f t="shared" ref="E38:E69" si="5">IF($I$11=0,$B38,(1-$H$11)*LN(1+$I$11*$B38)/LN(1+$I$11)+$H$11*$B38)</f>
         <v>0.39248413662535597</v>
       </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A39" s="2"/>
-      <c r="B39" s="13">
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+    </row>
+    <row r="39" spans="1:11" ht="31" customHeight="1">
+      <c r="A39" s="1"/>
+      <c r="B39" s="12">
         <v>0.33</v>
       </c>
-      <c r="C39" s="13">
+      <c r="C39" s="12">
         <f t="shared" si="3"/>
         <v>0.12556163883358859</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="12">
         <f t="shared" si="4"/>
         <v>0.27061517076129021</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="12">
         <f t="shared" si="5"/>
         <v>0.40328362115381855</v>
       </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A40" s="2"/>
-      <c r="B40" s="10">
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+    </row>
+    <row r="40" spans="1:11" ht="31" customHeight="1">
+      <c r="A40" s="1"/>
+      <c r="B40" s="9">
         <v>0.34</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="9">
         <f t="shared" si="3"/>
         <v>0.13021324018620845</v>
       </c>
-      <c r="D40" s="10">
+      <c r="D40" s="9">
         <f t="shared" si="4"/>
         <v>0.27944787797436538</v>
       </c>
-      <c r="E40" s="10">
+      <c r="E40" s="9">
         <f t="shared" si="5"/>
         <v>0.41400970061474307</v>
       </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-    </row>
-    <row r="41" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A41" s="2"/>
-      <c r="B41" s="13">
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+    </row>
+    <row r="41" spans="1:11" ht="31" customHeight="1">
+      <c r="A41" s="1"/>
+      <c r="B41" s="12">
         <v>0.35</v>
       </c>
-      <c r="C41" s="13">
+      <c r="C41" s="12">
         <f t="shared" si="3"/>
         <v>0.13493057850199364</v>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="12">
         <f t="shared" si="4"/>
         <v>0.28832357211277315</v>
       </c>
-      <c r="E41" s="13">
+      <c r="E41" s="12">
         <f t="shared" si="5"/>
         <v>0.42466346654849568</v>
       </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A42" s="2"/>
-      <c r="B42" s="10">
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+    </row>
+    <row r="42" spans="1:11" ht="31" customHeight="1">
+      <c r="A42" s="1"/>
+      <c r="B42" s="9">
         <v>0.36</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="9">
         <f t="shared" si="3"/>
         <v>0.1397155384517296</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="9">
         <f t="shared" si="4"/>
         <v>0.29724284076478735</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="9">
         <f t="shared" si="5"/>
         <v>0.43524598632805317</v>
       </c>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A43" s="2"/>
-      <c r="B43" s="13">
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+    </row>
+    <row r="43" spans="1:11" ht="31" customHeight="1">
+      <c r="A43" s="1"/>
+      <c r="B43" s="12">
         <v>0.37</v>
       </c>
-      <c r="C43" s="13">
+      <c r="C43" s="12">
         <f t="shared" si="3"/>
         <v>0.14457008693631948</v>
       </c>
-      <c r="D43" s="13">
+      <c r="D43" s="12">
         <f t="shared" si="4"/>
         <v>0.3062062836492514</v>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="12">
         <f t="shared" si="5"/>
         <v>0.44575830386722187</v>
       </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-    </row>
-    <row r="44" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A44" s="2"/>
-      <c r="B44" s="10">
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+    </row>
+    <row r="44" spans="1:11" ht="31" customHeight="1">
+      <c r="A44" s="1"/>
+      <c r="B44" s="9">
         <v>0.38</v>
       </c>
-      <c r="C44" s="10">
+      <c r="C44" s="9">
         <f t="shared" si="3"/>
         <v>0.14949627794118397</v>
       </c>
-      <c r="D44" s="10">
+      <c r="D44" s="9">
         <f t="shared" si="4"/>
         <v>0.31521451295180247</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E44" s="9">
         <f t="shared" si="5"/>
         <v>0.45620144030309984</v>
       </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-    </row>
-    <row r="45" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A45" s="2"/>
-      <c r="B45" s="13">
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+    </row>
+    <row r="45" spans="1:11" ht="31" customHeight="1">
+      <c r="A45" s="1"/>
+      <c r="B45" s="12">
         <v>0.39</v>
       </c>
-      <c r="C45" s="13">
+      <c r="C45" s="12">
         <f t="shared" si="3"/>
         <v>0.15449625775425421</v>
       </c>
-      <c r="D45" s="13">
+      <c r="D45" s="12">
         <f t="shared" si="4"/>
         <v>0.32426815367282602</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E45" s="12">
         <f t="shared" si="5"/>
         <v>0.46657639465390466</v>
       </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-    </row>
-    <row r="46" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A46" s="2"/>
-      <c r="B46" s="10">
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+    </row>
+    <row r="46" spans="1:11" ht="31" customHeight="1">
+      <c r="A46" s="1"/>
+      <c r="B46" s="9">
         <v>0.4</v>
       </c>
-      <c r="C46" s="10">
+      <c r="C46" s="9">
         <f t="shared" si="3"/>
         <v>0.1595722705807357</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="9">
         <f t="shared" si="4"/>
         <v>0.33336784398763486</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="9">
         <f t="shared" si="5"/>
         <v>0.47688414445321758</v>
       </c>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-    </row>
-    <row r="47" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A47" s="2"/>
-      <c r="B47" s="13">
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+    </row>
+    <row r="47" spans="1:11" ht="31" customHeight="1">
+      <c r="A47" s="1"/>
+      <c r="B47" s="12">
         <v>0.41</v>
       </c>
-      <c r="C47" s="13">
+      <c r="C47" s="12">
         <f t="shared" si="3"/>
         <v>0.16472666459140581</v>
       </c>
-      <c r="D47" s="13">
+      <c r="D47" s="12">
         <f t="shared" si="4"/>
         <v>0.3425142356193922</v>
       </c>
-      <c r="E47" s="13">
+      <c r="E47" s="12">
         <f t="shared" si="5"/>
         <v>0.48712564636166195</v>
       </c>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-    </row>
-    <row r="48" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A48" s="2"/>
-      <c r="B48" s="10">
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+    </row>
+    <row r="48" spans="1:11" ht="31" customHeight="1">
+      <c r="A48" s="1"/>
+      <c r="B48" s="9">
         <v>0.42</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C48" s="9">
         <f t="shared" si="3"/>
         <v>0.16996189844524612</v>
       </c>
-      <c r="D48" s="10">
+      <c r="D48" s="9">
         <f t="shared" si="4"/>
         <v>0.35170799422532273</v>
       </c>
-      <c r="E48" s="10">
+      <c r="E48" s="9">
         <f t="shared" si="5"/>
         <v>0.4973018367569616</v>
       </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A49" s="2"/>
-      <c r="B49" s="13">
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+    </row>
+    <row r="49" spans="1:11" ht="31" customHeight="1">
+      <c r="A49" s="1"/>
+      <c r="B49" s="12">
         <v>0.43</v>
       </c>
-      <c r="C49" s="13">
+      <c r="C49" s="12">
         <f t="shared" si="3"/>
         <v>0.17528054833176071</v>
       </c>
-      <c r="D49" s="13">
+      <c r="D49" s="12">
         <f t="shared" si="4"/>
         <v>0.36094979979678654</v>
       </c>
-      <c r="E49" s="13">
+      <c r="E49" s="12">
         <f t="shared" si="5"/>
         <v>0.50741363230329817</v>
       </c>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-    </row>
-    <row r="50" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A50" s="2"/>
-      <c r="B50" s="10">
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+    </row>
+    <row r="50" spans="1:11" ht="31" customHeight="1">
+      <c r="A50" s="1"/>
+      <c r="B50" s="9">
         <v>0.44</v>
       </c>
-      <c r="C50" s="10">
+      <c r="C50" s="9">
         <f t="shared" si="3"/>
         <v>0.18068531558347348</v>
       </c>
-      <c r="D50" s="10">
+      <c r="D50" s="9">
         <f t="shared" si="4"/>
         <v>0.37024034707381337</v>
       </c>
-      <c r="E50" s="10">
+      <c r="E50" s="9">
         <f t="shared" si="5"/>
         <v>0.51746193050082889</v>
       </c>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A51" s="2"/>
-      <c r="B51" s="13">
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+    </row>
+    <row r="51" spans="1:11" ht="31" customHeight="1">
+      <c r="A51" s="1"/>
+      <c r="B51" s="12">
         <v>0.45</v>
       </c>
-      <c r="C51" s="13">
+      <c r="C51" s="12">
         <f t="shared" si="3"/>
         <v>0.18617903491491378</v>
       </c>
-      <c r="D51" s="13">
+      <c r="D51" s="12">
         <f t="shared" si="4"/>
         <v>0.37958034597473334</v>
       </c>
-      <c r="E51" s="13">
+      <c r="E51" s="12">
         <f t="shared" si="5"/>
         <v>0.5274476102161888</v>
       </c>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A52" s="2"/>
-      <c r="B52" s="10">
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+    </row>
+    <row r="52" spans="1:11" ht="31" customHeight="1">
+      <c r="A52" s="1"/>
+      <c r="B52" s="9">
         <v>0.46</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C52" s="9">
         <f t="shared" si="3"/>
         <v>0.19176468335099819</v>
       </c>
-      <c r="D52" s="10">
+      <c r="D52" s="9">
         <f t="shared" si="4"/>
         <v>0.38897052204156446</v>
       </c>
-      <c r="E52" s="10">
+      <c r="E52" s="9">
         <f t="shared" si="5"/>
         <v>0.5373715321947633</v>
       </c>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A53" s="2"/>
-      <c r="B53" s="13">
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+    </row>
+    <row r="53" spans="1:11" ht="31" customHeight="1">
+      <c r="A53" s="1"/>
+      <c r="B53" s="12">
         <v>0.47</v>
       </c>
-      <c r="C53" s="13">
+      <c r="C53" s="12">
         <f t="shared" si="3"/>
         <v>0.19744538991520971</v>
       </c>
-      <c r="D53" s="13">
+      <c r="D53" s="12">
         <f t="shared" si="4"/>
         <v>0.39841161690185894</v>
       </c>
-      <c r="E53" s="13">
+      <c r="E53" s="12">
         <f t="shared" si="5"/>
         <v>0.54723453955547574</v>
       </c>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A54" s="2"/>
-      <c r="B54" s="10">
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+    </row>
+    <row r="54" spans="1:11" ht="31" customHeight="1">
+      <c r="A54" s="1"/>
+      <c r="B54" s="9">
         <v>0.48</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="9">
         <f t="shared" si="3"/>
         <v>0.20322444615651072</v>
       </c>
-      <c r="D54" s="10">
+      <c r="D54" s="9">
         <f t="shared" si="4"/>
         <v>0.40790438874774249</v>
       </c>
-      <c r="E54" s="10">
+      <c r="E54" s="9">
         <f t="shared" si="5"/>
         <v>0.55703745826880269</v>
       </c>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-    </row>
-    <row r="55" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A55" s="2"/>
-      <c r="B55" s="13">
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+    </row>
+    <row r="55" spans="1:11" ht="31" customHeight="1">
+      <c r="A55" s="1"/>
+      <c r="B55" s="12">
         <v>0.49</v>
       </c>
-      <c r="C55" s="13">
+      <c r="C55" s="12">
         <f t="shared" si="3"/>
         <v>0.20910531760365855</v>
       </c>
-      <c r="D55" s="13">
+      <c r="D55" s="12">
         <f t="shared" si="4"/>
         <v>0.4174496128329182</v>
       </c>
-      <c r="E55" s="13">
+      <c r="E55" s="12">
         <f t="shared" si="5"/>
         <v>0.56678109761869333</v>
       </c>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-    </row>
-    <row r="56" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A56" s="2"/>
-      <c r="B56" s="10">
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+    </row>
+    <row r="56" spans="1:11" ht="31" customHeight="1">
+      <c r="A56" s="1"/>
+      <c r="B56" s="9">
         <v>0.5</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C56" s="9">
         <f t="shared" si="3"/>
         <v>0.21509165624673118</v>
       </c>
-      <c r="D56" s="10">
+      <c r="D56" s="9">
         <f t="shared" si="4"/>
         <v>0.42704808198845362</v>
       </c>
-      <c r="E56" s="10">
+      <c r="E56" s="9">
         <f t="shared" si="5"/>
         <v>0.57646625064904067</v>
       </c>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A57" s="2"/>
-      <c r="B57" s="13">
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+    </row>
+    <row r="57" spans="1:11" ht="31" customHeight="1">
+      <c r="A57" s="1"/>
+      <c r="B57" s="12">
         <v>0.51</v>
       </c>
-      <c r="C57" s="13">
+      <c r="C57" s="12">
         <f t="shared" si="3"/>
         <v>0.22118731415842602</v>
       </c>
-      <c r="D57" s="13">
+      <c r="D57" s="12">
         <f t="shared" si="4"/>
         <v>0.43670060715820669</v>
       </c>
-      <c r="E57" s="13">
+      <c r="E57" s="12">
         <f t="shared" si="5"/>
         <v>0.5860936945953189</v>
       </c>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
-    </row>
-    <row r="58" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A58" s="2"/>
-      <c r="B58" s="10">
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+    </row>
+    <row r="58" spans="1:11" ht="31" customHeight="1">
+      <c r="A58" s="1"/>
+      <c r="B58" s="9">
         <v>0.52</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="9">
         <f t="shared" si="3"/>
         <v>0.22739635838235542</v>
       </c>
-      <c r="D58" s="10">
+      <c r="D58" s="9">
         <f t="shared" si="4"/>
         <v>0.44640801795479484</v>
       </c>
-      <c r="E58" s="10">
+      <c r="E58" s="9">
         <f t="shared" si="5"/>
         <v>0.59566419130197479</v>
       </c>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A59" s="2"/>
-      <c r="B59" s="13">
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+    </row>
+    <row r="59" spans="1:11" ht="31" customHeight="1">
+      <c r="A59" s="1"/>
+      <c r="B59" s="12">
         <v>0.53</v>
       </c>
-      <c r="C59" s="13">
+      <c r="C59" s="12">
         <f t="shared" si="3"/>
         <v>0.23372308723244489</v>
       </c>
-      <c r="D59" s="13">
+      <c r="D59" s="12">
         <f t="shared" si="4"/>
         <v>0.45617116323706058</v>
       </c>
-      <c r="E59" s="13">
+      <c r="E59" s="12">
         <f t="shared" si="5"/>
         <v>0.60517848762613446</v>
       </c>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A60" s="2"/>
-      <c r="B60" s="10">
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+    </row>
+    <row r="60" spans="1:11" ht="31" customHeight="1">
+      <c r="A60" s="1"/>
+      <c r="B60" s="9">
         <v>0.54</v>
       </c>
-      <c r="C60" s="10">
+      <c r="C60" s="9">
         <f t="shared" si="3"/>
         <v>0.24017204816703402</v>
       </c>
-      <c r="D60" s="10">
+      <c r="D60" s="9">
         <f t="shared" si="4"/>
         <v>0.46599091171004031</v>
       </c>
-      <c r="E60" s="10">
+      <c r="E60" s="9">
         <f t="shared" si="5"/>
         <v>0.61463731582815906</v>
       </c>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A61" s="2"/>
-      <c r="B61" s="13">
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+    </row>
+    <row r="61" spans="1:11" ht="31" customHeight="1">
+      <c r="A61" s="1"/>
+      <c r="B61" s="12">
         <v>0.55000000000000004</v>
       </c>
-      <c r="C61" s="13">
+      <c r="C61" s="12">
         <f t="shared" si="3"/>
         <v>0.24674805742384046</v>
       </c>
-      <c r="D61" s="13">
+      <c r="D61" s="12">
         <f t="shared" si="4"/>
         <v>0.47586815254849502</v>
       </c>
-      <c r="E61" s="13">
+      <c r="E61" s="12">
         <f t="shared" si="5"/>
         <v>0.62404139394956171</v>
       </c>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-    </row>
-    <row r="62" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A62" s="2"/>
-      <c r="B62" s="10">
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+    </row>
+    <row r="62" spans="1:11" ht="31" customHeight="1">
+      <c r="A62" s="1"/>
+      <c r="B62" s="9">
         <v>0.56000000000000005</v>
       </c>
-      <c r="C62" s="10">
+      <c r="C62" s="9">
         <f t="shared" si="3"/>
         <v>0.25345622162814618</v>
       </c>
-      <c r="D62" s="10">
+      <c r="D62" s="9">
         <f t="shared" si="4"/>
         <v>0.48580379604512214</v>
       </c>
-      <c r="E62" s="10">
+      <c r="E62" s="9">
         <f t="shared" si="5"/>
         <v>0.63339142617877142</v>
       </c>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-    </row>
-    <row r="63" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A63" s="2"/>
-      <c r="B63" s="13">
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+    </row>
+    <row r="63" spans="1:11" ht="31" customHeight="1">
+      <c r="A63" s="1"/>
+      <c r="B63" s="12">
         <v>0.56999999999999995</v>
       </c>
-      <c r="C63" s="13">
+      <c r="C63" s="12">
         <f t="shared" si="3"/>
         <v>0.26030196161705293</v>
       </c>
-      <c r="D63" s="13">
+      <c r="D63" s="12">
         <f t="shared" si="4"/>
         <v>0.49579877428463126</v>
       </c>
-      <c r="E63" s="13">
+      <c r="E63" s="12">
         <f t="shared" si="5"/>
         <v>0.64268810320521186</v>
       </c>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-    </row>
-    <row r="64" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A64" s="2"/>
-      <c r="B64" s="10">
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+    </row>
+    <row r="64" spans="1:11" ht="31" customHeight="1">
+      <c r="A64" s="1"/>
+      <c r="B64" s="9">
         <v>0.57999999999999996</v>
       </c>
-      <c r="C64" s="10">
+      <c r="C64" s="9">
         <f t="shared" si="3"/>
         <v>0.26729103875825755</v>
       </c>
-      <c r="D64" s="10">
+      <c r="D64" s="9">
         <f t="shared" si="4"/>
         <v>0.50585404184493254</v>
       </c>
-      <c r="E64" s="10">
+      <c r="E64" s="9">
         <f t="shared" si="5"/>
         <v>0.65193210256214051</v>
       </c>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-    </row>
-    <row r="65" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A65" s="2"/>
-      <c r="B65" s="13">
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+    </row>
+    <row r="65" spans="1:11" ht="31" customHeight="1">
+      <c r="A65" s="1"/>
+      <c r="B65" s="12">
         <v>0.59</v>
       </c>
-      <c r="C65" s="13">
+      <c r="C65" s="12">
         <f t="shared" si="3"/>
         <v>0.27442958408348866</v>
       </c>
-      <c r="D65" s="13">
+      <c r="D65" s="12">
         <f t="shared" si="4"/>
         <v>0.51597057652675415</v>
       </c>
-      <c r="E65" s="13">
+      <c r="E65" s="12">
         <f t="shared" si="5"/>
         <v>0.66112408895866737</v>
       </c>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-    </row>
-    <row r="66" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A66" s="2"/>
-      <c r="B66" s="10">
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+    </row>
+    <row r="66" spans="1:11" ht="31" customHeight="1">
+      <c r="A66" s="1"/>
+      <c r="B66" s="9">
         <v>0.6</v>
       </c>
-      <c r="C66" s="10">
+      <c r="C66" s="9">
         <f t="shared" si="3"/>
         <v>0.28172413060573137</v>
       </c>
-      <c r="D66" s="10">
+      <c r="D66" s="9">
         <f t="shared" si="4"/>
         <v>0.5261493801130871</v>
       </c>
-      <c r="E66" s="10">
+      <c r="E66" s="9">
         <f t="shared" si="5"/>
         <v>0.67026471460137405</v>
       </c>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-    </row>
-    <row r="67" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A67" s="2"/>
-      <c r="B67" s="13">
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+    </row>
+    <row r="67" spans="1:11" ht="31" customHeight="1">
+      <c r="A67" s="1"/>
+      <c r="B67" s="12">
         <v>0.61</v>
       </c>
-      <c r="C67" s="13">
+      <c r="C67" s="12">
         <f t="shared" si="3"/>
         <v>0.28918164924710904</v>
       </c>
-      <c r="D67" s="13">
+      <c r="D67" s="12">
         <f t="shared" si="4"/>
         <v>0.53639147915992924</v>
       </c>
-      <c r="E67" s="13">
+      <c r="E67" s="12">
         <f t="shared" si="5"/>
         <v>0.67935461950590303</v>
       </c>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-    </row>
-    <row r="68" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A68" s="2"/>
-      <c r="B68" s="10">
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+    </row>
+    <row r="68" spans="1:11" ht="31" customHeight="1">
+      <c r="A68" s="1"/>
+      <c r="B68" s="9">
         <v>0.62</v>
       </c>
-      <c r="C68" s="10">
+      <c r="C68" s="9">
         <f t="shared" si="3"/>
         <v>0.29680958887258779</v>
       </c>
-      <c r="D68" s="10">
+      <c r="D68" s="9">
         <f t="shared" si="4"/>
         <v>0.54669792581989296</v>
       </c>
-      <c r="E68" s="10">
+      <c r="E68" s="9">
         <f t="shared" si="5"/>
         <v>0.68839443179891013</v>
       </c>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-    </row>
-    <row r="69" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A69" s="2"/>
-      <c r="B69" s="13">
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+    </row>
+    <row r="69" spans="1:11" ht="31" customHeight="1">
+      <c r="A69" s="1"/>
+      <c r="B69" s="12">
         <v>0.63</v>
       </c>
-      <c r="C69" s="13">
+      <c r="C69" s="12">
         <f t="shared" si="3"/>
         <v>0.30461592100575746</v>
       </c>
-      <c r="D69" s="13">
+      <c r="D69" s="12">
         <f t="shared" si="4"/>
         <v>0.55706979870032503</v>
       </c>
-      <c r="E69" s="13">
+      <c r="E69" s="12">
         <f t="shared" si="5"/>
         <v>0.69738476801071747</v>
       </c>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-    </row>
-    <row r="70" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A70" s="2"/>
-      <c r="B70" s="10">
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+    </row>
+    <row r="70" spans="1:11" ht="31" customHeight="1">
+      <c r="A70" s="1"/>
+      <c r="B70" s="9">
         <v>0.64</v>
       </c>
-      <c r="C70" s="10">
+      <c r="C70" s="9">
         <f t="shared" ref="C70:C106" si="6">IF($I$9=0,$B70,(1-$H$9)*LN(1+$I$9*$B70)/LN(1+$I$9)+$H$9*$B70)</f>
         <v>0.31260918989955822</v>
       </c>
-      <c r="D70" s="10">
+      <c r="D70" s="9">
         <f t="shared" ref="D70:D106" si="7">IF($I$10=0,$B70,(1-$H$10)*LN(1+$I$10*$B70)/LN(1+$I$10)+$H$10*$B70)</f>
         <v>0.56750820375769195</v>
       </c>
-      <c r="E70" s="10">
+      <c r="E70" s="9">
         <f t="shared" ref="E70:E106" si="8">IF($I$11=0,$B70,(1-$H$11)*LN(1+$I$11*$B70)/LN(1+$I$11)+$H$11*$B70)</f>
         <v>0.70632623335902323</v>
       </c>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
-    </row>
-    <row r="71" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A71" s="2"/>
-      <c r="B71" s="13">
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+    </row>
+    <row r="71" spans="1:11" ht="31" customHeight="1">
+      <c r="A71" s="1"/>
+      <c r="B71" s="12">
         <v>0.65</v>
       </c>
-      <c r="C71" s="13">
+      <c r="C71" s="12">
         <f t="shared" si="6"/>
         <v>0.32079856875041485</v>
       </c>
-      <c r="D71" s="13">
+      <c r="D71" s="12">
         <f t="shared" si="7"/>
         <v>0.5780142752300842</v>
       </c>
-      <c r="E71" s="13">
+      <c r="E71" s="12">
         <f t="shared" si="8"/>
         <v>0.71521942202398203</v>
       </c>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-    </row>
-    <row r="72" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A72" s="2"/>
-      <c r="B72" s="10">
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+    </row>
+    <row r="72" spans="1:11" ht="31" customHeight="1">
+      <c r="A72" s="1"/>
+      <c r="B72" s="9">
         <v>0.66</v>
       </c>
-      <c r="C72" s="10">
+      <c r="C72" s="9">
         <f t="shared" si="6"/>
         <v>0.3291939229831008</v>
       </c>
-      <c r="D72" s="10">
+      <c r="D72" s="9">
         <f t="shared" si="7"/>
         <v>0.58858917660980759</v>
       </c>
-      <c r="E72" s="10">
+      <c r="E72" s="9">
         <f t="shared" si="8"/>
         <v>0.72406491741498025</v>
       </c>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-    </row>
-    <row r="73" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A73" s="2"/>
-      <c r="B73" s="13">
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+    </row>
+    <row r="73" spans="1:11" ht="31" customHeight="1">
+      <c r="A73" s="1"/>
+      <c r="B73" s="12">
         <v>0.67</v>
       </c>
-      <c r="C73" s="13">
+      <c r="C73" s="12">
         <f t="shared" si="6"/>
         <v>0.33780588170117226</v>
       </c>
-      <c r="D73" s="13">
+      <c r="D73" s="12">
         <f t="shared" si="7"/>
         <v>0.59923410165814361</v>
       </c>
-      <c r="E73" s="13">
+      <c r="E73" s="12">
         <f t="shared" si="8"/>
         <v>0.73286329242939496</v>
       </c>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-    </row>
-    <row r="74" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A74" s="2"/>
-      <c r="B74" s="10">
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+    </row>
+    <row r="74" spans="1:11" ht="31" customHeight="1">
+      <c r="A74" s="1"/>
+      <c r="B74" s="9">
         <v>0.68</v>
       </c>
-      <c r="C74" s="10">
+      <c r="C74" s="9">
         <f t="shared" si="6"/>
         <v>0.34664591860085897</v>
       </c>
-      <c r="D74" s="10">
+      <c r="D74" s="9">
         <f t="shared" si="7"/>
         <v>0.60995027546449632</v>
       </c>
-      <c r="E74" s="10">
+      <c r="E74" s="9">
         <f t="shared" si="8"/>
         <v>0.74161510970363209</v>
       </c>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
-    </row>
-    <row r="75" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A75" s="2"/>
-      <c r="B75" s="13">
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+    </row>
+    <row r="75" spans="1:11" ht="31" customHeight="1">
+      <c r="A75" s="1"/>
+      <c r="B75" s="12">
         <v>0.69</v>
       </c>
-      <c r="C75" s="13">
+      <c r="C75" s="12">
         <f t="shared" si="6"/>
         <v>0.35572644389352442</v>
       </c>
-      <c r="D75" s="13">
+      <c r="D75" s="12">
         <f t="shared" si="7"/>
         <v>0.62073895555227376</v>
       </c>
-      <c r="E75" s="13">
+      <c r="E75" s="12">
         <f t="shared" si="8"/>
         <v>0.75032092185671373</v>
       </c>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-    </row>
-    <row r="76" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A76" s="2"/>
-      <c r="B76" s="10">
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+    </row>
+    <row r="76" spans="1:11" ht="31" customHeight="1">
+      <c r="A76" s="1"/>
+      <c r="B76" s="9">
         <v>0.7</v>
       </c>
-      <c r="C76" s="10">
+      <c r="C76" s="9">
         <f t="shared" si="6"/>
         <v>0.36506090908439143</v>
       </c>
-      <c r="D76" s="10">
+      <c r="D76" s="9">
         <f t="shared" si="7"/>
         <v>0.63160143303400229</v>
       </c>
-      <c r="E76" s="10">
+      <c r="E76" s="9">
         <f t="shared" si="8"/>
         <v>0.75898127172667929</v>
       </c>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-    </row>
-    <row r="77" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A77" s="2"/>
-      <c r="B77" s="13">
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+    </row>
+    <row r="77" spans="1:11" ht="31" customHeight="1">
+      <c r="A77" s="1"/>
+      <c r="B77" s="12">
         <v>0.71</v>
       </c>
-      <c r="C77" s="13">
+      <c r="C77" s="12">
         <f t="shared" si="6"/>
         <v>0.37466392682746691</v>
       </c>
-      <c r="D77" s="13">
+      <c r="D77" s="12">
         <f t="shared" si="7"/>
         <v>0.64253903381832389</v>
       </c>
-      <c r="E77" s="13">
+      <c r="E77" s="12">
         <f t="shared" si="8"/>
         <v>0.76759669260005581</v>
       </c>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-    </row>
-    <row r="78" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A78" s="2"/>
-      <c r="B78" s="10">
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+    </row>
+    <row r="78" spans="1:11" ht="31" customHeight="1">
+      <c r="A78" s="1"/>
+      <c r="B78" s="9">
         <v>0.72</v>
       </c>
-      <c r="C78" s="10">
+      <c r="C78" s="9">
         <f t="shared" si="6"/>
         <v>0.3845514085370963</v>
       </c>
-      <c r="D78" s="10">
+      <c r="D78" s="9">
         <f t="shared" si="7"/>
         <v>0.65355311987170273</v>
       </c>
-      <c r="E78" s="10">
+      <c r="E78" s="9">
         <f t="shared" si="8"/>
         <v>0.77616770843463589</v>
       </c>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-    </row>
-    <row r="79" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A79" s="2"/>
-      <c r="B79" s="13">
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+    </row>
+    <row r="79" spans="1:11" ht="31" customHeight="1">
+      <c r="A79" s="1"/>
+      <c r="B79" s="12">
         <v>0.73</v>
       </c>
-      <c r="C79" s="13">
+      <c r="C79" s="12">
         <f t="shared" si="6"/>
         <v>0.39474072300959206</v>
       </c>
-      <c r="D79" s="13">
+      <c r="D79" s="12">
         <f t="shared" si="7"/>
         <v>0.66464509053784282</v>
       </c>
-      <c r="E79" s="13">
+      <c r="E79" s="12">
         <f t="shared" si="8"/>
         <v>0.78469483407579999</v>
       </c>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-    </row>
-    <row r="80" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A80" s="2"/>
-      <c r="B80" s="10">
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+    </row>
+    <row r="80" spans="1:11" ht="31" customHeight="1">
+      <c r="A80" s="1"/>
+      <c r="B80" s="9">
         <v>0.74</v>
       </c>
-      <c r="C80" s="10">
+      <c r="C80" s="9">
         <f t="shared" si="6"/>
         <v>0.4052508800257974</v>
       </c>
-      <c r="D80" s="10">
+      <c r="D80" s="9">
         <f t="shared" si="7"/>
         <v>0.67581638391801158</v>
       </c>
-      <c r="E80" s="10">
+      <c r="E80" s="9">
         <f t="shared" si="8"/>
         <v>0.7931785754666032</v>
       </c>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A81" s="2"/>
-      <c r="B81" s="13">
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+    </row>
+    <row r="81" spans="1:11" ht="31" customHeight="1">
+      <c r="A81" s="1"/>
+      <c r="B81" s="12">
         <v>0.75</v>
       </c>
-      <c r="C81" s="13">
+      <c r="C81" s="12">
         <f t="shared" si="6"/>
         <v>0.41610274380958168</v>
       </c>
-      <c r="D81" s="13">
+      <c r="D81" s="12">
         <f t="shared" si="7"/>
         <v>0.68706847831567486</v>
       </c>
-      <c r="E81" s="13">
+      <c r="E81" s="12">
         <f t="shared" si="8"/>
         <v>0.80161942985184376</v>
       </c>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-    </row>
-    <row r="82" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A82" s="2"/>
-      <c r="B82" s="10">
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+    </row>
+    <row r="82" spans="1:11" ht="31" customHeight="1">
+      <c r="A82" s="1"/>
+      <c r="B82" s="9">
         <v>0.76</v>
       </c>
-      <c r="C82" s="10">
+      <c r="C82" s="9">
         <f t="shared" si="6"/>
         <v>0.42731928236457911</v>
       </c>
-      <c r="D82" s="10">
+      <c r="D82" s="9">
         <f t="shared" si="7"/>
         <v>0.69840289374907738</v>
       </c>
-      <c r="E82" s="10">
+      <c r="E82" s="9">
         <f t="shared" si="8"/>
         <v>0.81001788597631541</v>
       </c>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-    </row>
-    <row r="83" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A83" s="2"/>
-      <c r="B83" s="13">
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+    </row>
+    <row r="83" spans="1:11" ht="31" customHeight="1">
+      <c r="A83" s="1"/>
+      <c r="B83" s="12">
         <v>0.77</v>
       </c>
-      <c r="C83" s="13">
+      <c r="C83" s="12">
         <f t="shared" si="6"/>
         <v>0.43892586017817919</v>
       </c>
-      <c r="D83" s="13">
+      <c r="D83" s="12">
         <f t="shared" si="7"/>
         <v>0.70982119353563444</v>
       </c>
-      <c r="E83" s="13">
+      <c r="E83" s="12">
         <f t="shared" si="8"/>
         <v>0.81837442427744556</v>
       </c>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
-    </row>
-    <row r="84" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A84" s="2"/>
-      <c r="B84" s="10">
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+    </row>
+    <row r="84" spans="1:11" ht="31" customHeight="1">
+      <c r="A84" s="1"/>
+      <c r="B84" s="9">
         <v>0.78</v>
       </c>
-      <c r="C84" s="10">
+      <c r="C84" s="9">
         <f t="shared" si="6"/>
         <v>0.45095058367145918</v>
       </c>
-      <c r="D84" s="10">
+      <c r="D84" s="9">
         <f t="shared" si="7"/>
         <v>0.72132498595226613</v>
       </c>
-      <c r="E84" s="10">
+      <c r="E84" s="9">
         <f t="shared" si="8"/>
         <v>0.82668951707250571</v>
       </c>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-    </row>
-    <row r="85" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A85" s="2"/>
-      <c r="B85" s="13">
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+    </row>
+    <row r="85" spans="1:11" ht="31" customHeight="1">
+      <c r="A85" s="1"/>
+      <c r="B85" s="12">
         <v>0.79</v>
       </c>
-      <c r="C85" s="13">
+      <c r="C85" s="12">
         <f t="shared" si="6"/>
         <v>0.46342471122880308</v>
       </c>
-      <c r="D85" s="13">
+      <c r="D85" s="12">
         <f t="shared" si="7"/>
         <v>0.73291592597608868</v>
       </c>
-      <c r="E85" s="13">
+      <c r="E85" s="12">
         <f t="shared" si="8"/>
         <v>0.83496362874057861</v>
       </c>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2"/>
-    </row>
-    <row r="86" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A86" s="2"/>
-      <c r="B86" s="10">
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+    </row>
+    <row r="86" spans="1:11" ht="31" customHeight="1">
+      <c r="A86" s="1"/>
+      <c r="B86" s="9">
         <v>0.8</v>
       </c>
-      <c r="C86" s="10">
+      <c r="C86" s="9">
         <f t="shared" si="6"/>
         <v>0.4763831428591197</v>
       </c>
-      <c r="D86" s="10">
+      <c r="D86" s="9">
         <f t="shared" si="7"/>
         <v>0.74459571711016936</v>
       </c>
-      <c r="E86" s="10">
+      <c r="E86" s="9">
         <f t="shared" si="8"/>
         <v>0.84319721589945518</v>
       </c>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
-    </row>
-    <row r="87" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A87" s="2"/>
-      <c r="B87" s="13">
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+    </row>
+    <row r="87" spans="1:11" ht="31" customHeight="1">
+      <c r="A87" s="1"/>
+      <c r="B87" s="12">
         <v>0.81</v>
       </c>
-      <c r="C87" s="13">
+      <c r="C87" s="12">
         <f t="shared" si="6"/>
         <v>0.48986500879948736</v>
       </c>
-      <c r="D87" s="13">
+      <c r="D87" s="12">
         <f t="shared" si="7"/>
         <v>0.75636611329938919</v>
       </c>
-      <c r="E87" s="13">
+      <c r="E87" s="12">
         <f t="shared" si="8"/>
         <v>0.85139072757763268</v>
       </c>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
-    </row>
-    <row r="88" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A88" s="2"/>
-      <c r="B88" s="10">
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+    </row>
+    <row r="88" spans="1:11" ht="31" customHeight="1">
+      <c r="A88" s="1"/>
+      <c r="B88" s="9">
         <v>0.82</v>
       </c>
-      <c r="C88" s="10">
+      <c r="C88" s="9">
         <f t="shared" si="6"/>
         <v>0.50391438206641781</v>
       </c>
-      <c r="D88" s="10">
+      <c r="D88" s="9">
         <f t="shared" si="7"/>
         <v>0.76822892094179585</v>
       </c>
-      <c r="E88" s="10">
+      <c r="E88" s="9">
         <f t="shared" si="8"/>
         <v>0.85954460538157429</v>
       </c>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
-    </row>
-    <row r="89" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A89" s="2"/>
-      <c r="B89" s="13">
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+    </row>
+    <row r="89" spans="1:11" ht="31" customHeight="1">
+      <c r="A89" s="1"/>
+      <c r="B89" s="12">
         <v>0.83</v>
       </c>
-      <c r="C89" s="13">
+      <c r="C89" s="12">
         <f t="shared" si="6"/>
         <v>0.51858114765802221</v>
       </c>
-      <c r="D89" s="13">
+      <c r="D89" s="12">
         <f t="shared" si="7"/>
         <v>0.7801860010012226</v>
       </c>
-      <c r="E89" s="13">
+      <c r="E89" s="12">
         <f t="shared" si="8"/>
         <v>0.86765928365838596</v>
       </c>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
-    </row>
-    <row r="90" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A90" s="2"/>
-      <c r="B90" s="10">
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+    </row>
+    <row r="90" spans="1:11" ht="31" customHeight="1">
+      <c r="A90" s="1"/>
+      <c r="B90" s="9">
         <v>0.84</v>
       </c>
-      <c r="C90" s="10">
+      <c r="C90" s="9">
         <f t="shared" si="6"/>
         <v>0.5339220716420624</v>
       </c>
-      <c r="D90" s="10">
+      <c r="D90" s="9">
         <f t="shared" si="7"/>
         <v>0.7922392712273485</v>
       </c>
-      <c r="E90" s="10">
+      <c r="E90" s="9">
         <f t="shared" si="8"/>
         <v>0.87573518965405928</v>
       </c>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-    </row>
-    <row r="91" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A91" s="2"/>
-      <c r="B91" s="13">
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+    </row>
+    <row r="91" spans="1:11" ht="31" customHeight="1">
+      <c r="A91" s="1"/>
+      <c r="B91" s="12">
         <v>0.85</v>
       </c>
-      <c r="C91" s="13">
+      <c r="C91" s="12">
         <f t="shared" si="6"/>
         <v>0.5500021279603855</v>
       </c>
-      <c r="D91" s="13">
+      <c r="D91" s="12">
         <f t="shared" si="7"/>
         <v>0.80439070848982852</v>
       </c>
-      <c r="E91" s="13">
+      <c r="E91" s="12">
         <f t="shared" si="8"/>
         <v>0.88377274366742875</v>
       </c>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
-    </row>
-    <row r="92" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A92" s="2"/>
-      <c r="B92" s="10">
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+    </row>
+    <row r="92" spans="1:11" ht="31" customHeight="1">
+      <c r="A92" s="1"/>
+      <c r="B92" s="9">
         <v>0.86</v>
       </c>
-      <c r="C92" s="10">
+      <c r="C92" s="9">
         <f t="shared" si="6"/>
         <v>0.56689616129346987</v>
       </c>
-      <c r="D92" s="10">
+      <c r="D92" s="9">
         <f t="shared" si="7"/>
         <v>0.81664235123359474</v>
       </c>
-      <c r="E92" s="10">
+      <c r="E92" s="9">
         <f t="shared" si="8"/>
         <v>0.89177235919997588</v>
       </c>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
-    </row>
-    <row r="93" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A93" s="2"/>
-      <c r="B93" s="13">
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+    </row>
+    <row r="93" spans="1:11" ht="31" customHeight="1">
+      <c r="A93" s="1"/>
+      <c r="B93" s="12">
         <v>0.87</v>
       </c>
-      <c r="C93" s="13">
+      <c r="C93" s="12">
         <f t="shared" si="6"/>
         <v>0.58469099360378995</v>
       </c>
-      <c r="D93" s="13">
+      <c r="D93" s="12">
         <f t="shared" si="7"/>
         <v>0.82899630206296215</v>
       </c>
-      <c r="E93" s="13">
+      <c r="E93" s="12">
         <f t="shared" si="8"/>
         <v>0.89973444310162098</v>
       </c>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
-    </row>
-    <row r="94" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A94" s="2"/>
-      <c r="B94" s="10">
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+    </row>
+    <row r="94" spans="1:11" ht="31" customHeight="1">
+      <c r="A94" s="1"/>
+      <c r="B94" s="9">
         <v>0.88</v>
       </c>
-      <c r="C94" s="10">
+      <c r="C94" s="9">
         <f t="shared" si="6"/>
         <v>0.60348812446218625</v>
       </c>
-      <c r="D94" s="10">
+      <c r="D94" s="9">
         <f t="shared" si="7"/>
         <v>0.84145473046272989</v>
       </c>
-      <c r="E94" s="10">
+      <c r="E94" s="9">
         <f t="shared" si="8"/>
         <v>0.90765939571262133</v>
       </c>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
-    </row>
-    <row r="95" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A95" s="2"/>
-      <c r="B95" s="13">
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1"/>
+    </row>
+    <row r="95" spans="1:11" ht="31" customHeight="1">
+      <c r="A95" s="1"/>
+      <c r="B95" s="12">
         <v>0.89</v>
       </c>
-      <c r="C95" s="13">
+      <c r="C95" s="12">
         <f t="shared" si="6"/>
         <v>0.6234072380669563</v>
       </c>
-      <c r="D95" s="13">
+      <c r="D95" s="12">
         <f t="shared" si="7"/>
         <v>0.85401987566508752</v>
       </c>
-      <c r="E95" s="13">
+      <c r="E95" s="12">
         <f t="shared" si="8"/>
         <v>0.91554761100171322</v>
       </c>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
-    </row>
-    <row r="96" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A96" s="2"/>
-      <c r="B96" s="10">
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+    </row>
+    <row r="96" spans="1:11" ht="31" customHeight="1">
+      <c r="A96" s="1"/>
+      <c r="B96" s="9">
         <v>0.9</v>
       </c>
-      <c r="C96" s="10">
+      <c r="C96" s="9">
         <f t="shared" si="6"/>
         <v>0.64459082462355466</v>
       </c>
-      <c r="D96" s="10">
+      <c r="D96" s="9">
         <f t="shared" si="7"/>
         <v>0.86669404967180197</v>
       </c>
-      <c r="E96" s="10">
+      <c r="E96" s="9">
         <f t="shared" si="8"/>
         <v>0.92339947670060074</v>
       </c>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
-    </row>
-    <row r="97" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A97" s="2"/>
-      <c r="B97" s="13">
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
+      <c r="K96" s="1"/>
+    </row>
+    <row r="97" spans="1:11" ht="31" customHeight="1">
+      <c r="A97" s="1"/>
+      <c r="B97" s="12">
         <v>0.91</v>
       </c>
-      <c r="C97" s="13">
+      <c r="C97" s="12">
         <f t="shared" si="6"/>
         <v>0.66721037000116235</v>
       </c>
-      <c r="D97" s="13">
+      <c r="D97" s="12">
         <f t="shared" si="7"/>
         <v>0.87947964044189242</v>
       </c>
-      <c r="E97" s="13">
+      <c r="E97" s="12">
         <f t="shared" si="8"/>
         <v>0.93121537443492164</v>
       </c>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
-    </row>
-    <row r="98" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A98" s="2"/>
-      <c r="B98" s="10">
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
+    </row>
+    <row r="98" spans="1:11" ht="31" customHeight="1">
+      <c r="A98" s="1"/>
+      <c r="B98" s="9">
         <v>0.92</v>
       </c>
-      <c r="C98" s="10">
+      <c r="C98" s="9">
         <f t="shared" si="6"/>
         <v>0.69147479910585075</v>
       </c>
-      <c r="D98" s="10">
+      <c r="D98" s="9">
         <f t="shared" si="7"/>
         <v>0.89237911525578284</v>
       </c>
-      <c r="E98" s="10">
+      <c r="E98" s="9">
         <f t="shared" si="8"/>
         <v>0.93899567985178833</v>
       </c>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="2"/>
-      <c r="K98" s="2"/>
-    </row>
-    <row r="99" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A99" s="2"/>
-      <c r="B99" s="13">
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
+      <c r="K98" s="1"/>
+    </row>
+    <row r="99" spans="1:11" ht="31" customHeight="1">
+      <c r="A99" s="1"/>
+      <c r="B99" s="12">
         <v>0.93</v>
       </c>
-      <c r="C99" s="13">
+      <c r="C99" s="12">
         <f t="shared" si="6"/>
         <v>0.71764223557463891</v>
       </c>
-      <c r="D99" s="13">
+      <c r="D99" s="12">
         <f t="shared" si="7"/>
         <v>0.90539502426779028</v>
       </c>
-      <c r="E99" s="13">
+      <c r="E99" s="12">
         <f t="shared" si="8"/>
         <v>0.9467407627440203</v>
       </c>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="2"/>
-      <c r="K99" s="2"/>
-    </row>
-    <row r="100" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A100" s="2"/>
-      <c r="B100" s="10">
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
+      <c r="K99" s="1"/>
+    </row>
+    <row r="100" spans="1:11" ht="31" customHeight="1">
+      <c r="A100" s="1"/>
+      <c r="B100" s="9">
         <v>0.94</v>
       </c>
-      <c r="C100" s="10">
+      <c r="C100" s="9">
         <f t="shared" si="6"/>
         <v>0.74603677513171862</v>
       </c>
-      <c r="D100" s="10">
+      <c r="D100" s="9">
         <f t="shared" si="7"/>
         <v>0.91853000425974562</v>
       </c>
-      <c r="E100" s="10">
+      <c r="E100" s="9">
         <f t="shared" si="8"/>
         <v>0.95445098717116272</v>
       </c>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
-    </row>
-    <row r="101" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A101" s="2"/>
-      <c r="B101" s="13">
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="K100" s="1"/>
+    </row>
+    <row r="101" spans="1:11" ht="31" customHeight="1">
+      <c r="A101" s="1"/>
+      <c r="B101" s="12">
         <v>0.95</v>
       </c>
-      <c r="C101" s="13">
+      <c r="C101" s="12">
         <f t="shared" si="6"/>
         <v>0.77707307876902676</v>
       </c>
-      <c r="D101" s="13">
+      <c r="D101" s="12">
         <f t="shared" si="7"/>
         <v>0.93178678260956671</v>
       </c>
-      <c r="E101" s="13">
+      <c r="E101" s="12">
         <f t="shared" si="8"/>
         <v>0.96212671157739738</v>
       </c>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="2"/>
-    </row>
-    <row r="102" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A102" s="2"/>
-      <c r="B102" s="10">
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+    </row>
+    <row r="102" spans="1:11" ht="31" customHeight="1">
+      <c r="A102" s="1"/>
+      <c r="B102" s="9">
         <v>0.96</v>
       </c>
-      <c r="C102" s="10">
+      <c r="C102" s="9">
         <f t="shared" si="6"/>
         <v>0.8112936145727736</v>
       </c>
-      <c r="D102" s="10">
+      <c r="D102" s="9">
         <f t="shared" si="7"/>
         <v>0.94516818148972548</v>
       </c>
-      <c r="E102" s="10">
+      <c r="E102" s="9">
         <f t="shared" si="8"/>
         <v>0.96976828890643507</v>
       </c>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-      <c r="K102" s="2"/>
-    </row>
-    <row r="103" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A103" s="2"/>
-      <c r="B103" s="13">
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
+      <c r="K102" s="1"/>
+    </row>
+    <row r="103" spans="1:11" ht="31" customHeight="1">
+      <c r="A103" s="1"/>
+      <c r="B103" s="12">
         <v>0.97</v>
       </c>
-      <c r="C103" s="13">
+      <c r="C103" s="12">
         <f t="shared" si="6"/>
         <v>0.84942725912383288</v>
       </c>
-      <c r="D103" s="13">
+      <c r="D103" s="12">
         <f t="shared" si="7"/>
         <v>0.95867712231178137</v>
       </c>
-      <c r="E103" s="13">
+      <c r="E103" s="12">
         <f t="shared" si="8"/>
         <v>0.97737606671348642</v>
       </c>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
-      <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
-    </row>
-    <row r="104" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A104" s="2"/>
-      <c r="B104" s="10">
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
+      <c r="K103" s="1"/>
+    </row>
+    <row r="104" spans="1:11" ht="31" customHeight="1">
+      <c r="A104" s="1"/>
+      <c r="B104" s="9">
         <v>0.98</v>
       </c>
-      <c r="C104" s="10">
+      <c r="C104" s="9">
         <f t="shared" si="6"/>
         <v>0.8924858866687011</v>
       </c>
-      <c r="D104" s="10">
+      <c r="D104" s="9">
         <f t="shared" si="7"/>
         <v>0.97231663043448913</v>
       </c>
-      <c r="E104" s="10">
+      <c r="E104" s="9">
         <f t="shared" si="8"/>
         <v>0.98495038727439643</v>
       </c>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
-    </row>
-    <row r="105" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A105" s="2"/>
-      <c r="B105" s="13">
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
+      <c r="K104" s="1"/>
+    </row>
+    <row r="105" spans="1:11" ht="31" customHeight="1">
+      <c r="A105" s="1"/>
+      <c r="B105" s="12">
         <v>0.99</v>
       </c>
-      <c r="C105" s="13">
+      <c r="C105" s="12">
         <f t="shared" si="6"/>
         <v>0.94193295954412271</v>
       </c>
-      <c r="D105" s="13">
+      <c r="D105" s="12">
         <f t="shared" si="7"/>
         <v>0.98608984015446355</v>
       </c>
-      <c r="E105" s="13">
+      <c r="E105" s="12">
         <f t="shared" si="8"/>
         <v>0.99249158769203172</v>
       </c>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2"/>
-      <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
-    </row>
-    <row r="106" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A106" s="2"/>
-      <c r="B106" s="10">
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+      <c r="K105" s="1"/>
+    </row>
+    <row r="106" spans="1:11" ht="31" customHeight="1">
+      <c r="A106" s="1"/>
+      <c r="B106" s="9">
         <v>1</v>
       </c>
-      <c r="C106" s="10">
+      <c r="C106" s="9">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D106" s="10">
+      <c r="D106" s="9">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="E106" s="10">
+      <c r="E106" s="9">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
-      <c r="J106" s="2"/>
-      <c r="K106" s="2"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6623,5 +7058,6 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/throttle_curve.xlsx
+++ b/docs/throttle_curve.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\xlsx-locale-20261027\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F1388E-3FA3-476A-A59E-E86EF9A176BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AD12C4-7DA1-4671-885D-08A873B1AE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Throttle Curves" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
   <si>
     <t>Astral · Throttle curves</t>
   </si>
@@ -192,10 +192,6 @@
   </si>
   <si>
     <t>Astral · 油门采样</t>
-  </si>
-  <si>
-    <t>WRC17 / Rally1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>简体中文</t>
@@ -698,6 +694,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -712,9 +711,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1777,301 +1773,301 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.6801448322603195E-3</c:v>
+                  <c:v>9.1404428218141969E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5389017612306488E-2</c:v>
+                  <c:v>1.8292848425662499E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.3126938755721561E-2</c:v>
+                  <c:v>2.7457325702157483E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.0894234068771745E-2</c:v>
+                  <c:v>3.6633985035468962E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.8691234870011873E-2</c:v>
+                  <c:v>4.5822938330763369E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.6518278115341136E-2</c:v>
+                  <c:v>5.5024299042277271E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.437570652662372E-2</c:v>
+                  <c:v>6.4238182202040542E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.2263868724000346E-2</c:v>
+                  <c:v>7.3464704449269363E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.0183119362015323E-2</c:v>
+                  <c:v>8.2703984060445948E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.8133819269695204E-2</c:v>
+                  <c:v>9.1956140980106266E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.6116335594713919E-2</c:v>
+                  <c:v>0.10122129685235373</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.4131041951792213E-2</c:v>
+                  <c:v>0.11049957505312191</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.10217831857547742</c:v>
+                  <c:v>0.11979110072320517</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.1102585524774635</c:v>
+                  <c:v>0.1290960008020817</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.11837213760861129</c:v>
+                  <c:v>0.13841440406254965</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.1265194750258396</c:v>
+                  <c:v>0.14774644114620222</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.13470097306406517</c:v>
+                  <c:v>0.15709224459976348</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.1429170475133727</c:v>
+                  <c:v>0.16645194891231319</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.15116812180161127</c:v>
+                  <c:v>0.17582569055342423</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.1594546271826133</c:v>
+                  <c:v>0.18521360801224068</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.1677770029302495</c:v>
+                  <c:v>0.19461584183752534</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.1761356965385342</c:v>
+                  <c:v>0.20403253467870386</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.18453116392801255</c:v>
+                  <c:v>0.21346383132793717</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.19296386965866436</c:v>
+                  <c:v>0.22290987876325186</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.20143428714957642</c:v>
+                  <c:v>0.23237082619276217</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.20994289890563997</c:v>
+                  <c:v>0.2418468251000146</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.21849019675154671</c:v>
+                  <c:v>0.25133802929049232</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.22707668207336662</c:v>
+                  <c:v>0.26084459493931289</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.23570286606800478</c:v>
+                  <c:v>0.27036668064015723</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.24436927000084591</c:v>
+                  <c:v>0.27990444745546811</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.25307642547191278</c:v>
+                  <c:v>0.28945805896795801</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.26182487469087928</c:v>
+                  <c:v>0.29902768133346697</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.27061517076129021</c:v>
+                  <c:v>0.30861348333521332</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.27944787797436538</c:v>
+                  <c:v>0.31821563643948236</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.28832357211277315</c:v>
+                  <c:v>0.32783431485279835</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.29724284076478735</c:v>
+                  <c:v>0.33746969558062667</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.3062062836492514</c:v>
+                  <c:v>0.34712195848765665</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.31521451295180247</c:v>
+                  <c:v>0.35679128635971713</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.32426815367282602</c:v>
+                  <c:v>0.36647786496737544</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.33336784398763486</c:v>
+                  <c:v>0.37618188313127832</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.3425142356193922</c:v>
+                  <c:v>0.38590353278928913</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.35170799422532273</c:v>
+                  <c:v>0.39564300906548427</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.36094979979678654</c:v>
+                  <c:v>0.40540051034106744</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.37024034707381337</c:v>
+                  <c:v>0.4151762383272693</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.37958034597473334</c:v>
+                  <c:v>0.42497039814029708</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.38897052204156446</c:v>
+                  <c:v>0.43478319837840529</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.39841161690185894</c:v>
+                  <c:v>0.44461485120115912</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.40790438874774249</c:v>
+                  <c:v>0.45446557241096708</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.4174496128329182</c:v>
+                  <c:v>0.46433558153695859</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.42704808198845362</c:v>
+                  <c:v>0.47422510192129119</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.43670060715820669</c:v>
+                  <c:v>0.48413436080797057</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.44640801795479484</c:v>
+                  <c:v>0.49406358943427087</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.45617116323706058</c:v>
+                  <c:v>0.50401302312484997</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.46599091171004031</c:v>
+                  <c:v>0.51398290138865232</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.47586815254849502</c:v>
+                  <c:v>0.52397346801870159</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.48580379604512214</c:v>
+                  <c:v>0.53398497119488564</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.49579877428463126</c:v>
+                  <c:v>0.54401766358984305</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.50585404184493254</c:v>
+                  <c:v>0.55407180247806387</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.51597057652675415</c:v>
+                  <c:v>0.56414764984832111</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.5261493801130871</c:v>
+                  <c:v>0.57424547251955871</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.53639147915992924</c:v>
+                  <c:v>0.58436554226036197</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.54669792581989296</c:v>
+                  <c:v>0.59450813591214391</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.55706979870032503</c:v>
+                  <c:v>0.60467353551618852</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.56750820375769195</c:v>
+                  <c:v>0.61486202844469695</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.5780142752300842</c:v>
+                  <c:v>0.62507390753598646</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.58858917660980759</c:v>
+                  <c:v>0.63530947123400461</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.59923410165814361</c:v>
+                  <c:v>0.64556902373232139</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.60995027546449632</c:v>
+                  <c:v>0.65585287512277568</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.62073895555227376</c:v>
+                  <c:v>0.66616134154895701</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.63160143303400229</c:v>
+                  <c:v>0.67649474536471166</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.64253903381832389</c:v>
+                  <c:v>0.68685341529787225</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.65355311987170273</c:v>
+                  <c:v>0.69723768661941943</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.66464509053784282</c:v>
+                  <c:v>0.70764790131829303</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.67581638391801158</c:v>
+                  <c:v>0.71808440828207987</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.68706847831567486</c:v>
+                  <c:v>0.72854756348381833</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.69840289374907738</c:v>
+                  <c:v>0.73903773017516727</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.70982119353563444</c:v>
+                  <c:v>0.74955527908620567</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.72132498595226613</c:v>
+                  <c:v>0.76010058863213303</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.73291592597608868</c:v>
+                  <c:v>0.77067404512716231</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.74459571711016936</c:v>
+                  <c:v>0.78127604300590525</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.75636611329938919</c:v>
+                  <c:v>0.79190698505256951</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.76822892094179585</c:v>
+                  <c:v>0.80256728263829913</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.7801860010012226</c:v>
+                  <c:v>0.81325735596700799</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.7922392712273485</c:v>
+                  <c:v>0.82397763433007598</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.80439070848982852</c:v>
+                  <c:v>0.83472855637028831</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.81664235123359474</c:v>
+                  <c:v>0.84551057035543264</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.82899630206296215</c:v>
+                  <c:v>0.85632413446197142</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.84145473046272989</c:v>
+                  <c:v>0.8671697170692455</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.85401987566508752</c:v>
+                  <c:v>0.87804779706467562</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.86669404967180197</c:v>
+                  <c:v>0.88895886416046532</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.87947964044189242</c:v>
+                  <c:v>0.89990341922232331</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.89237911525578284</c:v>
+                  <c:v>0.91088197461076126</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.90539502426779028</c:v>
+                  <c:v>0.92189505453554421</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.91853000425974562</c:v>
+                  <c:v>0.93294319542391368</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.93178678260956671</c:v>
+                  <c:v>0.94402694630322204</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.94516818148972548</c:v>
+                  <c:v>0.95514686919866731</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.95867712231178137</c:v>
+                  <c:v>0.96630353954684489</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.97231663043448913</c:v>
+                  <c:v>0.97749754662588029</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.98608984015446355</c:v>
+                  <c:v>0.98872949400294385</c:v>
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>1</c:v>
@@ -2433,301 +2429,301 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.391976367936305E-2</c:v>
+                  <c:v>0.01</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.7712236977093824E-2</c:v>
+                  <c:v>0.02</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.1379903667644352E-2</c:v>
+                  <c:v>0.03</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.4925175529730766E-2</c:v>
+                  <c:v>0.04</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.835039510225821E-2</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.1657838309627112E-2</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.4849716963780112E-2</c:v>
+                  <c:v>7.0000000000000007E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.10792818114986957</c:v>
+                  <c:v>0.08</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.12089532150198161</c:v>
+                  <c:v>0.09</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.13375317137494153</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.14650370891784326</c:v>
+                  <c:v>0.11</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.15914885905459161</c:v>
+                  <c:v>0.12</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.17169049537641662</c:v>
+                  <c:v>0.13</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.18413044195101544</c:v>
+                  <c:v>0.14000000000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.19647047505268539</c:v>
+                  <c:v>0.15</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.20871232481756263</c:v>
+                  <c:v>0.16</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.22085767682781182</c:v>
+                  <c:v>0.17</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.23290817362840482</c:v>
+                  <c:v>0.18</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.24486541617989693</c:v>
+                  <c:v>0.19</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.25673096525041444</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.26850634274988283</c:v>
+                  <c:v>0.21</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.28019303300934545</c:v>
+                  <c:v>0.22</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.29179248400806368</c:v>
+                  <c:v>0.23</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.30330610855093548</c:v>
+                  <c:v>0.24</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.31473528539862616</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.32608136035267266</c:v>
+                  <c:v>0.26</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.33734564729769712</c:v>
+                  <c:v>0.27</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.34852942920274782</c:v>
+                  <c:v>0.28000000000000003</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.35963395908367646</c:v>
+                  <c:v>0.28999999999999998</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.37066046092835692</c:v>
+                  <c:v>0.3</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.3816101305864531</c:v>
+                  <c:v>0.31</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.39248413662535597</c:v>
+                  <c:v>0.32</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.40328362115381855</c:v>
+                  <c:v>0.33</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.41400970061474307</c:v>
+                  <c:v>0.34</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.42466346654849568</c:v>
+                  <c:v>0.35</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.43524598632805317</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.44575830386722187</c:v>
+                  <c:v>0.37</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.45620144030309984</c:v>
+                  <c:v>0.38</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.46657639465390466</c:v>
+                  <c:v>0.39</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.47688414445321758</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.48712564636166195</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.4973018367569616</c:v>
+                  <c:v>0.42</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.50741363230329817</c:v>
+                  <c:v>0.43</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.51746193050082889</c:v>
+                  <c:v>0.44</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.5274476102161888</c:v>
+                  <c:v>0.45</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.5373715321947633</c:v>
+                  <c:v>0.46</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.54723453955547574</c:v>
+                  <c:v>0.47</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.55703745826880269</c:v>
+                  <c:v>0.48</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.56678109761869333</c:v>
+                  <c:v>0.49</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.57646625064904067</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.5860936945953189</c:v>
+                  <c:v>0.51</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.59566419130197479</c:v>
+                  <c:v>0.52</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.60517848762613446</c:v>
+                  <c:v>0.53</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.61463731582815906</c:v>
+                  <c:v>0.54</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.62404139394956171</c:v>
+                  <c:v>0.55000000000000004</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.63339142617877142</c:v>
+                  <c:v>0.56000000000000005</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.64268810320521186</c:v>
+                  <c:v>0.56999999999999995</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.65193210256214051</c:v>
+                  <c:v>0.57999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.66112408895866737</c:v>
+                  <c:v>0.59</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.67026471460137405</c:v>
+                  <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.67935461950590303</c:v>
+                  <c:v>0.61</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.68839443179891013</c:v>
+                  <c:v>0.62</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.69738476801071747</c:v>
+                  <c:v>0.63</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.70632623335902323</c:v>
+                  <c:v>0.64</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.71521942202398203</c:v>
+                  <c:v>0.65</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.72406491741498025</c:v>
+                  <c:v>0.66</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.73286329242939496</c:v>
+                  <c:v>0.67</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.74161510970363209</c:v>
+                  <c:v>0.68</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.75032092185671373</c:v>
+                  <c:v>0.69</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.75898127172667929</c:v>
+                  <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.76759669260005581</c:v>
+                  <c:v>0.71</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.77616770843463589</c:v>
+                  <c:v>0.72</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.78469483407579999</c:v>
+                  <c:v>0.73</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.7931785754666032</c:v>
+                  <c:v>0.74</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.80161942985184376</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.81001788597631541</c:v>
+                  <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.81837442427744556</c:v>
+                  <c:v>0.77</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.82668951707250571</c:v>
+                  <c:v>0.78</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.83496362874057861</c:v>
+                  <c:v>0.79</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.84319721589945518</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.85139072757763268</c:v>
+                  <c:v>0.81</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.85954460538157429</c:v>
+                  <c:v>0.82</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.86765928365838596</c:v>
+                  <c:v>0.83</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.87573518965405928</c:v>
+                  <c:v>0.84</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.88377274366742875</c:v>
+                  <c:v>0.85</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.89177235919997588</c:v>
+                  <c:v>0.86</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.89973444310162098</c:v>
+                  <c:v>0.87</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.90765939571262133</c:v>
+                  <c:v>0.88</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.91554761100171322</c:v>
+                  <c:v>0.89</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.92339947670060074</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.93121537443492164</c:v>
+                  <c:v>0.91</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.93899567985178833</c:v>
+                  <c:v>0.92</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.9467407627440203</c:v>
+                  <c:v>0.93</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.95445098717116272</c:v>
+                  <c:v>0.94</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.96212671157739738</c:v>
+                  <c:v>0.95</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.96976828890643507</c:v>
+                  <c:v>0.96</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.97737606671348642</c:v>
+                  <c:v>0.97</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.98495038727439643</c:v>
+                  <c:v>0.98</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.99249158769203172</c:v>
+                  <c:v>0.99</c:v>
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>1</c:v>
@@ -3172,22 +3168,22 @@
   <sheetData>
     <row r="1" spans="1:15" ht="22" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="26" t="s">
         <v>19</v>
       </c>
       <c r="H1" s="1"/>
@@ -3242,11 +3238,11 @@
         <f>VLOOKUP("label.vehicleEcu",Locale!$A$2:$D$14,4,FALSE)</f>
         <v>车型 / ECU</v>
       </c>
-      <c r="C4" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="C4" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -3973,21 +3969,21 @@
     <row r="5" spans="1:14" ht="32.15" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="26" t="str">
+      <c r="C5" s="27" t="str">
         <f>VLOOKUP("label.progressiveMap",Locale!$A$2:$D$14,4,FALSE)</f>
         <v>1 · 渐进</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26" t="str">
+      <c r="D5" s="27"/>
+      <c r="E5" s="27" t="str">
         <f>VLOOKUP("label.subtleLinearMap",Locale!$A$2:$D$14,4,FALSE)</f>
         <v>2 · 轻度线性</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26" t="str">
+      <c r="F5" s="27"/>
+      <c r="G5" s="27" t="str">
         <f>VLOOKUP("label.aggressiveMap",Locale!$A$2:$D$14,4,FALSE)</f>
         <v>3 · 激进</v>
       </c>
-      <c r="H5" s="26"/>
+      <c r="H5" s="27"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -4102,23 +4098,19 @@
         <v>11</v>
       </c>
       <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-0.97</v>
+      </c>
+      <c r="E10" s="6">
         <v>0.15</v>
       </c>
-      <c r="D10" s="6">
-        <v>-0.88</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.69</v>
-      </c>
       <c r="F10" s="6">
-        <v>-0.28000000000000003</v>
-      </c>
-      <c r="G10" s="6">
-        <v>0.59</v>
-      </c>
-      <c r="H10" s="6">
-        <v>9.8000000000000007</v>
-      </c>
+        <v>-0.65</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="31" customHeight="1">
@@ -4127,23 +4119,19 @@
         <v>12</v>
       </c>
       <c r="C11" s="6">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="D11" s="6">
-        <v>-0.88</v>
+        <v>-0.95</v>
       </c>
       <c r="E11" s="6">
-        <v>0.69</v>
+        <v>0.65</v>
       </c>
       <c r="F11" s="6">
-        <v>-0.28000000000000003</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0.59</v>
-      </c>
-      <c r="H11" s="6">
-        <v>9.8000000000000007</v>
-      </c>
+        <v>-0.45</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:14" ht="23.15" customHeight="1">
@@ -4557,9 +4545,9 @@
         <f>VLOOKUP("label.selectedEcu",Locale!$A$2:$D$14,4,FALSE)</f>
         <v>所选 ECU</v>
       </c>
-      <c r="H4" s="27" t="str">
+      <c r="H4" s="22" t="str">
         <f>'Throttle Curves'!C4</f>
-        <v>WRC17 / Rally1</v>
+        <v>RX3</v>
       </c>
       <c r="I4" s="21"/>
       <c r="J4" s="21"/>
@@ -4614,7 +4602,7 @@
       </c>
       <c r="H6" s="11">
         <f>MATCH('Throttle Curves'!C4,Parameters!B7:B11,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -4631,11 +4619,11 @@
       </c>
       <c r="D7" s="12">
         <f t="shared" si="1"/>
-        <v>7.6801448322603195E-3</v>
+        <v>9.1404428218141969E-3</v>
       </c>
       <c r="E7" s="12">
         <f t="shared" si="2"/>
-        <v>1.391976367936305E-2</v>
+        <v>0.01</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -4655,11 +4643,11 @@
       </c>
       <c r="D8" s="9">
         <f t="shared" si="1"/>
-        <v>1.5389017612306488E-2</v>
+        <v>1.8292848425662499E-2</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="2"/>
-        <v>2.7712236977093824E-2</v>
+        <v>0.02</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="13" t="str">
@@ -4686,11 +4674,11 @@
       </c>
       <c r="D9" s="12">
         <f t="shared" si="1"/>
-        <v>2.3126938755721561E-2</v>
+        <v>2.7457325702157483E-2</v>
       </c>
       <c r="E9" s="12">
         <f t="shared" si="2"/>
-        <v>4.1379903667644352E-2</v>
+        <v>0.03</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="14">
@@ -4718,11 +4706,11 @@
       </c>
       <c r="D10" s="9">
         <f t="shared" si="1"/>
-        <v>3.0894234068771745E-2</v>
+        <v>3.6633985035468962E-2</v>
       </c>
       <c r="E10" s="9">
         <f t="shared" si="2"/>
-        <v>5.4925175529730766E-2</v>
+        <v>0.04</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="16">
@@ -4730,11 +4718,11 @@
       </c>
       <c r="H10" s="17">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,3)</f>
-        <v>0.25</v>
+        <v>0.65</v>
       </c>
       <c r="I10" s="17">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,4)</f>
-        <v>-0.55000000000000004</v>
+        <v>-0.45</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -4750,11 +4738,11 @@
       </c>
       <c r="D11" s="12">
         <f t="shared" si="1"/>
-        <v>3.8691234870011873E-2</v>
+        <v>4.5822938330763369E-2</v>
       </c>
       <c r="E11" s="12">
         <f t="shared" si="2"/>
-        <v>6.835039510225821E-2</v>
+        <v>0.05</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="14">
@@ -4762,11 +4750,11 @@
       </c>
       <c r="H11" s="15">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,5)</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="15">
         <f>INDEX(Parameters!$C$7:$H$11,$H$6,6)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -4782,11 +4770,11 @@
       </c>
       <c r="D12" s="9">
         <f t="shared" si="1"/>
-        <v>4.6518278115341136E-2</v>
+        <v>5.5024299042277271E-2</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="2"/>
-        <v>8.1657838309627112E-2</v>
+        <v>0.06</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -4806,11 +4794,11 @@
       </c>
       <c r="D13" s="12">
         <f t="shared" si="1"/>
-        <v>5.437570652662372E-2</v>
+        <v>6.4238182202040542E-2</v>
       </c>
       <c r="E13" s="12">
         <f t="shared" si="2"/>
-        <v>9.4849716963780112E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -4830,11 +4818,11 @@
       </c>
       <c r="D14" s="9">
         <f t="shared" si="1"/>
-        <v>6.2263868724000346E-2</v>
+        <v>7.3464704449269363E-2</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="2"/>
-        <v>0.10792818114986957</v>
+        <v>0.08</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -4854,11 +4842,11 @@
       </c>
       <c r="D15" s="12">
         <f t="shared" si="1"/>
-        <v>7.0183119362015323E-2</v>
+        <v>8.2703984060445948E-2</v>
       </c>
       <c r="E15" s="12">
         <f t="shared" si="2"/>
-        <v>0.12089532150198161</v>
+        <v>0.09</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -4878,11 +4866,11 @@
       </c>
       <c r="D16" s="9">
         <f t="shared" si="1"/>
-        <v>7.8133819269695204E-2</v>
+        <v>9.1956140980106266E-2</v>
       </c>
       <c r="E16" s="9">
         <f t="shared" si="2"/>
-        <v>0.13375317137494153</v>
+        <v>0.1</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -4902,11 +4890,11 @@
       </c>
       <c r="D17" s="12">
         <f t="shared" si="1"/>
-        <v>8.6116335594713919E-2</v>
+        <v>0.10122129685235373</v>
       </c>
       <c r="E17" s="12">
         <f t="shared" si="2"/>
-        <v>0.14650370891784326</v>
+        <v>0.11</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -4926,11 +4914,11 @@
       </c>
       <c r="D18" s="9">
         <f t="shared" si="1"/>
-        <v>9.4131041951792213E-2</v>
+        <v>0.11049957505312191</v>
       </c>
       <c r="E18" s="9">
         <f t="shared" si="2"/>
-        <v>0.15914885905459161</v>
+        <v>0.12</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -4950,11 +4938,11 @@
       </c>
       <c r="D19" s="12">
         <f t="shared" si="1"/>
-        <v>0.10217831857547742</v>
+        <v>0.11979110072320517</v>
       </c>
       <c r="E19" s="12">
         <f t="shared" si="2"/>
-        <v>0.17169049537641662</v>
+        <v>0.13</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -4974,11 +4962,11 @@
       </c>
       <c r="D20" s="9">
         <f t="shared" si="1"/>
-        <v>0.1102585524774635</v>
+        <v>0.1290960008020817</v>
       </c>
       <c r="E20" s="9">
         <f t="shared" si="2"/>
-        <v>0.18413044195101544</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -4998,11 +4986,11 @@
       </c>
       <c r="D21" s="12">
         <f t="shared" si="1"/>
-        <v>0.11837213760861129</v>
+        <v>0.13841440406254965</v>
       </c>
       <c r="E21" s="12">
         <f t="shared" si="2"/>
-        <v>0.19647047505268539</v>
+        <v>0.15</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -5022,11 +5010,11 @@
       </c>
       <c r="D22" s="9">
         <f t="shared" si="1"/>
-        <v>0.1265194750258396</v>
+        <v>0.14774644114620222</v>
       </c>
       <c r="E22" s="9">
         <f t="shared" si="2"/>
-        <v>0.20871232481756263</v>
+        <v>0.16</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -5046,11 +5034,11 @@
       </c>
       <c r="D23" s="12">
         <f t="shared" si="1"/>
-        <v>0.13470097306406517</v>
+        <v>0.15709224459976348</v>
       </c>
       <c r="E23" s="12">
         <f t="shared" si="2"/>
-        <v>0.22085767682781182</v>
+        <v>0.17</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -5070,11 +5058,11 @@
       </c>
       <c r="D24" s="9">
         <f t="shared" si="1"/>
-        <v>0.1429170475133727</v>
+        <v>0.16645194891231319</v>
       </c>
       <c r="E24" s="9">
         <f t="shared" si="2"/>
-        <v>0.23290817362840482</v>
+        <v>0.18</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -5094,11 +5082,11 @@
       </c>
       <c r="D25" s="12">
         <f t="shared" si="1"/>
-        <v>0.15116812180161127</v>
+        <v>0.17582569055342423</v>
       </c>
       <c r="E25" s="12">
         <f t="shared" si="2"/>
-        <v>0.24486541617989693</v>
+        <v>0.19</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -5118,11 +5106,11 @@
       </c>
       <c r="D26" s="9">
         <f t="shared" si="1"/>
-        <v>0.1594546271826133</v>
+        <v>0.18521360801224068</v>
       </c>
       <c r="E26" s="9">
         <f t="shared" si="2"/>
-        <v>0.25673096525041444</v>
+        <v>0.2</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -5142,11 +5130,11 @@
       </c>
       <c r="D27" s="12">
         <f t="shared" si="1"/>
-        <v>0.1677770029302495</v>
+        <v>0.19461584183752534</v>
       </c>
       <c r="E27" s="12">
         <f t="shared" si="2"/>
-        <v>0.26850634274988283</v>
+        <v>0.21</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -5166,11 +5154,11 @@
       </c>
       <c r="D28" s="9">
         <f t="shared" si="1"/>
-        <v>0.1761356965385342</v>
+        <v>0.20403253467870386</v>
       </c>
       <c r="E28" s="9">
         <f t="shared" si="2"/>
-        <v>0.28019303300934545</v>
+        <v>0.22</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -5190,11 +5178,11 @@
       </c>
       <c r="D29" s="12">
         <f t="shared" si="1"/>
-        <v>0.18453116392801255</v>
+        <v>0.21346383132793717</v>
       </c>
       <c r="E29" s="12">
         <f t="shared" si="2"/>
-        <v>0.29179248400806368</v>
+        <v>0.23</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -5214,11 +5202,11 @@
       </c>
       <c r="D30" s="9">
         <f t="shared" si="1"/>
-        <v>0.19296386965866436</v>
+        <v>0.22290987876325186</v>
       </c>
       <c r="E30" s="9">
         <f t="shared" si="2"/>
-        <v>0.30330610855093548</v>
+        <v>0.24</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -5238,11 +5226,11 @@
       </c>
       <c r="D31" s="12">
         <f t="shared" si="1"/>
-        <v>0.20143428714957642</v>
+        <v>0.23237082619276217</v>
       </c>
       <c r="E31" s="12">
         <f t="shared" si="2"/>
-        <v>0.31473528539862616</v>
+        <v>0.25</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -5262,11 +5250,11 @@
       </c>
       <c r="D32" s="9">
         <f t="shared" si="1"/>
-        <v>0.20994289890563997</v>
+        <v>0.2418468251000146</v>
       </c>
       <c r="E32" s="9">
         <f t="shared" si="2"/>
-        <v>0.32608136035267266</v>
+        <v>0.26</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -5286,11 +5274,11 @@
       </c>
       <c r="D33" s="12">
         <f t="shared" si="1"/>
-        <v>0.21849019675154671</v>
+        <v>0.25133802929049232</v>
       </c>
       <c r="E33" s="12">
         <f t="shared" si="2"/>
-        <v>0.33734564729769712</v>
+        <v>0.27</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -5310,11 +5298,11 @@
       </c>
       <c r="D34" s="9">
         <f t="shared" si="1"/>
-        <v>0.22707668207336662</v>
+        <v>0.26084459493931289</v>
       </c>
       <c r="E34" s="9">
         <f t="shared" si="2"/>
-        <v>0.34852942920274782</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -5334,11 +5322,11 @@
       </c>
       <c r="D35" s="12">
         <f t="shared" si="1"/>
-        <v>0.23570286606800478</v>
+        <v>0.27036668064015723</v>
       </c>
       <c r="E35" s="12">
         <f t="shared" si="2"/>
-        <v>0.35963395908367646</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -5358,11 +5346,11 @@
       </c>
       <c r="D36" s="9">
         <f t="shared" si="1"/>
-        <v>0.24436927000084591</v>
+        <v>0.27990444745546811</v>
       </c>
       <c r="E36" s="9">
         <f t="shared" si="2"/>
-        <v>0.37066046092835692</v>
+        <v>0.3</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -5382,11 +5370,11 @@
       </c>
       <c r="D37" s="12">
         <f t="shared" si="1"/>
-        <v>0.25307642547191278</v>
+        <v>0.28945805896795801</v>
       </c>
       <c r="E37" s="12">
         <f t="shared" si="2"/>
-        <v>0.3816101305864531</v>
+        <v>0.31</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -5406,11 +5394,11 @@
       </c>
       <c r="D38" s="9">
         <f t="shared" ref="D38:D69" si="4">IF($I$10=0,$B38,(1-$H$10)*LN(1+$I$10*$B38)/LN(1+$I$10)+$H$10*$B38)</f>
-        <v>0.26182487469087928</v>
+        <v>0.29902768133346697</v>
       </c>
       <c r="E38" s="9">
         <f t="shared" ref="E38:E69" si="5">IF($I$11=0,$B38,(1-$H$11)*LN(1+$I$11*$B38)/LN(1+$I$11)+$H$11*$B38)</f>
-        <v>0.39248413662535597</v>
+        <v>0.32</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -5430,11 +5418,11 @@
       </c>
       <c r="D39" s="12">
         <f t="shared" si="4"/>
-        <v>0.27061517076129021</v>
+        <v>0.30861348333521332</v>
       </c>
       <c r="E39" s="12">
         <f t="shared" si="5"/>
-        <v>0.40328362115381855</v>
+        <v>0.33</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -5454,11 +5442,11 @@
       </c>
       <c r="D40" s="9">
         <f t="shared" si="4"/>
-        <v>0.27944787797436538</v>
+        <v>0.31821563643948236</v>
       </c>
       <c r="E40" s="9">
         <f t="shared" si="5"/>
-        <v>0.41400970061474307</v>
+        <v>0.34</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -5478,11 +5466,11 @@
       </c>
       <c r="D41" s="12">
         <f t="shared" si="4"/>
-        <v>0.28832357211277315</v>
+        <v>0.32783431485279835</v>
       </c>
       <c r="E41" s="12">
         <f t="shared" si="5"/>
-        <v>0.42466346654849568</v>
+        <v>0.35</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -5502,11 +5490,11 @@
       </c>
       <c r="D42" s="9">
         <f t="shared" si="4"/>
-        <v>0.29724284076478735</v>
+        <v>0.33746969558062667</v>
       </c>
       <c r="E42" s="9">
         <f t="shared" si="5"/>
-        <v>0.43524598632805317</v>
+        <v>0.36</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -5526,11 +5514,11 @@
       </c>
       <c r="D43" s="12">
         <f t="shared" si="4"/>
-        <v>0.3062062836492514</v>
+        <v>0.34712195848765665</v>
       </c>
       <c r="E43" s="12">
         <f t="shared" si="5"/>
-        <v>0.44575830386722187</v>
+        <v>0.37</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -5550,11 +5538,11 @@
       </c>
       <c r="D44" s="9">
         <f t="shared" si="4"/>
-        <v>0.31521451295180247</v>
+        <v>0.35679128635971713</v>
       </c>
       <c r="E44" s="9">
         <f t="shared" si="5"/>
-        <v>0.45620144030309984</v>
+        <v>0.38</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -5574,11 +5562,11 @@
       </c>
       <c r="D45" s="12">
         <f t="shared" si="4"/>
-        <v>0.32426815367282602</v>
+        <v>0.36647786496737544</v>
       </c>
       <c r="E45" s="12">
         <f t="shared" si="5"/>
-        <v>0.46657639465390466</v>
+        <v>0.39</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -5598,11 +5586,11 @@
       </c>
       <c r="D46" s="9">
         <f t="shared" si="4"/>
-        <v>0.33336784398763486</v>
+        <v>0.37618188313127832</v>
       </c>
       <c r="E46" s="9">
         <f t="shared" si="5"/>
-        <v>0.47688414445321758</v>
+        <v>0.4</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -5622,11 +5610,11 @@
       </c>
       <c r="D47" s="12">
         <f t="shared" si="4"/>
-        <v>0.3425142356193922</v>
+        <v>0.38590353278928913</v>
       </c>
       <c r="E47" s="12">
         <f t="shared" si="5"/>
-        <v>0.48712564636166195</v>
+        <v>0.41</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -5646,11 +5634,11 @@
       </c>
       <c r="D48" s="9">
         <f t="shared" si="4"/>
-        <v>0.35170799422532273</v>
+        <v>0.39564300906548427</v>
       </c>
       <c r="E48" s="9">
         <f t="shared" si="5"/>
-        <v>0.4973018367569616</v>
+        <v>0.42</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -5670,11 +5658,11 @@
       </c>
       <c r="D49" s="12">
         <f t="shared" si="4"/>
-        <v>0.36094979979678654</v>
+        <v>0.40540051034106744</v>
       </c>
       <c r="E49" s="12">
         <f t="shared" si="5"/>
-        <v>0.50741363230329817</v>
+        <v>0.43</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -5694,11 +5682,11 @@
       </c>
       <c r="D50" s="9">
         <f t="shared" si="4"/>
-        <v>0.37024034707381337</v>
+        <v>0.4151762383272693</v>
       </c>
       <c r="E50" s="9">
         <f t="shared" si="5"/>
-        <v>0.51746193050082889</v>
+        <v>0.44</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -5718,11 +5706,11 @@
       </c>
       <c r="D51" s="12">
         <f t="shared" si="4"/>
-        <v>0.37958034597473334</v>
+        <v>0.42497039814029708</v>
       </c>
       <c r="E51" s="12">
         <f t="shared" si="5"/>
-        <v>0.5274476102161888</v>
+        <v>0.45</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -5742,11 +5730,11 @@
       </c>
       <c r="D52" s="9">
         <f t="shared" si="4"/>
-        <v>0.38897052204156446</v>
+        <v>0.43478319837840529</v>
       </c>
       <c r="E52" s="9">
         <f t="shared" si="5"/>
-        <v>0.5373715321947633</v>
+        <v>0.46</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -5766,11 +5754,11 @@
       </c>
       <c r="D53" s="12">
         <f t="shared" si="4"/>
-        <v>0.39841161690185894</v>
+        <v>0.44461485120115912</v>
       </c>
       <c r="E53" s="12">
         <f t="shared" si="5"/>
-        <v>0.54723453955547574</v>
+        <v>0.47</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -5790,11 +5778,11 @@
       </c>
       <c r="D54" s="9">
         <f t="shared" si="4"/>
-        <v>0.40790438874774249</v>
+        <v>0.45446557241096708</v>
       </c>
       <c r="E54" s="9">
         <f t="shared" si="5"/>
-        <v>0.55703745826880269</v>
+        <v>0.48</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -5814,11 +5802,11 @@
       </c>
       <c r="D55" s="12">
         <f t="shared" si="4"/>
-        <v>0.4174496128329182</v>
+        <v>0.46433558153695859</v>
       </c>
       <c r="E55" s="12">
         <f t="shared" si="5"/>
-        <v>0.56678109761869333</v>
+        <v>0.49</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -5838,11 +5826,11 @@
       </c>
       <c r="D56" s="9">
         <f t="shared" si="4"/>
-        <v>0.42704808198845362</v>
+        <v>0.47422510192129119</v>
       </c>
       <c r="E56" s="9">
         <f t="shared" si="5"/>
-        <v>0.57646625064904067</v>
+        <v>0.5</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -5862,11 +5850,11 @@
       </c>
       <c r="D57" s="12">
         <f t="shared" si="4"/>
-        <v>0.43670060715820669</v>
+        <v>0.48413436080797057</v>
       </c>
       <c r="E57" s="12">
         <f t="shared" si="5"/>
-        <v>0.5860936945953189</v>
+        <v>0.51</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -5886,11 +5874,11 @@
       </c>
       <c r="D58" s="9">
         <f t="shared" si="4"/>
-        <v>0.44640801795479484</v>
+        <v>0.49406358943427087</v>
       </c>
       <c r="E58" s="9">
         <f t="shared" si="5"/>
-        <v>0.59566419130197479</v>
+        <v>0.52</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -5910,11 +5898,11 @@
       </c>
       <c r="D59" s="12">
         <f t="shared" si="4"/>
-        <v>0.45617116323706058</v>
+        <v>0.50401302312484997</v>
       </c>
       <c r="E59" s="12">
         <f t="shared" si="5"/>
-        <v>0.60517848762613446</v>
+        <v>0.53</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -5934,11 +5922,11 @@
       </c>
       <c r="D60" s="9">
         <f t="shared" si="4"/>
-        <v>0.46599091171004031</v>
+        <v>0.51398290138865232</v>
       </c>
       <c r="E60" s="9">
         <f t="shared" si="5"/>
-        <v>0.61463731582815906</v>
+        <v>0.54</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -5958,11 +5946,11 @@
       </c>
       <c r="D61" s="12">
         <f t="shared" si="4"/>
-        <v>0.47586815254849502</v>
+        <v>0.52397346801870159</v>
       </c>
       <c r="E61" s="12">
         <f t="shared" si="5"/>
-        <v>0.62404139394956171</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -5982,11 +5970,11 @@
       </c>
       <c r="D62" s="9">
         <f t="shared" si="4"/>
-        <v>0.48580379604512214</v>
+        <v>0.53398497119488564</v>
       </c>
       <c r="E62" s="9">
         <f t="shared" si="5"/>
-        <v>0.63339142617877142</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -6006,11 +5994,11 @@
       </c>
       <c r="D63" s="12">
         <f t="shared" si="4"/>
-        <v>0.49579877428463126</v>
+        <v>0.54401766358984305</v>
       </c>
       <c r="E63" s="12">
         <f t="shared" si="5"/>
-        <v>0.64268810320521186</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -6030,11 +6018,11 @@
       </c>
       <c r="D64" s="9">
         <f t="shared" si="4"/>
-        <v>0.50585404184493254</v>
+        <v>0.55407180247806387</v>
       </c>
       <c r="E64" s="9">
         <f t="shared" si="5"/>
-        <v>0.65193210256214051</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -6054,11 +6042,11 @@
       </c>
       <c r="D65" s="12">
         <f t="shared" si="4"/>
-        <v>0.51597057652675415</v>
+        <v>0.56414764984832111</v>
       </c>
       <c r="E65" s="12">
         <f t="shared" si="5"/>
-        <v>0.66112408895866737</v>
+        <v>0.59</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -6078,11 +6066,11 @@
       </c>
       <c r="D66" s="9">
         <f t="shared" si="4"/>
-        <v>0.5261493801130871</v>
+        <v>0.57424547251955871</v>
       </c>
       <c r="E66" s="9">
         <f t="shared" si="5"/>
-        <v>0.67026471460137405</v>
+        <v>0.6</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
@@ -6102,11 +6090,11 @@
       </c>
       <c r="D67" s="12">
         <f t="shared" si="4"/>
-        <v>0.53639147915992924</v>
+        <v>0.58436554226036197</v>
       </c>
       <c r="E67" s="12">
         <f t="shared" si="5"/>
-        <v>0.67935461950590303</v>
+        <v>0.61</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -6126,11 +6114,11 @@
       </c>
       <c r="D68" s="9">
         <f t="shared" si="4"/>
-        <v>0.54669792581989296</v>
+        <v>0.59450813591214391</v>
       </c>
       <c r="E68" s="9">
         <f t="shared" si="5"/>
-        <v>0.68839443179891013</v>
+        <v>0.62</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -6150,11 +6138,11 @@
       </c>
       <c r="D69" s="12">
         <f t="shared" si="4"/>
-        <v>0.55706979870032503</v>
+        <v>0.60467353551618852</v>
       </c>
       <c r="E69" s="12">
         <f t="shared" si="5"/>
-        <v>0.69738476801071747</v>
+        <v>0.63</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
@@ -6174,11 +6162,11 @@
       </c>
       <c r="D70" s="9">
         <f t="shared" ref="D70:D106" si="7">IF($I$10=0,$B70,(1-$H$10)*LN(1+$I$10*$B70)/LN(1+$I$10)+$H$10*$B70)</f>
-        <v>0.56750820375769195</v>
+        <v>0.61486202844469695</v>
       </c>
       <c r="E70" s="9">
         <f t="shared" ref="E70:E106" si="8">IF($I$11=0,$B70,(1-$H$11)*LN(1+$I$11*$B70)/LN(1+$I$11)+$H$11*$B70)</f>
-        <v>0.70632623335902323</v>
+        <v>0.64</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
@@ -6198,11 +6186,11 @@
       </c>
       <c r="D71" s="12">
         <f t="shared" si="7"/>
-        <v>0.5780142752300842</v>
+        <v>0.62507390753598646</v>
       </c>
       <c r="E71" s="12">
         <f t="shared" si="8"/>
-        <v>0.71521942202398203</v>
+        <v>0.65</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -6222,11 +6210,11 @@
       </c>
       <c r="D72" s="9">
         <f t="shared" si="7"/>
-        <v>0.58858917660980759</v>
+        <v>0.63530947123400461</v>
       </c>
       <c r="E72" s="9">
         <f t="shared" si="8"/>
-        <v>0.72406491741498025</v>
+        <v>0.66</v>
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
@@ -6246,11 +6234,11 @@
       </c>
       <c r="D73" s="12">
         <f t="shared" si="7"/>
-        <v>0.59923410165814361</v>
+        <v>0.64556902373232139</v>
       </c>
       <c r="E73" s="12">
         <f t="shared" si="8"/>
-        <v>0.73286329242939496</v>
+        <v>0.67</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
@@ -6270,11 +6258,11 @@
       </c>
       <c r="D74" s="9">
         <f t="shared" si="7"/>
-        <v>0.60995027546449632</v>
+        <v>0.65585287512277568</v>
       </c>
       <c r="E74" s="9">
         <f t="shared" si="8"/>
-        <v>0.74161510970363209</v>
+        <v>0.68</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -6294,11 +6282,11 @@
       </c>
       <c r="D75" s="12">
         <f t="shared" si="7"/>
-        <v>0.62073895555227376</v>
+        <v>0.66616134154895701</v>
       </c>
       <c r="E75" s="12">
         <f t="shared" si="8"/>
-        <v>0.75032092185671373</v>
+        <v>0.69</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
@@ -6318,11 +6306,11 @@
       </c>
       <c r="D76" s="9">
         <f t="shared" si="7"/>
-        <v>0.63160143303400229</v>
+        <v>0.67649474536471166</v>
       </c>
       <c r="E76" s="9">
         <f t="shared" si="8"/>
-        <v>0.75898127172667929</v>
+        <v>0.7</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
@@ -6342,11 +6330,11 @@
       </c>
       <c r="D77" s="12">
         <f t="shared" si="7"/>
-        <v>0.64253903381832389</v>
+        <v>0.68685341529787225</v>
       </c>
       <c r="E77" s="12">
         <f t="shared" si="8"/>
-        <v>0.76759669260005581</v>
+        <v>0.71</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -6366,11 +6354,11 @@
       </c>
       <c r="D78" s="9">
         <f t="shared" si="7"/>
-        <v>0.65355311987170273</v>
+        <v>0.69723768661941943</v>
       </c>
       <c r="E78" s="9">
         <f t="shared" si="8"/>
-        <v>0.77616770843463589</v>
+        <v>0.72</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
@@ -6390,11 +6378,11 @@
       </c>
       <c r="D79" s="12">
         <f t="shared" si="7"/>
-        <v>0.66464509053784282</v>
+        <v>0.70764790131829303</v>
       </c>
       <c r="E79" s="12">
         <f t="shared" si="8"/>
-        <v>0.78469483407579999</v>
+        <v>0.73</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
@@ -6414,11 +6402,11 @@
       </c>
       <c r="D80" s="9">
         <f t="shared" si="7"/>
-        <v>0.67581638391801158</v>
+        <v>0.71808440828207987</v>
       </c>
       <c r="E80" s="9">
         <f t="shared" si="8"/>
-        <v>0.7931785754666032</v>
+        <v>0.74</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
@@ -6438,11 +6426,11 @@
       </c>
       <c r="D81" s="12">
         <f t="shared" si="7"/>
-        <v>0.68706847831567486</v>
+        <v>0.72854756348381833</v>
       </c>
       <c r="E81" s="12">
         <f t="shared" si="8"/>
-        <v>0.80161942985184376</v>
+        <v>0.75</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
@@ -6462,11 +6450,11 @@
       </c>
       <c r="D82" s="9">
         <f t="shared" si="7"/>
-        <v>0.69840289374907738</v>
+        <v>0.73903773017516727</v>
       </c>
       <c r="E82" s="9">
         <f t="shared" si="8"/>
-        <v>0.81001788597631541</v>
+        <v>0.76</v>
       </c>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
@@ -6486,11 +6474,11 @@
       </c>
       <c r="D83" s="12">
         <f t="shared" si="7"/>
-        <v>0.70982119353563444</v>
+        <v>0.74955527908620567</v>
       </c>
       <c r="E83" s="12">
         <f t="shared" si="8"/>
-        <v>0.81837442427744556</v>
+        <v>0.77</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
@@ -6510,11 +6498,11 @@
       </c>
       <c r="D84" s="9">
         <f t="shared" si="7"/>
-        <v>0.72132498595226613</v>
+        <v>0.76010058863213303</v>
       </c>
       <c r="E84" s="9">
         <f t="shared" si="8"/>
-        <v>0.82668951707250571</v>
+        <v>0.78</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
@@ -6534,11 +6522,11 @@
       </c>
       <c r="D85" s="12">
         <f t="shared" si="7"/>
-        <v>0.73291592597608868</v>
+        <v>0.77067404512716231</v>
       </c>
       <c r="E85" s="12">
         <f t="shared" si="8"/>
-        <v>0.83496362874057861</v>
+        <v>0.79</v>
       </c>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
@@ -6558,11 +6546,11 @@
       </c>
       <c r="D86" s="9">
         <f t="shared" si="7"/>
-        <v>0.74459571711016936</v>
+        <v>0.78127604300590525</v>
       </c>
       <c r="E86" s="9">
         <f t="shared" si="8"/>
-        <v>0.84319721589945518</v>
+        <v>0.8</v>
       </c>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
@@ -6582,11 +6570,11 @@
       </c>
       <c r="D87" s="12">
         <f t="shared" si="7"/>
-        <v>0.75636611329938919</v>
+        <v>0.79190698505256951</v>
       </c>
       <c r="E87" s="12">
         <f t="shared" si="8"/>
-        <v>0.85139072757763268</v>
+        <v>0.81</v>
       </c>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
@@ -6606,11 +6594,11 @@
       </c>
       <c r="D88" s="9">
         <f t="shared" si="7"/>
-        <v>0.76822892094179585</v>
+        <v>0.80256728263829913</v>
       </c>
       <c r="E88" s="9">
         <f t="shared" si="8"/>
-        <v>0.85954460538157429</v>
+        <v>0.82</v>
       </c>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
@@ -6630,11 +6618,11 @@
       </c>
       <c r="D89" s="12">
         <f t="shared" si="7"/>
-        <v>0.7801860010012226</v>
+        <v>0.81325735596700799</v>
       </c>
       <c r="E89" s="12">
         <f t="shared" si="8"/>
-        <v>0.86765928365838596</v>
+        <v>0.83</v>
       </c>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
@@ -6654,11 +6642,11 @@
       </c>
       <c r="D90" s="9">
         <f t="shared" si="7"/>
-        <v>0.7922392712273485</v>
+        <v>0.82397763433007598</v>
       </c>
       <c r="E90" s="9">
         <f t="shared" si="8"/>
-        <v>0.87573518965405928</v>
+        <v>0.84</v>
       </c>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
@@ -6678,11 +6666,11 @@
       </c>
       <c r="D91" s="12">
         <f t="shared" si="7"/>
-        <v>0.80439070848982852</v>
+        <v>0.83472855637028831</v>
       </c>
       <c r="E91" s="12">
         <f t="shared" si="8"/>
-        <v>0.88377274366742875</v>
+        <v>0.85</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
@@ -6702,11 +6690,11 @@
       </c>
       <c r="D92" s="9">
         <f t="shared" si="7"/>
-        <v>0.81664235123359474</v>
+        <v>0.84551057035543264</v>
       </c>
       <c r="E92" s="9">
         <f t="shared" si="8"/>
-        <v>0.89177235919997588</v>
+        <v>0.86</v>
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
@@ -6726,11 +6714,11 @@
       </c>
       <c r="D93" s="12">
         <f t="shared" si="7"/>
-        <v>0.82899630206296215</v>
+        <v>0.85632413446197142</v>
       </c>
       <c r="E93" s="12">
         <f t="shared" si="8"/>
-        <v>0.89973444310162098</v>
+        <v>0.87</v>
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
@@ -6750,11 +6738,11 @@
       </c>
       <c r="D94" s="9">
         <f t="shared" si="7"/>
-        <v>0.84145473046272989</v>
+        <v>0.8671697170692455</v>
       </c>
       <c r="E94" s="9">
         <f t="shared" si="8"/>
-        <v>0.90765939571262133</v>
+        <v>0.88</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
@@ -6774,11 +6762,11 @@
       </c>
       <c r="D95" s="12">
         <f t="shared" si="7"/>
-        <v>0.85401987566508752</v>
+        <v>0.87804779706467562</v>
       </c>
       <c r="E95" s="12">
         <f t="shared" si="8"/>
-        <v>0.91554761100171322</v>
+        <v>0.89</v>
       </c>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
@@ -6798,11 +6786,11 @@
       </c>
       <c r="D96" s="9">
         <f t="shared" si="7"/>
-        <v>0.86669404967180197</v>
+        <v>0.88895886416046532</v>
       </c>
       <c r="E96" s="9">
         <f t="shared" si="8"/>
-        <v>0.92339947670060074</v>
+        <v>0.9</v>
       </c>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
@@ -6822,11 +6810,11 @@
       </c>
       <c r="D97" s="12">
         <f t="shared" si="7"/>
-        <v>0.87947964044189242</v>
+        <v>0.89990341922232331</v>
       </c>
       <c r="E97" s="12">
         <f t="shared" si="8"/>
-        <v>0.93121537443492164</v>
+        <v>0.91</v>
       </c>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
@@ -6846,11 +6834,11 @@
       </c>
       <c r="D98" s="9">
         <f t="shared" si="7"/>
-        <v>0.89237911525578284</v>
+        <v>0.91088197461076126</v>
       </c>
       <c r="E98" s="9">
         <f t="shared" si="8"/>
-        <v>0.93899567985178833</v>
+        <v>0.92</v>
       </c>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
@@ -6870,11 +6858,11 @@
       </c>
       <c r="D99" s="12">
         <f t="shared" si="7"/>
-        <v>0.90539502426779028</v>
+        <v>0.92189505453554421</v>
       </c>
       <c r="E99" s="12">
         <f t="shared" si="8"/>
-        <v>0.9467407627440203</v>
+        <v>0.93</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
@@ -6894,11 +6882,11 @@
       </c>
       <c r="D100" s="9">
         <f t="shared" si="7"/>
-        <v>0.91853000425974562</v>
+        <v>0.93294319542391368</v>
       </c>
       <c r="E100" s="9">
         <f t="shared" si="8"/>
-        <v>0.95445098717116272</v>
+        <v>0.94</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
@@ -6918,11 +6906,11 @@
       </c>
       <c r="D101" s="12">
         <f t="shared" si="7"/>
-        <v>0.93178678260956671</v>
+        <v>0.94402694630322204</v>
       </c>
       <c r="E101" s="12">
         <f t="shared" si="8"/>
-        <v>0.96212671157739738</v>
+        <v>0.95</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
@@ -6942,11 +6930,11 @@
       </c>
       <c r="D102" s="9">
         <f t="shared" si="7"/>
-        <v>0.94516818148972548</v>
+        <v>0.95514686919866731</v>
       </c>
       <c r="E102" s="9">
         <f t="shared" si="8"/>
-        <v>0.96976828890643507</v>
+        <v>0.96</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
@@ -6966,11 +6954,11 @@
       </c>
       <c r="D103" s="12">
         <f t="shared" si="7"/>
-        <v>0.95867712231178137</v>
+        <v>0.96630353954684489</v>
       </c>
       <c r="E103" s="12">
         <f t="shared" si="8"/>
-        <v>0.97737606671348642</v>
+        <v>0.97</v>
       </c>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
@@ -6990,11 +6978,11 @@
       </c>
       <c r="D104" s="9">
         <f t="shared" si="7"/>
-        <v>0.97231663043448913</v>
+        <v>0.97749754662588029</v>
       </c>
       <c r="E104" s="9">
         <f t="shared" si="8"/>
-        <v>0.98495038727439643</v>
+        <v>0.98</v>
       </c>
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
@@ -7014,11 +7002,11 @@
       </c>
       <c r="D105" s="12">
         <f t="shared" si="7"/>
-        <v>0.98608984015446355</v>
+        <v>0.98872949400294385</v>
       </c>
       <c r="E105" s="12">
         <f t="shared" si="8"/>
-        <v>0.99249158769203172</v>
+        <v>0.99</v>
       </c>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
